--- a/Översikt HALLSTAHAMMAR.xlsx
+++ b/Översikt HALLSTAHAMMAR.xlsx
@@ -601,7 +601,7 @@
         <v>45978</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -713,7 +713,7 @@
         <v>44635</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -791,7 +791,7 @@
         <v>44887</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -864,7 +864,7 @@
         <v>44502</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -937,7 +937,7 @@
         <v>44502</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1010,7 +1010,7 @@
         <v>44739</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1083,7 +1083,7 @@
         <v>44502</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1139,7 +1139,7 @@
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 10263-2024</t>
+          <t>A 21264-2022</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1153,10 +1153,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>45365</v>
+        <v>44705</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1170,11 +1170,11 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Kyrkan</t>
+          <t>Allmännings- och besparingsskogar</t>
         </is>
       </c>
       <c r="I9" t="n">
-        <v>1.4</v>
+        <v>2.4</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -1217,7 +1217,7 @@
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 22072-2023</t>
+          <t>A 21972-2023</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1231,10 +1231,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>45069</v>
+        <v>45068</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1247,7 +1247,7 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>3.5</v>
+        <v>1.5</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
@@ -1290,7 +1290,7 @@
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 34984-2024</t>
+          <t>A 10263-2024</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1304,10 +1304,10 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>45527</v>
+        <v>45365</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1319,8 +1319,13 @@
           <t>HALLSTAHAMMAR</t>
         </is>
       </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I11" t="n">
-        <v>4.1</v>
+        <v>1.4</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -1363,7 +1368,7 @@
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 55562-2022</t>
+          <t>A 1622-2026</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1377,10 +1382,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>44888</v>
+        <v>46034</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1393,7 +1398,7 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>0.8</v>
+        <v>1.4</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -1436,7 +1441,7 @@
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 16762-2022</t>
+          <t>A 1621-2026</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1450,10 +1455,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>44673</v>
+        <v>46034</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1466,7 +1471,7 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>4.2</v>
+        <v>1.4</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
@@ -1509,7 +1514,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 42991-2025</t>
+          <t>A 55562-2022</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1523,10 +1528,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>45909</v>
+        <v>44888</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1539,7 +1544,7 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>7.2</v>
+        <v>0.8</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -1582,7 +1587,7 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 43448-2025</t>
+          <t>A 42991-2025</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1596,10 +1601,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>45911</v>
+        <v>45909</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1612,7 +1617,7 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>1.2</v>
+        <v>7.2</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -1655,7 +1660,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 44192-2025</t>
+          <t>A 43448-2025</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1669,10 +1674,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45915</v>
+        <v>45911</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1685,7 +1690,7 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>0.8</v>
+        <v>1.2</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -1728,7 +1733,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 37072-2025</t>
+          <t>A 44192-2025</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1742,10 +1747,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>45875</v>
+        <v>45915</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1758,7 +1763,7 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>1.5</v>
+        <v>0.8</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -1801,7 +1806,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 37076-2025</t>
+          <t>A 37072-2025</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1818,7 +1823,7 @@
         <v>45875</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -1831,7 +1836,7 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>2.4</v>
+        <v>1.5</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -1874,7 +1879,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 13510-2025</t>
+          <t>A 37076-2025</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1888,10 +1893,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>45736</v>
+        <v>45875</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -1904,7 +1909,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -1947,7 +1952,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 10069-2026</t>
+          <t>A 12077-2022</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1961,10 +1966,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>46073</v>
+        <v>44636</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -1976,13 +1981,8 @@
           <t>HALLSTAHAMMAR</t>
         </is>
       </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I20" t="n">
-        <v>13</v>
+        <v>2.1</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2025,7 +2025,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 15224-2026</t>
+          <t>A 13510-2025</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2039,10 +2039,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>46105</v>
+        <v>45736</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2054,13 +2054,8 @@
           <t>HALLSTAHAMMAR</t>
         </is>
       </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I21" t="n">
-        <v>1.5</v>
+        <v>2.5</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2103,7 +2098,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 15230-2026</t>
+          <t>A 10069-2026</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2117,10 +2112,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>46105</v>
+        <v>46073</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2138,7 +2133,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>1.5</v>
+        <v>13</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2181,7 +2176,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 58125-2025</t>
+          <t>A 37407-2023</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2195,10 +2190,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>45982</v>
+        <v>45156</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2211,7 +2206,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>0.8</v>
+        <v>3.3</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2254,7 +2249,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 58109-2025</t>
+          <t>A 15224-2026</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2268,10 +2263,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45982</v>
+        <v>46105</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2283,8 +2278,13 @@
           <t>HALLSTAHAMMAR</t>
         </is>
       </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I24" t="n">
-        <v>2.5</v>
+        <v>1.5</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2327,7 +2327,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 58111-2025</t>
+          <t>A 15230-2026</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2341,10 +2341,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>45982</v>
+        <v>46105</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2356,8 +2356,13 @@
           <t>HALLSTAHAMMAR</t>
         </is>
       </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I25" t="n">
-        <v>0.6</v>
+        <v>1.5</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2400,7 +2405,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 21972-2023</t>
+          <t>A 58109-2025</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2414,10 +2419,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>45068</v>
+        <v>45982</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2430,7 +2435,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>1.5</v>
+        <v>2.5</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2473,7 +2478,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 1621-2026</t>
+          <t>A 58111-2025</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2487,10 +2492,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>46034</v>
+        <v>45982</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2503,7 +2508,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>1.4</v>
+        <v>0.6</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -2546,7 +2551,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 1622-2026</t>
+          <t>A 58125-2025</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2560,10 +2565,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>46034</v>
+        <v>45982</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2576,7 +2581,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>1.4</v>
+        <v>0.8</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -2619,7 +2624,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 35036-2024</t>
+          <t>A 21049-2026</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2633,10 +2638,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>45527</v>
+        <v>46146</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2649,7 +2654,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>1.7</v>
+        <v>2.9</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -2692,7 +2697,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 62831-2023</t>
+          <t>A 14149-2022</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2706,10 +2711,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>45270</v>
+        <v>44651</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -2721,8 +2726,13 @@
           <t>HALLSTAHAMMAR</t>
         </is>
       </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I30" t="n">
-        <v>1.1</v>
+        <v>3.8</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -2765,7 +2775,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 8848-2025</t>
+          <t>A 53343-2024</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2779,10 +2789,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45713</v>
+        <v>45614</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -2795,7 +2805,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>2</v>
+        <v>0.9</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -2838,7 +2848,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 21049-2026</t>
+          <t>A 8848-2025</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2852,10 +2862,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>46146</v>
+        <v>45713</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -2868,7 +2878,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>2.9</v>
+        <v>2</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -2911,7 +2921,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 30766-2022</t>
+          <t>A 54207-2025</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2925,10 +2935,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>44764</v>
+        <v>45964</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -2941,7 +2951,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>0.6</v>
+        <v>2.1</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -2984,7 +2994,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 54207-2025</t>
+          <t>A 26059-2026</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2998,10 +3008,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>45964</v>
+        <v>46181</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3014,7 +3024,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>2.1</v>
+        <v>4.7</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3057,7 +3067,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 7245-2025</t>
+          <t>A 26060-2026</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3071,10 +3081,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>45702</v>
+        <v>46181</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3087,7 +3097,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>4</v>
+        <v>3.6</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3147,7 +3157,7 @@
         <v>44977</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3208,7 +3218,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 26059-2026</t>
+          <t>A 7245-2025</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3222,10 +3232,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>46181</v>
+        <v>45702</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3238,7 +3248,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>4.7</v>
+        <v>4</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3281,7 +3291,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 26060-2026</t>
+          <t>A 34984-2024</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3295,10 +3305,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>46181</v>
+        <v>45527</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3311,7 +3321,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>3.6</v>
+        <v>4.1</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3354,7 +3364,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 21264-2022</t>
+          <t>A 35238-2026</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3364,14 +3374,14 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>44705</v>
+        <v>46260</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3383,13 +3393,8 @@
           <t>HALLSTAHAMMAR</t>
         </is>
       </c>
-      <c r="H39" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I39" t="n">
-        <v>2.4</v>
+        <v>3.3</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3432,7 +3437,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 12077-2022</t>
+          <t>A 37109-2026</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3446,10 +3451,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>44636</v>
+        <v>46274</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3462,7 +3467,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>2.1</v>
+        <v>3</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -3505,7 +3510,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 37407-2023</t>
+          <t>A 16762-2022</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3519,10 +3524,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45156</v>
+        <v>44673</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3535,7 +3540,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>3.3</v>
+        <v>4.2</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -3578,7 +3583,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 35238-2026</t>
+          <t>A 22072-2023</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3588,14 +3593,14 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>46260</v>
+        <v>45069</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3608,7 +3613,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -3651,7 +3656,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 14149-2022</t>
+          <t>A 30766-2022</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3665,10 +3670,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>44651</v>
+        <v>44764</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -3680,13 +3685,8 @@
           <t>HALLSTAHAMMAR</t>
         </is>
       </c>
-      <c r="H43" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I43" t="n">
-        <v>3.8</v>
+        <v>0.6</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -3729,7 +3729,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 37109-2026</t>
+          <t>A 35036-2024</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3743,10 +3743,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>46274</v>
+        <v>45527</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -3759,7 +3759,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>3</v>
+        <v>1.7</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -3802,7 +3802,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 53343-2024</t>
+          <t>A 62831-2023</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3816,10 +3816,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45614</v>
+        <v>45270</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -3832,7 +3832,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>0.9</v>
+        <v>1.1</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -3892,7 +3892,7 @@
         <v>46091</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -3965,7 +3965,7 @@
         <v>46111</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>

--- a/Översikt HALLSTAHAMMAR.xlsx
+++ b/Översikt HALLSTAHAMMAR.xlsx
@@ -601,7 +601,7 @@
         <v>45978</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -713,7 +713,7 @@
         <v>44635</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -791,7 +791,7 @@
         <v>44887</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -864,7 +864,7 @@
         <v>44502</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -937,7 +937,7 @@
         <v>44502</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1010,7 +1010,7 @@
         <v>44739</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A 68621-2021</t>
+          <t>A 7245-2025</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1080,10 +1080,10 @@
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>44502</v>
+        <v>45702</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1096,7 +1096,7 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -1139,7 +1139,7 @@
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 21264-2022</t>
+          <t>A 10263-2024</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1153,10 +1153,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>44705</v>
+        <v>45365</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1170,11 +1170,11 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Allmännings- och besparingsskogar</t>
+          <t>Kyrkan</t>
         </is>
       </c>
       <c r="I9" t="n">
-        <v>2.4</v>
+        <v>1.4</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -1217,7 +1217,7 @@
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 21972-2023</t>
+          <t>A 68621-2021</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1231,10 +1231,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>45068</v>
+        <v>44502</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1247,7 +1247,7 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>1.5</v>
+        <v>3.8</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
@@ -1290,7 +1290,7 @@
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 10263-2024</t>
+          <t>A 37072-2025</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1304,10 +1304,10 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>45365</v>
+        <v>45875</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1319,13 +1319,8 @@
           <t>HALLSTAHAMMAR</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I11" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -1368,7 +1363,7 @@
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 1622-2026</t>
+          <t>A 37076-2025</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1382,10 +1377,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>46034</v>
+        <v>45875</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1398,7 +1393,7 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>1.4</v>
+        <v>2.4</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -1441,7 +1436,7 @@
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 1621-2026</t>
+          <t>A 13510-2025</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1455,10 +1450,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>46034</v>
+        <v>45736</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1471,7 +1466,7 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>1.4</v>
+        <v>2.5</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
@@ -1514,7 +1509,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 55562-2022</t>
+          <t>A 34984-2024</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1528,10 +1523,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>44888</v>
+        <v>45527</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1544,7 +1539,7 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>0.8</v>
+        <v>4.1</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -1587,7 +1582,7 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 42991-2025</t>
+          <t>A 10069-2026</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1601,10 +1596,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>45909</v>
+        <v>46073</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1616,8 +1611,13 @@
           <t>HALLSTAHAMMAR</t>
         </is>
       </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I15" t="n">
-        <v>7.2</v>
+        <v>13</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -1660,7 +1660,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 43448-2025</t>
+          <t>A 22072-2023</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1674,10 +1674,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45911</v>
+        <v>45069</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1690,7 +1690,7 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>1.2</v>
+        <v>3.5</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -1733,7 +1733,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 44192-2025</t>
+          <t>A 42991-2025</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1747,10 +1747,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>45915</v>
+        <v>45909</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1763,7 +1763,7 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>0.8</v>
+        <v>7.2</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -1806,7 +1806,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 37072-2025</t>
+          <t>A 15224-2026</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1820,10 +1820,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>45875</v>
+        <v>46105</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -1833,6 +1833,11 @@
       <c r="G18" t="inlineStr">
         <is>
           <t>HALLSTAHAMMAR</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
         </is>
       </c>
       <c r="I18" t="n">
@@ -1879,7 +1884,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 37076-2025</t>
+          <t>A 15230-2026</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1893,10 +1898,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>45875</v>
+        <v>46105</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -1908,8 +1913,13 @@
           <t>HALLSTAHAMMAR</t>
         </is>
       </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I19" t="n">
-        <v>2.4</v>
+        <v>1.5</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -1952,7 +1962,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 12077-2022</t>
+          <t>A 43448-2025</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1966,10 +1976,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>44636</v>
+        <v>45911</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -1982,7 +1992,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>2.1</v>
+        <v>1.2</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2025,7 +2035,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 13510-2025</t>
+          <t>A 44192-2025</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2039,10 +2049,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>45736</v>
+        <v>45915</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2055,7 +2065,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>2.5</v>
+        <v>0.8</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2098,7 +2108,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 10069-2026</t>
+          <t>A 55562-2022</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2112,10 +2122,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>46073</v>
+        <v>44888</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2127,13 +2137,8 @@
           <t>HALLSTAHAMMAR</t>
         </is>
       </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I22" t="n">
-        <v>13</v>
+        <v>0.8</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2176,7 +2181,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 37407-2023</t>
+          <t>A 16762-2022</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2190,10 +2195,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>45156</v>
+        <v>44673</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2206,7 +2211,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>3.3</v>
+        <v>4.2</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2249,7 +2254,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 15224-2026</t>
+          <t>A 8436-2023</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2263,10 +2268,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>46105</v>
+        <v>44977</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2280,11 +2285,11 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Allmännings- och besparingsskogar</t>
+          <t>Kyrkan</t>
         </is>
       </c>
       <c r="I24" t="n">
-        <v>1.5</v>
+        <v>4</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2327,7 +2332,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 15230-2026</t>
+          <t>A 58125-2025</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2341,10 +2346,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>46105</v>
+        <v>45982</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2356,13 +2361,8 @@
           <t>HALLSTAHAMMAR</t>
         </is>
       </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I25" t="n">
-        <v>1.5</v>
+        <v>0.8</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2422,7 +2422,7 @@
         <v>45982</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2495,7 +2495,7 @@
         <v>45982</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2551,7 +2551,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 58125-2025</t>
+          <t>A 21049-2026</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2565,10 +2565,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>45982</v>
+        <v>46146</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2581,7 +2581,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>0.8</v>
+        <v>2.9</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -2624,7 +2624,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 21049-2026</t>
+          <t>A 54207-2025</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2638,10 +2638,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>46146</v>
+        <v>45964</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2654,7 +2654,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>2.9</v>
+        <v>2.1</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -2697,7 +2697,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 14149-2022</t>
+          <t>A 1621-2026</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2711,10 +2711,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>44651</v>
+        <v>46034</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -2726,13 +2726,8 @@
           <t>HALLSTAHAMMAR</t>
         </is>
       </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I30" t="n">
-        <v>3.8</v>
+        <v>1.4</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -2775,7 +2770,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 53343-2024</t>
+          <t>A 1622-2026</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2789,10 +2784,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45614</v>
+        <v>46034</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -2805,7 +2800,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>0.9</v>
+        <v>1.4</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -2848,7 +2843,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 8848-2025</t>
+          <t>A 21972-2023</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2862,10 +2857,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>45713</v>
+        <v>45068</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -2878,7 +2873,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -2921,7 +2916,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 54207-2025</t>
+          <t>A 35036-2024</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2935,10 +2930,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>45964</v>
+        <v>45527</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -2951,7 +2946,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>2.1</v>
+        <v>1.7</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -2994,7 +2989,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 26059-2026</t>
+          <t>A 62831-2023</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3008,10 +3003,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>46181</v>
+        <v>45270</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3024,7 +3019,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>4.7</v>
+        <v>1.1</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3067,7 +3062,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 26060-2026</t>
+          <t>A 21264-2022</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3081,10 +3076,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>46181</v>
+        <v>44705</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3096,8 +3091,13 @@
           <t>HALLSTAHAMMAR</t>
         </is>
       </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I35" t="n">
-        <v>3.6</v>
+        <v>2.4</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3140,7 +3140,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 8436-2023</t>
+          <t>A 12077-2022</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3154,10 +3154,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>44977</v>
+        <v>44636</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3169,13 +3169,8 @@
           <t>HALLSTAHAMMAR</t>
         </is>
       </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I36" t="n">
-        <v>4</v>
+        <v>2.1</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3218,7 +3213,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 7245-2025</t>
+          <t>A 37407-2023</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3232,10 +3227,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45702</v>
+        <v>45156</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3248,7 +3243,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>4</v>
+        <v>3.3</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3291,7 +3286,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 34984-2024</t>
+          <t>A 8848-2025</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3305,10 +3300,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45527</v>
+        <v>45713</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3321,7 +3316,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>4.1</v>
+        <v>2</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3364,7 +3359,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 35238-2026</t>
+          <t>A 26059-2026</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3374,14 +3369,14 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>46260</v>
+        <v>46181</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3394,7 +3389,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>3.3</v>
+        <v>4.7</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3437,7 +3432,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 37109-2026</t>
+          <t>A 26060-2026</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3451,10 +3446,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>46274</v>
+        <v>46181</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3467,7 +3462,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>3</v>
+        <v>3.6</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -3510,7 +3505,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 16762-2022</t>
+          <t>A 30766-2022</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3524,10 +3519,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>44673</v>
+        <v>44764</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3540,7 +3535,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>4.2</v>
+        <v>0.6</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -3583,7 +3578,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 22072-2023</t>
+          <t>A 14149-2022</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3597,10 +3592,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>45069</v>
+        <v>44651</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3612,8 +3607,13 @@
           <t>HALLSTAHAMMAR</t>
         </is>
       </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I42" t="n">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -3656,7 +3656,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 30766-2022</t>
+          <t>A 35238-2026</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3666,14 +3666,14 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>44764</v>
+        <v>46260</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -3686,7 +3686,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>0.6</v>
+        <v>3.3</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -3729,7 +3729,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 35036-2024</t>
+          <t>A 37109-2026</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3743,10 +3743,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45527</v>
+        <v>46274</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -3759,7 +3759,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>1.7</v>
+        <v>3</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -3802,7 +3802,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 62831-2023</t>
+          <t>A 53343-2024</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3816,10 +3816,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45270</v>
+        <v>45614</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -3832,7 +3832,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>1.1</v>
+        <v>0.9</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -3892,7 +3892,7 @@
         <v>46091</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -3965,7 +3965,7 @@
         <v>46111</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>

--- a/Översikt HALLSTAHAMMAR.xlsx
+++ b/Översikt HALLSTAHAMMAR.xlsx
@@ -601,7 +601,7 @@
         <v>45978</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -713,7 +713,7 @@
         <v>44635</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -791,7 +791,7 @@
         <v>44887</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -864,7 +864,7 @@
         <v>44502</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -937,7 +937,7 @@
         <v>44502</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1010,7 +1010,7 @@
         <v>44739</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A 7245-2025</t>
+          <t>A 68621-2021</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1080,10 +1080,10 @@
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>45702</v>
+        <v>44502</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1096,7 +1096,7 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -1139,7 +1139,7 @@
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 10263-2024</t>
+          <t>A 21264-2022</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1153,10 +1153,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>45365</v>
+        <v>44705</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1170,11 +1170,11 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Kyrkan</t>
+          <t>Allmännings- och besparingsskogar</t>
         </is>
       </c>
       <c r="I9" t="n">
-        <v>1.4</v>
+        <v>2.4</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -1217,7 +1217,7 @@
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 68621-2021</t>
+          <t>A 21972-2023</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1231,10 +1231,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>44502</v>
+        <v>45068</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1247,7 +1247,7 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>3.8</v>
+        <v>1.5</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
@@ -1290,7 +1290,7 @@
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 37072-2025</t>
+          <t>A 10263-2024</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1304,10 +1304,10 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>45875</v>
+        <v>45365</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1319,8 +1319,13 @@
           <t>HALLSTAHAMMAR</t>
         </is>
       </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I11" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -1363,7 +1368,7 @@
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 37076-2025</t>
+          <t>A 55562-2022</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1377,10 +1382,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>45875</v>
+        <v>44888</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1393,7 +1398,7 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>2.4</v>
+        <v>0.8</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -1436,7 +1441,7 @@
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 13510-2025</t>
+          <t>A 1622-2026</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1450,10 +1455,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>45736</v>
+        <v>46034</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1466,7 +1471,7 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>2.5</v>
+        <v>1.4</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
@@ -1509,7 +1514,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 34984-2024</t>
+          <t>A 1621-2026</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1523,10 +1528,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>45527</v>
+        <v>46034</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1539,7 +1544,7 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>4.1</v>
+        <v>1.4</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -1582,7 +1587,7 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 10069-2026</t>
+          <t>A 42991-2025</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1596,10 +1601,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>46073</v>
+        <v>45909</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1611,13 +1616,8 @@
           <t>HALLSTAHAMMAR</t>
         </is>
       </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I15" t="n">
-        <v>13</v>
+        <v>7.2</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -1660,7 +1660,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 22072-2023</t>
+          <t>A 43448-2025</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1674,10 +1674,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45069</v>
+        <v>45911</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1690,7 +1690,7 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>3.5</v>
+        <v>1.2</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -1733,7 +1733,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 42991-2025</t>
+          <t>A 44192-2025</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1747,10 +1747,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>45909</v>
+        <v>45915</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1763,7 +1763,7 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>7.2</v>
+        <v>0.8</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -1806,7 +1806,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 15224-2026</t>
+          <t>A 12077-2022</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1820,10 +1820,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>46105</v>
+        <v>44636</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -1835,13 +1835,8 @@
           <t>HALLSTAHAMMAR</t>
         </is>
       </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I18" t="n">
-        <v>1.5</v>
+        <v>2.1</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -1884,7 +1879,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 15230-2026</t>
+          <t>A 37407-2023</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1898,10 +1893,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>46105</v>
+        <v>45156</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -1913,13 +1908,8 @@
           <t>HALLSTAHAMMAR</t>
         </is>
       </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I19" t="n">
-        <v>1.5</v>
+        <v>3.3</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -1962,7 +1952,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 43448-2025</t>
+          <t>A 37072-2025</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1976,10 +1966,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>45911</v>
+        <v>45875</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -1992,7 +1982,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>1.2</v>
+        <v>1.5</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2035,7 +2025,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 44192-2025</t>
+          <t>A 37076-2025</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2049,10 +2039,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>45915</v>
+        <v>45875</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2065,7 +2055,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>0.8</v>
+        <v>2.4</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2108,7 +2098,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 55562-2022</t>
+          <t>A 13510-2025</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2122,10 +2112,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>44888</v>
+        <v>45736</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2138,7 +2128,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>0.8</v>
+        <v>2.5</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2181,7 +2171,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 16762-2022</t>
+          <t>A 58109-2025</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2195,10 +2185,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>44673</v>
+        <v>45982</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2211,7 +2201,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>4.2</v>
+        <v>2.5</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2254,7 +2244,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 8436-2023</t>
+          <t>A 58111-2025</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2268,10 +2258,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>44977</v>
+        <v>45982</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2283,13 +2273,8 @@
           <t>HALLSTAHAMMAR</t>
         </is>
       </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I24" t="n">
-        <v>4</v>
+        <v>0.6</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2349,7 +2334,7 @@
         <v>45982</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2405,7 +2390,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 58109-2025</t>
+          <t>A 10069-2026</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2419,10 +2404,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>45982</v>
+        <v>46073</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2434,8 +2419,13 @@
           <t>HALLSTAHAMMAR</t>
         </is>
       </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I26" t="n">
-        <v>2.5</v>
+        <v>13</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2478,7 +2468,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 58111-2025</t>
+          <t>A 15224-2026</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2492,10 +2482,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>45982</v>
+        <v>46105</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2507,8 +2497,13 @@
           <t>HALLSTAHAMMAR</t>
         </is>
       </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I27" t="n">
-        <v>0.6</v>
+        <v>1.5</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -2551,7 +2546,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 21049-2026</t>
+          <t>A 14149-2022</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2565,10 +2560,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>46146</v>
+        <v>44651</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2580,8 +2575,13 @@
           <t>HALLSTAHAMMAR</t>
         </is>
       </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I28" t="n">
-        <v>2.9</v>
+        <v>3.8</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -2624,7 +2624,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 54207-2025</t>
+          <t>A 15230-2026</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2638,10 +2638,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>45964</v>
+        <v>46105</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2653,8 +2653,13 @@
           <t>HALLSTAHAMMAR</t>
         </is>
       </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I29" t="n">
-        <v>2.1</v>
+        <v>1.5</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -2697,7 +2702,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 1621-2026</t>
+          <t>A 53343-2024</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2711,10 +2716,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>46034</v>
+        <v>45614</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -2727,7 +2732,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>1.4</v>
+        <v>0.9</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -2770,7 +2775,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 1622-2026</t>
+          <t>A 8848-2025</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2784,10 +2789,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>46034</v>
+        <v>45713</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -2800,7 +2805,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>1.4</v>
+        <v>2</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -2843,7 +2848,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 21972-2023</t>
+          <t>A 8436-2023</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2857,10 +2862,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>45068</v>
+        <v>44977</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -2872,8 +2877,13 @@
           <t>HALLSTAHAMMAR</t>
         </is>
       </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I32" t="n">
-        <v>1.5</v>
+        <v>4</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -2916,7 +2926,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 35036-2024</t>
+          <t>A 7245-2025</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2930,10 +2940,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>45527</v>
+        <v>45702</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -2946,7 +2956,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>1.7</v>
+        <v>4</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -2989,7 +2999,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 62831-2023</t>
+          <t>A 34984-2024</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3003,10 +3013,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>45270</v>
+        <v>45527</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3019,7 +3029,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>1.1</v>
+        <v>4.1</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3062,7 +3072,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 21264-2022</t>
+          <t>A 21049-2026</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3076,10 +3086,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>44705</v>
+        <v>46146</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3091,13 +3101,8 @@
           <t>HALLSTAHAMMAR</t>
         </is>
       </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I35" t="n">
-        <v>2.4</v>
+        <v>2.9</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3140,7 +3145,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 12077-2022</t>
+          <t>A 54207-2025</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3154,10 +3159,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>44636</v>
+        <v>45964</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3213,7 +3218,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 37407-2023</t>
+          <t>A 16762-2022</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3227,10 +3232,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45156</v>
+        <v>44673</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3243,7 +3248,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>3.3</v>
+        <v>4.2</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3286,7 +3291,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 8848-2025</t>
+          <t>A 22072-2023</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3300,10 +3305,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45713</v>
+        <v>45069</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3316,7 +3321,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>2</v>
+        <v>3.5</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3359,7 +3364,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 26059-2026</t>
+          <t>A 30766-2022</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3373,10 +3378,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>46181</v>
+        <v>44764</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3389,7 +3394,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>4.7</v>
+        <v>0.6</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3432,7 +3437,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 26060-2026</t>
+          <t>A 35036-2024</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3446,10 +3451,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>46181</v>
+        <v>45527</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3462,7 +3467,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>3.6</v>
+        <v>1.7</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -3505,7 +3510,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 30766-2022</t>
+          <t>A 26059-2026</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3519,10 +3524,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>44764</v>
+        <v>46181</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3535,7 +3540,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>0.6</v>
+        <v>4.7</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -3578,7 +3583,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 14149-2022</t>
+          <t>A 26060-2026</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3592,10 +3597,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>44651</v>
+        <v>46181</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3607,13 +3612,8 @@
           <t>HALLSTAHAMMAR</t>
         </is>
       </c>
-      <c r="H42" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I42" t="n">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -3673,7 +3673,7 @@
         <v>46260</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -3746,7 +3746,7 @@
         <v>46274</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -3802,7 +3802,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 53343-2024</t>
+          <t>A 62831-2023</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3816,10 +3816,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45614</v>
+        <v>45270</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -3832,7 +3832,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>0.9</v>
+        <v>1.1</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -3892,7 +3892,7 @@
         <v>46091</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -3965,7 +3965,7 @@
         <v>46111</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>

--- a/Översikt HALLSTAHAMMAR.xlsx
+++ b/Översikt HALLSTAHAMMAR.xlsx
@@ -601,7 +601,7 @@
         <v>45978</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -713,7 +713,7 @@
         <v>44635</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -791,7 +791,7 @@
         <v>44887</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -864,7 +864,7 @@
         <v>44502</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -937,7 +937,7 @@
         <v>44502</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1010,7 +1010,7 @@
         <v>44739</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1083,7 +1083,7 @@
         <v>44502</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1139,7 +1139,7 @@
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 21264-2022</t>
+          <t>A 10263-2024</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1153,10 +1153,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>44705</v>
+        <v>45365</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1170,11 +1170,11 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Allmännings- och besparingsskogar</t>
+          <t>Kyrkan</t>
         </is>
       </c>
       <c r="I9" t="n">
-        <v>2.4</v>
+        <v>1.4</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -1217,7 +1217,7 @@
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 21972-2023</t>
+          <t>A 34984-2024</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1231,10 +1231,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>45068</v>
+        <v>45527</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1247,7 +1247,7 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>1.5</v>
+        <v>4.1</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
@@ -1290,7 +1290,7 @@
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 10263-2024</t>
+          <t>A 22072-2023</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1304,10 +1304,10 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>45365</v>
+        <v>45069</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1319,13 +1319,8 @@
           <t>HALLSTAHAMMAR</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I11" t="n">
-        <v>1.4</v>
+        <v>3.5</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -1385,7 +1380,7 @@
         <v>44888</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1441,7 +1436,7 @@
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 1622-2026</t>
+          <t>A 10069-2026</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1455,10 +1450,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>46034</v>
+        <v>46073</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1470,8 +1465,13 @@
           <t>HALLSTAHAMMAR</t>
         </is>
       </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I13" t="n">
-        <v>1.4</v>
+        <v>13</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
@@ -1514,7 +1514,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 1621-2026</t>
+          <t>A 16762-2022</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1528,10 +1528,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>46034</v>
+        <v>44673</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1544,7 +1544,7 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>1.4</v>
+        <v>4.2</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -1587,7 +1587,7 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 42991-2025</t>
+          <t>A 15224-2026</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1601,10 +1601,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>45909</v>
+        <v>46105</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1616,8 +1616,13 @@
           <t>HALLSTAHAMMAR</t>
         </is>
       </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I15" t="n">
-        <v>7.2</v>
+        <v>1.5</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -1660,7 +1665,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 43448-2025</t>
+          <t>A 15230-2026</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1674,10 +1679,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45911</v>
+        <v>46105</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1689,8 +1694,13 @@
           <t>HALLSTAHAMMAR</t>
         </is>
       </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I16" t="n">
-        <v>1.2</v>
+        <v>1.5</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -1733,7 +1743,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 44192-2025</t>
+          <t>A 37072-2025</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1747,10 +1757,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>45915</v>
+        <v>45875</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1763,7 +1773,7 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>0.8</v>
+        <v>1.5</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -1806,7 +1816,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 12077-2022</t>
+          <t>A 37076-2025</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1820,10 +1830,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>44636</v>
+        <v>45875</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -1836,7 +1846,7 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>2.1</v>
+        <v>2.4</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -1879,7 +1889,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 37407-2023</t>
+          <t>A 13510-2025</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1893,10 +1903,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>45156</v>
+        <v>45736</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -1909,7 +1919,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>3.3</v>
+        <v>2.5</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -1952,7 +1962,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 37072-2025</t>
+          <t>A 42991-2025</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1966,10 +1976,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>45875</v>
+        <v>45909</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -1982,7 +1992,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>1.5</v>
+        <v>7.2</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2025,7 +2035,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 37076-2025</t>
+          <t>A 43448-2025</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2039,10 +2049,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>45875</v>
+        <v>45911</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2055,7 +2065,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>2.4</v>
+        <v>1.2</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2098,7 +2108,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 13510-2025</t>
+          <t>A 44192-2025</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2112,10 +2122,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>45736</v>
+        <v>45915</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2128,7 +2138,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>2.5</v>
+        <v>0.8</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2171,7 +2181,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 58109-2025</t>
+          <t>A 21972-2023</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2185,10 +2195,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>45982</v>
+        <v>45068</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2201,7 +2211,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>2.5</v>
+        <v>1.5</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2244,7 +2254,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 58111-2025</t>
+          <t>A 21049-2026</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2258,10 +2268,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45982</v>
+        <v>46146</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2274,7 +2284,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>0.6</v>
+        <v>2.9</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2317,7 +2327,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 58125-2025</t>
+          <t>A 54207-2025</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2331,10 +2341,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>45982</v>
+        <v>45964</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2347,7 +2357,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>0.8</v>
+        <v>2.1</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2390,7 +2400,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 10069-2026</t>
+          <t>A 35036-2024</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2404,10 +2414,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>46073</v>
+        <v>45527</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2419,13 +2429,8 @@
           <t>HALLSTAHAMMAR</t>
         </is>
       </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I26" t="n">
-        <v>13</v>
+        <v>1.7</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2468,7 +2473,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 15224-2026</t>
+          <t>A 62831-2023</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2482,10 +2487,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>46105</v>
+        <v>45270</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2497,13 +2502,8 @@
           <t>HALLSTAHAMMAR</t>
         </is>
       </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I27" t="n">
-        <v>1.5</v>
+        <v>1.1</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -2546,7 +2546,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 14149-2022</t>
+          <t>A 8848-2025</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2560,10 +2560,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>44651</v>
+        <v>45713</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2575,13 +2575,8 @@
           <t>HALLSTAHAMMAR</t>
         </is>
       </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I28" t="n">
-        <v>3.8</v>
+        <v>2</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -2624,7 +2619,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 15230-2026</t>
+          <t>A 30766-2022</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2638,10 +2633,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>46105</v>
+        <v>44764</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2653,13 +2648,8 @@
           <t>HALLSTAHAMMAR</t>
         </is>
       </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I29" t="n">
-        <v>1.5</v>
+        <v>0.6</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -2702,7 +2692,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 53343-2024</t>
+          <t>A 58125-2025</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2716,10 +2706,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>45614</v>
+        <v>45982</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -2732,7 +2722,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -2775,7 +2765,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 8848-2025</t>
+          <t>A 58109-2025</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2789,10 +2779,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45713</v>
+        <v>45982</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -2805,7 +2795,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -2848,7 +2838,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 8436-2023</t>
+          <t>A 58111-2025</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2862,10 +2852,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>44977</v>
+        <v>45982</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -2877,13 +2867,8 @@
           <t>HALLSTAHAMMAR</t>
         </is>
       </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I32" t="n">
-        <v>4</v>
+        <v>0.6</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -2926,7 +2911,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 7245-2025</t>
+          <t>A 26059-2026</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2940,10 +2925,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>45702</v>
+        <v>46181</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -2956,7 +2941,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>4</v>
+        <v>4.7</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -2999,7 +2984,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 34984-2024</t>
+          <t>A 26060-2026</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3013,10 +2998,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>45527</v>
+        <v>46181</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3029,7 +3014,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>4.1</v>
+        <v>3.6</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3072,7 +3057,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 21049-2026</t>
+          <t>A 7245-2025</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3086,10 +3071,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>46146</v>
+        <v>45702</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3102,7 +3087,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>2.9</v>
+        <v>4</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3145,7 +3130,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 54207-2025</t>
+          <t>A 35238-2026</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3155,14 +3140,14 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45964</v>
+        <v>46260</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3175,7 +3160,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>2.1</v>
+        <v>3.3</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3218,7 +3203,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 16762-2022</t>
+          <t>A 8436-2023</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3232,10 +3217,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>44673</v>
+        <v>44977</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3247,8 +3232,13 @@
           <t>HALLSTAHAMMAR</t>
         </is>
       </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I37" t="n">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3291,7 +3281,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 22072-2023</t>
+          <t>A 1621-2026</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3305,10 +3295,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45069</v>
+        <v>46034</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3321,7 +3311,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>3.5</v>
+        <v>1.4</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3364,7 +3354,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 30766-2022</t>
+          <t>A 37109-2026</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3378,10 +3368,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>44764</v>
+        <v>46274</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3394,7 +3384,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>0.6</v>
+        <v>3</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3437,7 +3427,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 35036-2024</t>
+          <t>A 1622-2026</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3451,10 +3441,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45527</v>
+        <v>46034</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3467,7 +3457,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>1.7</v>
+        <v>1.4</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -3510,7 +3500,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 26059-2026</t>
+          <t>A 21264-2022</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3524,10 +3514,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>46181</v>
+        <v>44705</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3539,8 +3529,13 @@
           <t>HALLSTAHAMMAR</t>
         </is>
       </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I41" t="n">
-        <v>4.7</v>
+        <v>2.4</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -3583,7 +3578,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 26060-2026</t>
+          <t>A 12077-2022</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3597,10 +3592,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>46181</v>
+        <v>44636</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3613,7 +3608,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>3.6</v>
+        <v>2.1</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -3656,7 +3651,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 35238-2026</t>
+          <t>A 37407-2023</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3666,14 +3661,14 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>46260</v>
+        <v>45156</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -3729,7 +3724,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 37109-2026</t>
+          <t>A 14149-2022</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3743,10 +3738,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>46274</v>
+        <v>44651</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -3758,8 +3753,13 @@
           <t>HALLSTAHAMMAR</t>
         </is>
       </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I44" t="n">
-        <v>3</v>
+        <v>3.8</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -3802,7 +3802,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 62831-2023</t>
+          <t>A 53343-2024</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3816,10 +3816,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45270</v>
+        <v>45614</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -3832,7 +3832,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>1.1</v>
+        <v>0.9</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -3892,7 +3892,7 @@
         <v>46091</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -3965,7 +3965,7 @@
         <v>46111</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>

--- a/Översikt HALLSTAHAMMAR.xlsx
+++ b/Översikt HALLSTAHAMMAR.xlsx
@@ -601,7 +601,7 @@
         <v>45978</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -713,7 +713,7 @@
         <v>44635</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -791,7 +791,7 @@
         <v>44887</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -864,7 +864,7 @@
         <v>44502</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -937,7 +937,7 @@
         <v>44502</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1010,7 +1010,7 @@
         <v>44739</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1083,7 +1083,7 @@
         <v>44502</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1139,7 +1139,7 @@
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 10263-2024</t>
+          <t>A 21972-2023</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1153,10 +1153,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>45365</v>
+        <v>45068</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1168,13 +1168,8 @@
           <t>HALLSTAHAMMAR</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I9" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -1217,7 +1212,7 @@
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 34984-2024</t>
+          <t>A 21264-2022</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1231,10 +1226,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>45527</v>
+        <v>44705</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1246,8 +1241,13 @@
           <t>HALLSTAHAMMAR</t>
         </is>
       </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I10" t="n">
-        <v>4.1</v>
+        <v>2.4</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
@@ -1290,7 +1290,7 @@
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 22072-2023</t>
+          <t>A 10263-2024</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1304,10 +1304,10 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>45069</v>
+        <v>45365</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1319,8 +1319,13 @@
           <t>HALLSTAHAMMAR</t>
         </is>
       </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I11" t="n">
-        <v>3.5</v>
+        <v>1.4</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -1380,7 +1385,7 @@
         <v>44888</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1436,7 +1441,7 @@
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 10069-2026</t>
+          <t>A 12077-2022</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1450,10 +1455,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>46073</v>
+        <v>44636</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1465,13 +1470,8 @@
           <t>HALLSTAHAMMAR</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I13" t="n">
-        <v>13</v>
+        <v>2.1</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
@@ -1514,7 +1514,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 16762-2022</t>
+          <t>A 37407-2023</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1528,10 +1528,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>44673</v>
+        <v>45156</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1544,7 +1544,7 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>4.2</v>
+        <v>3.3</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -1587,7 +1587,7 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 15224-2026</t>
+          <t>A 42991-2025</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1601,10 +1601,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>46105</v>
+        <v>45909</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1616,13 +1616,8 @@
           <t>HALLSTAHAMMAR</t>
         </is>
       </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I15" t="n">
-        <v>1.5</v>
+        <v>7.2</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -1665,7 +1660,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 15230-2026</t>
+          <t>A 43448-2025</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1679,10 +1674,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>46105</v>
+        <v>45911</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1694,13 +1689,8 @@
           <t>HALLSTAHAMMAR</t>
         </is>
       </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I16" t="n">
-        <v>1.5</v>
+        <v>1.2</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -1743,7 +1733,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 37072-2025</t>
+          <t>A 44192-2025</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1757,10 +1747,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>45875</v>
+        <v>45915</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1773,7 +1763,7 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>1.5</v>
+        <v>0.8</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -1816,7 +1806,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 37076-2025</t>
+          <t>A 14149-2022</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1830,10 +1820,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>45875</v>
+        <v>44651</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -1845,8 +1835,13 @@
           <t>HALLSTAHAMMAR</t>
         </is>
       </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I18" t="n">
-        <v>2.4</v>
+        <v>3.8</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -1889,7 +1884,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 13510-2025</t>
+          <t>A 21049-2026</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1903,10 +1898,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>45736</v>
+        <v>46146</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -1919,7 +1914,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>2.5</v>
+        <v>2.9</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -1962,7 +1957,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 42991-2025</t>
+          <t>A 53343-2024</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1976,10 +1971,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>45909</v>
+        <v>45614</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -1992,7 +1987,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>7.2</v>
+        <v>0.9</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2035,7 +2030,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 43448-2025</t>
+          <t>A 8848-2025</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2049,10 +2044,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>45911</v>
+        <v>45713</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2065,7 +2060,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>1.2</v>
+        <v>2</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2108,7 +2103,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 44192-2025</t>
+          <t>A 8436-2023</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2122,10 +2117,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>45915</v>
+        <v>44977</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2137,8 +2132,13 @@
           <t>HALLSTAHAMMAR</t>
         </is>
       </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I22" t="n">
-        <v>0.8</v>
+        <v>4</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2181,7 +2181,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 21972-2023</t>
+          <t>A 7245-2025</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2195,10 +2195,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>45068</v>
+        <v>45702</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2211,7 +2211,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>1.5</v>
+        <v>4</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2254,7 +2254,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 21049-2026</t>
+          <t>A 58109-2025</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2268,10 +2268,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>46146</v>
+        <v>45982</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2284,7 +2284,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>2.9</v>
+        <v>2.5</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2327,7 +2327,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 54207-2025</t>
+          <t>A 58111-2025</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2341,10 +2341,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>45964</v>
+        <v>45982</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2357,7 +2357,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>2.1</v>
+        <v>0.6</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2400,7 +2400,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 35036-2024</t>
+          <t>A 58125-2025</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2414,10 +2414,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>45527</v>
+        <v>45982</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2430,7 +2430,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>1.7</v>
+        <v>0.8</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2473,7 +2473,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 62831-2023</t>
+          <t>A 54207-2025</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2487,10 +2487,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>45270</v>
+        <v>45964</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2503,7 +2503,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>1.1</v>
+        <v>2.1</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -2546,7 +2546,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 8848-2025</t>
+          <t>A 34984-2024</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2560,10 +2560,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>45713</v>
+        <v>45527</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2576,7 +2576,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>2</v>
+        <v>4.1</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -2619,7 +2619,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 30766-2022</t>
+          <t>A 1622-2026</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2633,10 +2633,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>44764</v>
+        <v>46034</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2649,7 +2649,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>0.6</v>
+        <v>1.4</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -2692,7 +2692,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 58125-2025</t>
+          <t>A 1621-2026</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2706,10 +2706,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>45982</v>
+        <v>46034</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -2722,7 +2722,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>0.8</v>
+        <v>1.4</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -2765,7 +2765,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 58109-2025</t>
+          <t>A 16762-2022</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2779,10 +2779,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45982</v>
+        <v>44673</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -2795,7 +2795,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>2.5</v>
+        <v>4.2</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -2838,7 +2838,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 58111-2025</t>
+          <t>A 22072-2023</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2852,10 +2852,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>45982</v>
+        <v>45069</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -2868,7 +2868,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>0.6</v>
+        <v>3.5</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -2911,7 +2911,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 26059-2026</t>
+          <t>A 30766-2022</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2925,10 +2925,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>46181</v>
+        <v>44764</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -2941,7 +2941,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>4.7</v>
+        <v>0.6</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -2984,7 +2984,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 26060-2026</t>
+          <t>A 10069-2026</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2998,10 +2998,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>46181</v>
+        <v>46073</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3013,8 +3013,13 @@
           <t>HALLSTAHAMMAR</t>
         </is>
       </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I34" t="n">
-        <v>3.6</v>
+        <v>13</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3057,7 +3062,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 7245-2025</t>
+          <t>A 35036-2024</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3071,10 +3076,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>45702</v>
+        <v>45527</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3087,7 +3092,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>4</v>
+        <v>1.7</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3130,7 +3135,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 35238-2026</t>
+          <t>A 15224-2026</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3140,14 +3145,14 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>46260</v>
+        <v>46105</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3159,8 +3164,13 @@
           <t>HALLSTAHAMMAR</t>
         </is>
       </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I36" t="n">
-        <v>3.3</v>
+        <v>1.5</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3203,7 +3213,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 8436-2023</t>
+          <t>A 15230-2026</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3217,10 +3227,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>44977</v>
+        <v>46105</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3234,11 +3244,11 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Kyrkan</t>
+          <t>Allmännings- och besparingsskogar</t>
         </is>
       </c>
       <c r="I37" t="n">
-        <v>4</v>
+        <v>1.5</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3281,7 +3291,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 1621-2026</t>
+          <t>A 26059-2026</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3295,10 +3305,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>46034</v>
+        <v>46181</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3311,7 +3321,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>1.4</v>
+        <v>4.7</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3354,7 +3364,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 37109-2026</t>
+          <t>A 26060-2026</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3368,10 +3378,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>46274</v>
+        <v>46181</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3384,7 +3394,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>3</v>
+        <v>3.6</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3427,7 +3437,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 1622-2026</t>
+          <t>A 62831-2023</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3441,10 +3451,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>46034</v>
+        <v>45270</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3457,7 +3467,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>1.4</v>
+        <v>1.1</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -3500,7 +3510,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 21264-2022</t>
+          <t>A 35238-2026</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3510,14 +3520,14 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>44705</v>
+        <v>46260</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3529,13 +3539,8 @@
           <t>HALLSTAHAMMAR</t>
         </is>
       </c>
-      <c r="H41" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I41" t="n">
-        <v>2.4</v>
+        <v>3.3</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -3578,7 +3583,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 12077-2022</t>
+          <t>A 37109-2026</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3592,10 +3597,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>44636</v>
+        <v>46274</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3608,7 +3613,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>2.1</v>
+        <v>3</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -3651,7 +3656,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 37407-2023</t>
+          <t>A 37072-2025</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3665,10 +3670,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45156</v>
+        <v>45875</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -3681,7 +3686,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>3.3</v>
+        <v>1.5</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -3724,7 +3729,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 14149-2022</t>
+          <t>A 37076-2025</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3738,10 +3743,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>44651</v>
+        <v>45875</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -3753,13 +3758,8 @@
           <t>HALLSTAHAMMAR</t>
         </is>
       </c>
-      <c r="H44" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I44" t="n">
-        <v>3.8</v>
+        <v>2.4</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -3802,7 +3802,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 53343-2024</t>
+          <t>A 13510-2025</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3816,10 +3816,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45614</v>
+        <v>45736</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -3832,7 +3832,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>0.9</v>
+        <v>2.5</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -3892,7 +3892,7 @@
         <v>46091</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -3965,7 +3965,7 @@
         <v>46111</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46283</v>
+        <v>46284</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>

--- a/Översikt HALLSTAHAMMAR.xlsx
+++ b/Översikt HALLSTAHAMMAR.xlsx
@@ -601,7 +601,7 @@
         <v>45978</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -713,7 +713,7 @@
         <v>44635</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -791,7 +791,7 @@
         <v>44887</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -864,7 +864,7 @@
         <v>44502</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -937,7 +937,7 @@
         <v>44502</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1010,7 +1010,7 @@
         <v>44739</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1083,7 +1083,7 @@
         <v>44502</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1156,7 +1156,7 @@
         <v>45068</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1229,7 +1229,7 @@
         <v>44705</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1307,7 +1307,7 @@
         <v>45365</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1385,7 +1385,7 @@
         <v>44888</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1458,7 +1458,7 @@
         <v>44636</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1531,7 +1531,7 @@
         <v>45156</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1604,7 +1604,7 @@
         <v>45909</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1677,7 +1677,7 @@
         <v>45911</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1750,7 +1750,7 @@
         <v>45915</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1823,7 +1823,7 @@
         <v>44651</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -1901,7 +1901,7 @@
         <v>46146</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -1974,7 +1974,7 @@
         <v>45614</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2047,7 +2047,7 @@
         <v>45713</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2120,7 +2120,7 @@
         <v>44977</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2198,7 +2198,7 @@
         <v>45702</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2271,7 +2271,7 @@
         <v>45982</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2344,7 +2344,7 @@
         <v>45982</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2417,7 +2417,7 @@
         <v>45982</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2490,7 +2490,7 @@
         <v>45964</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2563,7 +2563,7 @@
         <v>45527</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2636,7 +2636,7 @@
         <v>46034</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2709,7 +2709,7 @@
         <v>46034</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -2782,7 +2782,7 @@
         <v>44673</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -2855,7 +2855,7 @@
         <v>45069</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -2928,7 +2928,7 @@
         <v>44764</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3001,7 +3001,7 @@
         <v>46073</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3079,7 +3079,7 @@
         <v>45527</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3152,7 +3152,7 @@
         <v>46105</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3230,7 +3230,7 @@
         <v>46105</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3308,7 +3308,7 @@
         <v>46181</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3381,7 +3381,7 @@
         <v>46181</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3454,7 +3454,7 @@
         <v>45270</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3527,7 +3527,7 @@
         <v>46260</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3600,7 +3600,7 @@
         <v>46274</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3673,7 +3673,7 @@
         <v>45875</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -3746,7 +3746,7 @@
         <v>45875</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -3819,7 +3819,7 @@
         <v>45736</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -3892,7 +3892,7 @@
         <v>46091</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -3965,7 +3965,7 @@
         <v>46111</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>

--- a/Översikt HALLSTAHAMMAR.xlsx
+++ b/Översikt HALLSTAHAMMAR.xlsx
@@ -601,7 +601,7 @@
         <v>45978</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -713,7 +713,7 @@
         <v>44635</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -791,7 +791,7 @@
         <v>44887</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -864,7 +864,7 @@
         <v>44502</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -937,7 +937,7 @@
         <v>44502</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1010,7 +1010,7 @@
         <v>44739</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1083,7 +1083,7 @@
         <v>44502</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1139,7 +1139,7 @@
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 21972-2023</t>
+          <t>A 21264-2022</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1153,10 +1153,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>45068</v>
+        <v>44705</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1168,8 +1168,13 @@
           <t>HALLSTAHAMMAR</t>
         </is>
       </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I9" t="n">
-        <v>1.5</v>
+        <v>2.4</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -1212,7 +1217,7 @@
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 21264-2022</t>
+          <t>A 21972-2023</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1226,10 +1231,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>44705</v>
+        <v>45068</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1241,13 +1246,8 @@
           <t>HALLSTAHAMMAR</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I10" t="n">
-        <v>2.4</v>
+        <v>1.5</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
@@ -1307,7 +1307,7 @@
         <v>45365</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1385,7 +1385,7 @@
         <v>44888</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1458,7 +1458,7 @@
         <v>44636</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1531,7 +1531,7 @@
         <v>45156</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1587,7 +1587,7 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 42991-2025</t>
+          <t>A 37072-2025</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1601,10 +1601,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>45909</v>
+        <v>45875</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1617,7 +1617,7 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>7.2</v>
+        <v>1.5</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -1660,7 +1660,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 43448-2025</t>
+          <t>A 37076-2025</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1674,10 +1674,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45911</v>
+        <v>45875</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1690,7 +1690,7 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>1.2</v>
+        <v>2.4</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -1733,7 +1733,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 44192-2025</t>
+          <t>A 13510-2025</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1747,10 +1747,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>45915</v>
+        <v>45736</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1763,7 +1763,7 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>0.8</v>
+        <v>2.5</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -1806,7 +1806,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 14149-2022</t>
+          <t>A 42991-2025</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1820,10 +1820,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>44651</v>
+        <v>45909</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -1835,13 +1835,8 @@
           <t>HALLSTAHAMMAR</t>
         </is>
       </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I18" t="n">
-        <v>3.8</v>
+        <v>7.2</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -1884,7 +1879,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 21049-2026</t>
+          <t>A 43448-2025</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1898,10 +1893,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>46146</v>
+        <v>45911</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -1914,7 +1909,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>2.9</v>
+        <v>1.2</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -1957,7 +1952,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 53343-2024</t>
+          <t>A 44192-2025</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1971,10 +1966,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>45614</v>
+        <v>45915</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -1987,7 +1982,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2030,7 +2025,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 8848-2025</t>
+          <t>A 21049-2026</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2044,10 +2039,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>45713</v>
+        <v>46146</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2060,7 +2055,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>2</v>
+        <v>2.9</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2103,7 +2098,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 8436-2023</t>
+          <t>A 54207-2025</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2117,10 +2112,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>44977</v>
+        <v>45964</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2132,13 +2127,8 @@
           <t>HALLSTAHAMMAR</t>
         </is>
       </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I22" t="n">
-        <v>4</v>
+        <v>2.1</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2181,7 +2171,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 7245-2025</t>
+          <t>A 14149-2022</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2195,10 +2185,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>45702</v>
+        <v>44651</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2210,8 +2200,13 @@
           <t>HALLSTAHAMMAR</t>
         </is>
       </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I23" t="n">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2254,7 +2249,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 58109-2025</t>
+          <t>A 53343-2024</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2268,10 +2263,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45982</v>
+        <v>45614</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2284,7 +2279,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>2.5</v>
+        <v>0.9</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2327,7 +2322,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 58111-2025</t>
+          <t>A 8848-2025</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2341,10 +2336,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>45982</v>
+        <v>45713</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2357,7 +2352,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>0.6</v>
+        <v>2</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2400,7 +2395,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 58125-2025</t>
+          <t>A 58109-2025</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2417,7 +2412,7 @@
         <v>45982</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2430,7 +2425,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>0.8</v>
+        <v>2.5</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2473,7 +2468,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 54207-2025</t>
+          <t>A 58111-2025</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2487,10 +2482,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>45964</v>
+        <v>45982</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2503,7 +2498,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>2.1</v>
+        <v>0.6</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -2546,7 +2541,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 34984-2024</t>
+          <t>A 58125-2025</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2560,10 +2555,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>45527</v>
+        <v>45982</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2576,7 +2571,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>4.1</v>
+        <v>0.8</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -2619,7 +2614,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 1622-2026</t>
+          <t>A 8436-2023</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2633,10 +2628,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>46034</v>
+        <v>44977</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2648,8 +2643,13 @@
           <t>HALLSTAHAMMAR</t>
         </is>
       </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I29" t="n">
-        <v>1.4</v>
+        <v>4</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -2692,7 +2692,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 1621-2026</t>
+          <t>A 7245-2025</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2706,10 +2706,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>46034</v>
+        <v>45702</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -2722,7 +2722,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>1.4</v>
+        <v>4</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -2765,7 +2765,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 16762-2022</t>
+          <t>A 1622-2026</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2779,10 +2779,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>44673</v>
+        <v>46034</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -2795,7 +2795,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>4.2</v>
+        <v>1.4</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -2838,7 +2838,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 22072-2023</t>
+          <t>A 1621-2026</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2852,10 +2852,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>45069</v>
+        <v>46034</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -2868,7 +2868,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>3.5</v>
+        <v>1.4</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -2911,7 +2911,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 30766-2022</t>
+          <t>A 34984-2024</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2925,10 +2925,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>44764</v>
+        <v>45527</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -2941,7 +2941,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>0.6</v>
+        <v>4.1</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3001,7 +3001,7 @@
         <v>46073</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3062,7 +3062,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 35036-2024</t>
+          <t>A 16762-2022</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3076,10 +3076,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>45527</v>
+        <v>44673</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3092,7 +3092,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>1.7</v>
+        <v>4.2</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3152,7 +3152,7 @@
         <v>46105</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3230,7 +3230,7 @@
         <v>46105</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3308,7 +3308,7 @@
         <v>46181</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3381,7 +3381,7 @@
         <v>46181</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3437,7 +3437,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 62831-2023</t>
+          <t>A 22072-2023</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3451,10 +3451,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45270</v>
+        <v>45069</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3467,7 +3467,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>1.1</v>
+        <v>3.5</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -3510,7 +3510,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 35238-2026</t>
+          <t>A 30766-2022</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3520,14 +3520,14 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>46260</v>
+        <v>44764</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3540,7 +3540,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>3.3</v>
+        <v>0.6</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -3583,7 +3583,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 37109-2026</t>
+          <t>A 35036-2024</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3597,10 +3597,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>46274</v>
+        <v>45527</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3613,7 +3613,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>3</v>
+        <v>1.7</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -3656,7 +3656,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 37072-2025</t>
+          <t>A 35238-2026</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3666,14 +3666,14 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45875</v>
+        <v>46260</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -3686,7 +3686,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>1.5</v>
+        <v>3.3</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -3729,7 +3729,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 37076-2025</t>
+          <t>A 37109-2026</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3743,10 +3743,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45875</v>
+        <v>46274</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -3759,7 +3759,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>2.4</v>
+        <v>3</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -3802,7 +3802,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 13510-2025</t>
+          <t>A 62831-2023</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3816,10 +3816,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45736</v>
+        <v>45270</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -3832,7 +3832,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>2.5</v>
+        <v>1.1</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -3892,7 +3892,7 @@
         <v>46091</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -3965,7 +3965,7 @@
         <v>46111</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>

--- a/Översikt HALLSTAHAMMAR.xlsx
+++ b/Översikt HALLSTAHAMMAR.xlsx
@@ -601,7 +601,7 @@
         <v>45978</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -713,7 +713,7 @@
         <v>44635</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -791,7 +791,7 @@
         <v>44887</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -864,7 +864,7 @@
         <v>44502</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -937,7 +937,7 @@
         <v>44502</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1010,7 +1010,7 @@
         <v>44739</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1083,7 +1083,7 @@
         <v>44502</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1139,7 +1139,7 @@
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 21264-2022</t>
+          <t>A 10263-2024</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1153,10 +1153,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>44705</v>
+        <v>45365</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1170,11 +1170,11 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Allmännings- och besparingsskogar</t>
+          <t>Kyrkan</t>
         </is>
       </c>
       <c r="I9" t="n">
-        <v>2.4</v>
+        <v>1.4</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -1234,7 +1234,7 @@
         <v>45068</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1290,7 +1290,7 @@
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 10263-2024</t>
+          <t>A 34984-2024</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1304,10 +1304,10 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>45365</v>
+        <v>45527</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1319,13 +1319,8 @@
           <t>HALLSTAHAMMAR</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I11" t="n">
-        <v>1.4</v>
+        <v>4.1</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -1368,7 +1363,7 @@
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 55562-2022</t>
+          <t>A 35036-2024</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1382,10 +1377,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>44888</v>
+        <v>45527</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1398,7 +1393,7 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>0.8</v>
+        <v>1.7</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -1441,7 +1436,7 @@
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 12077-2022</t>
+          <t>A 62831-2023</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1455,10 +1450,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>44636</v>
+        <v>45270</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1471,7 +1466,7 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>2.1</v>
+        <v>1.1</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
@@ -1514,7 +1509,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 37407-2023</t>
+          <t>A 42991-2025</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1528,10 +1523,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>45156</v>
+        <v>45909</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1544,7 +1539,7 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>3.3</v>
+        <v>7.2</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -1587,7 +1582,7 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 37072-2025</t>
+          <t>A 43448-2025</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1601,10 +1596,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>45875</v>
+        <v>45911</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1617,7 +1612,7 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>1.5</v>
+        <v>1.2</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -1660,7 +1655,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 37076-2025</t>
+          <t>A 44192-2025</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1674,10 +1669,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45875</v>
+        <v>45915</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1690,7 +1685,7 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>2.4</v>
+        <v>0.8</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -1733,7 +1728,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 13510-2025</t>
+          <t>A 22072-2023</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1747,10 +1742,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>45736</v>
+        <v>45069</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1763,7 +1758,7 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>2.5</v>
+        <v>3.5</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -1806,7 +1801,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 42991-2025</t>
+          <t>A 8848-2025</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1820,10 +1815,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>45909</v>
+        <v>45713</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -1836,7 +1831,7 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>7.2</v>
+        <v>2</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -1879,7 +1874,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 43448-2025</t>
+          <t>A 55562-2022</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1893,10 +1888,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>45911</v>
+        <v>44888</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -1909,7 +1904,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>1.2</v>
+        <v>0.8</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -1952,7 +1947,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 44192-2025</t>
+          <t>A 30766-2022</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1966,10 +1961,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>45915</v>
+        <v>44764</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -1982,7 +1977,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2025,7 +2020,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 21049-2026</t>
+          <t>A 16762-2022</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2039,10 +2034,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>46146</v>
+        <v>44673</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2055,7 +2050,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>2.9</v>
+        <v>4.2</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2098,7 +2093,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 54207-2025</t>
+          <t>A 58125-2025</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2112,10 +2107,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>45964</v>
+        <v>45982</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2128,7 +2123,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>2.1</v>
+        <v>0.8</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2171,7 +2166,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 14149-2022</t>
+          <t>A 58109-2025</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2185,10 +2180,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>44651</v>
+        <v>45982</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2200,13 +2195,8 @@
           <t>HALLSTAHAMMAR</t>
         </is>
       </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I23" t="n">
-        <v>3.8</v>
+        <v>2.5</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2249,7 +2239,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 53343-2024</t>
+          <t>A 58111-2025</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2263,10 +2253,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45614</v>
+        <v>45982</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2279,7 +2269,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>0.9</v>
+        <v>0.6</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2322,7 +2312,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 8848-2025</t>
+          <t>A 7245-2025</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2336,10 +2326,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>45713</v>
+        <v>45702</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2352,7 +2342,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2395,7 +2385,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 58109-2025</t>
+          <t>A 1621-2026</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2409,10 +2399,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>45982</v>
+        <v>46034</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2425,7 +2415,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>2.5</v>
+        <v>1.4</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2468,7 +2458,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 58111-2025</t>
+          <t>A 1622-2026</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2482,10 +2472,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>45982</v>
+        <v>46034</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2498,7 +2488,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>0.6</v>
+        <v>1.4</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -2541,7 +2531,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 58125-2025</t>
+          <t>A 10069-2026</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2555,10 +2545,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>45982</v>
+        <v>46073</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2570,8 +2560,13 @@
           <t>HALLSTAHAMMAR</t>
         </is>
       </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I28" t="n">
-        <v>0.8</v>
+        <v>13</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -2631,7 +2626,7 @@
         <v>44977</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2692,7 +2687,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 7245-2025</t>
+          <t>A 15224-2026</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2706,10 +2701,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>45702</v>
+        <v>46105</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -2721,8 +2716,13 @@
           <t>HALLSTAHAMMAR</t>
         </is>
       </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I30" t="n">
-        <v>4</v>
+        <v>1.5</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -2765,7 +2765,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 1622-2026</t>
+          <t>A 15230-2026</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2779,10 +2779,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>46034</v>
+        <v>46105</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -2794,8 +2794,13 @@
           <t>HALLSTAHAMMAR</t>
         </is>
       </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I31" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -2838,7 +2843,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 1621-2026</t>
+          <t>A 21264-2022</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2852,10 +2857,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>46034</v>
+        <v>44705</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -2867,8 +2872,13 @@
           <t>HALLSTAHAMMAR</t>
         </is>
       </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I32" t="n">
-        <v>1.4</v>
+        <v>2.4</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -2911,7 +2921,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 34984-2024</t>
+          <t>A 12077-2022</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2925,10 +2935,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>45527</v>
+        <v>44636</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -2941,7 +2951,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>4.1</v>
+        <v>2.1</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -2984,7 +2994,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 10069-2026</t>
+          <t>A 37407-2023</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2998,10 +3008,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>46073</v>
+        <v>45156</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3013,13 +3023,8 @@
           <t>HALLSTAHAMMAR</t>
         </is>
       </c>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I34" t="n">
-        <v>13</v>
+        <v>3.3</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3062,7 +3067,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 16762-2022</t>
+          <t>A 37072-2025</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3076,10 +3081,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>44673</v>
+        <v>45875</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3092,7 +3097,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>4.2</v>
+        <v>1.5</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3135,7 +3140,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 15224-2026</t>
+          <t>A 37076-2025</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3149,10 +3154,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>46105</v>
+        <v>45875</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3164,13 +3169,8 @@
           <t>HALLSTAHAMMAR</t>
         </is>
       </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I36" t="n">
-        <v>1.5</v>
+        <v>2.4</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3213,7 +3213,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 15230-2026</t>
+          <t>A 13510-2025</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3227,10 +3227,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>46105</v>
+        <v>45736</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3242,13 +3242,8 @@
           <t>HALLSTAHAMMAR</t>
         </is>
       </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I37" t="n">
-        <v>1.5</v>
+        <v>2.5</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3291,7 +3286,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 26059-2026</t>
+          <t>A 14149-2022</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3305,10 +3300,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>46181</v>
+        <v>44651</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3320,8 +3315,13 @@
           <t>HALLSTAHAMMAR</t>
         </is>
       </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I38" t="n">
-        <v>4.7</v>
+        <v>3.8</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3364,7 +3364,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 26060-2026</t>
+          <t>A 53343-2024</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3378,10 +3378,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>46181</v>
+        <v>45614</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3394,7 +3394,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>3.6</v>
+        <v>0.9</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3437,7 +3437,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 22072-2023</t>
+          <t>A 21049-2026</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3451,10 +3451,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45069</v>
+        <v>46146</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3467,7 +3467,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>3.5</v>
+        <v>2.9</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -3510,7 +3510,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 30766-2022</t>
+          <t>A 54207-2025</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3524,10 +3524,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>44764</v>
+        <v>45964</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3540,7 +3540,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>0.6</v>
+        <v>2.1</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -3583,7 +3583,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 35036-2024</t>
+          <t>A 26059-2026</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3597,10 +3597,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>45527</v>
+        <v>46181</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3613,7 +3613,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>1.7</v>
+        <v>4.7</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -3656,7 +3656,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 35238-2026</t>
+          <t>A 26060-2026</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3666,14 +3666,14 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>46260</v>
+        <v>46181</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -3686,7 +3686,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>3.3</v>
+        <v>3.6</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -3729,7 +3729,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 37109-2026</t>
+          <t>A 35238-2026</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3739,14 +3739,14 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>46274</v>
+        <v>46260</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -3759,7 +3759,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>3</v>
+        <v>3.3</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -3802,7 +3802,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 62831-2023</t>
+          <t>A 37109-2026</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3816,10 +3816,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45270</v>
+        <v>46274</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -3832,7 +3832,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>1.1</v>
+        <v>3</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -3892,7 +3892,7 @@
         <v>46091</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -3965,7 +3965,7 @@
         <v>46111</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>

--- a/Översikt HALLSTAHAMMAR.xlsx
+++ b/Översikt HALLSTAHAMMAR.xlsx
@@ -601,7 +601,7 @@
         <v>45978</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -713,7 +713,7 @@
         <v>44635</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -791,7 +791,7 @@
         <v>44887</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -864,7 +864,7 @@
         <v>44502</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -937,7 +937,7 @@
         <v>44502</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1010,7 +1010,7 @@
         <v>44739</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1083,7 +1083,7 @@
         <v>44502</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1139,7 +1139,7 @@
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 10263-2024</t>
+          <t>A 21264-2022</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1153,10 +1153,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>45365</v>
+        <v>44705</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1170,11 +1170,11 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Kyrkan</t>
+          <t>Allmännings- och besparingsskogar</t>
         </is>
       </c>
       <c r="I9" t="n">
-        <v>1.4</v>
+        <v>2.4</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -1234,7 +1234,7 @@
         <v>45068</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1290,7 +1290,7 @@
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 34984-2024</t>
+          <t>A 10263-2024</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1304,10 +1304,10 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>45527</v>
+        <v>45365</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1319,8 +1319,13 @@
           <t>HALLSTAHAMMAR</t>
         </is>
       </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I11" t="n">
-        <v>4.1</v>
+        <v>1.4</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -1363,7 +1368,7 @@
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 35036-2024</t>
+          <t>A 55562-2022</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1377,10 +1382,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>45527</v>
+        <v>44888</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1393,7 +1398,7 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>1.7</v>
+        <v>0.8</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -1436,7 +1441,7 @@
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 62831-2023</t>
+          <t>A 37407-2023</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1450,10 +1455,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>45270</v>
+        <v>45156</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1466,7 +1471,7 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>1.1</v>
+        <v>3.3</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
@@ -1509,7 +1514,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 42991-2025</t>
+          <t>A 12077-2022</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1523,10 +1528,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>45909</v>
+        <v>44636</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1539,7 +1544,7 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>7.2</v>
+        <v>2.1</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -1582,7 +1587,7 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 43448-2025</t>
+          <t>A 37072-2025</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1596,10 +1601,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>45911</v>
+        <v>45875</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1612,7 +1617,7 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>1.2</v>
+        <v>1.5</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -1655,7 +1660,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 44192-2025</t>
+          <t>A 37076-2025</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1669,10 +1674,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45915</v>
+        <v>45875</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1685,7 +1690,7 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>0.8</v>
+        <v>2.4</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -1728,7 +1733,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 22072-2023</t>
+          <t>A 13510-2025</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1742,10 +1747,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>45069</v>
+        <v>45736</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1758,7 +1763,7 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>3.5</v>
+        <v>2.5</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -1801,7 +1806,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 8848-2025</t>
+          <t>A 42991-2025</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1815,10 +1820,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>45713</v>
+        <v>45909</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -1831,7 +1836,7 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>2</v>
+        <v>7.2</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -1874,7 +1879,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 55562-2022</t>
+          <t>A 43448-2025</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1888,10 +1893,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>44888</v>
+        <v>45911</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -1904,7 +1909,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>0.8</v>
+        <v>1.2</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -1947,7 +1952,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 30766-2022</t>
+          <t>A 44192-2025</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1961,10 +1966,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>44764</v>
+        <v>45915</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -1977,7 +1982,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2020,7 +2025,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 16762-2022</t>
+          <t>A 14149-2022</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2034,10 +2039,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>44673</v>
+        <v>44651</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2049,8 +2054,13 @@
           <t>HALLSTAHAMMAR</t>
         </is>
       </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I21" t="n">
-        <v>4.2</v>
+        <v>3.8</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2093,7 +2103,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 58125-2025</t>
+          <t>A 53343-2024</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2107,10 +2117,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>45982</v>
+        <v>45614</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2123,7 +2133,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2166,7 +2176,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 58109-2025</t>
+          <t>A 8848-2025</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2180,10 +2190,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>45982</v>
+        <v>45713</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2196,7 +2206,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2239,7 +2249,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 58111-2025</t>
+          <t>A 58109-2025</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2256,7 +2266,7 @@
         <v>45982</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2269,7 +2279,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>0.6</v>
+        <v>2.5</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2312,7 +2322,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 7245-2025</t>
+          <t>A 58111-2025</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2326,10 +2336,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>45702</v>
+        <v>45982</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2342,7 +2352,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>4</v>
+        <v>0.6</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2385,7 +2395,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 1621-2026</t>
+          <t>A 58125-2025</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2399,10 +2409,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>46034</v>
+        <v>45982</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2415,7 +2425,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>1.4</v>
+        <v>0.8</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2458,7 +2468,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 1622-2026</t>
+          <t>A 21049-2026</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2472,10 +2482,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>46034</v>
+        <v>46146</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2488,7 +2498,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>1.4</v>
+        <v>2.9</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -2531,7 +2541,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 10069-2026</t>
+          <t>A 8436-2023</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2545,10 +2555,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>46073</v>
+        <v>44977</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2562,11 +2572,11 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Allmännings- och besparingsskogar</t>
+          <t>Kyrkan</t>
         </is>
       </c>
       <c r="I28" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -2609,7 +2619,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 8436-2023</t>
+          <t>A 54207-2025</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2623,10 +2633,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>44977</v>
+        <v>45964</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2638,13 +2648,8 @@
           <t>HALLSTAHAMMAR</t>
         </is>
       </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I29" t="n">
-        <v>4</v>
+        <v>2.1</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -2687,7 +2692,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 15224-2026</t>
+          <t>A 7245-2025</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2701,10 +2706,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>46105</v>
+        <v>45702</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -2716,13 +2721,8 @@
           <t>HALLSTAHAMMAR</t>
         </is>
       </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I30" t="n">
-        <v>1.5</v>
+        <v>4</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -2765,7 +2765,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 15230-2026</t>
+          <t>A 1622-2026</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2779,10 +2779,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>46105</v>
+        <v>46034</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -2794,13 +2794,8 @@
           <t>HALLSTAHAMMAR</t>
         </is>
       </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I31" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -2843,7 +2838,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 21264-2022</t>
+          <t>A 1621-2026</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2857,10 +2852,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>44705</v>
+        <v>46034</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -2872,13 +2867,8 @@
           <t>HALLSTAHAMMAR</t>
         </is>
       </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I32" t="n">
-        <v>2.4</v>
+        <v>1.4</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -2921,7 +2911,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 12077-2022</t>
+          <t>A 34984-2024</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2935,10 +2925,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>44636</v>
+        <v>45527</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -2951,7 +2941,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>2.1</v>
+        <v>4.1</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -2994,7 +2984,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 37407-2023</t>
+          <t>A 10069-2026</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3008,10 +2998,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>45156</v>
+        <v>46073</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3023,8 +3013,13 @@
           <t>HALLSTAHAMMAR</t>
         </is>
       </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I34" t="n">
-        <v>3.3</v>
+        <v>13</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3067,7 +3062,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 37072-2025</t>
+          <t>A 16762-2022</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3081,10 +3076,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>45875</v>
+        <v>44673</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3097,7 +3092,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>1.5</v>
+        <v>4.2</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3140,7 +3135,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 37076-2025</t>
+          <t>A 15224-2026</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3154,10 +3149,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45875</v>
+        <v>46105</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3169,8 +3164,13 @@
           <t>HALLSTAHAMMAR</t>
         </is>
       </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I36" t="n">
-        <v>2.4</v>
+        <v>1.5</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3213,7 +3213,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 13510-2025</t>
+          <t>A 15230-2026</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3227,10 +3227,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45736</v>
+        <v>46105</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3242,8 +3242,13 @@
           <t>HALLSTAHAMMAR</t>
         </is>
       </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I37" t="n">
-        <v>2.5</v>
+        <v>1.5</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3286,7 +3291,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 14149-2022</t>
+          <t>A 22072-2023</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3300,10 +3305,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>44651</v>
+        <v>45069</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3315,13 +3320,8 @@
           <t>HALLSTAHAMMAR</t>
         </is>
       </c>
-      <c r="H38" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I38" t="n">
-        <v>3.8</v>
+        <v>3.5</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3364,7 +3364,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 53343-2024</t>
+          <t>A 30766-2022</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3378,10 +3378,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45614</v>
+        <v>44764</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3394,7 +3394,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>0.9</v>
+        <v>0.6</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3437,7 +3437,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 21049-2026</t>
+          <t>A 35036-2024</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3451,10 +3451,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>46146</v>
+        <v>45527</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3467,7 +3467,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>2.9</v>
+        <v>1.7</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -3510,7 +3510,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 54207-2025</t>
+          <t>A 26059-2026</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3524,10 +3524,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45964</v>
+        <v>46181</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3540,7 +3540,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>2.1</v>
+        <v>4.7</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -3583,7 +3583,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 26059-2026</t>
+          <t>A 26060-2026</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3600,7 +3600,7 @@
         <v>46181</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3613,7 +3613,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>4.7</v>
+        <v>3.6</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -3656,7 +3656,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 26060-2026</t>
+          <t>A 35238-2026</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3666,14 +3666,14 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>46181</v>
+        <v>46260</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -3686,7 +3686,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>3.6</v>
+        <v>3.3</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -3729,7 +3729,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 35238-2026</t>
+          <t>A 62831-2023</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3739,14 +3739,14 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>46260</v>
+        <v>45270</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -3759,7 +3759,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>3.3</v>
+        <v>1.1</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -3819,7 +3819,7 @@
         <v>46274</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -3892,7 +3892,7 @@
         <v>46091</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -3965,7 +3965,7 @@
         <v>46111</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>

--- a/Översikt HALLSTAHAMMAR.xlsx
+++ b/Översikt HALLSTAHAMMAR.xlsx
@@ -601,7 +601,7 @@
         <v>45978</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -713,7 +713,7 @@
         <v>44635</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -791,7 +791,7 @@
         <v>44887</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -864,7 +864,7 @@
         <v>44502</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -937,7 +937,7 @@
         <v>44502</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1010,7 +1010,7 @@
         <v>44739</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1083,7 +1083,7 @@
         <v>44502</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1139,7 +1139,7 @@
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 21264-2022</t>
+          <t>A 10263-2024</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1153,10 +1153,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>44705</v>
+        <v>45365</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1170,11 +1170,11 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Allmännings- och besparingsskogar</t>
+          <t>Kyrkan</t>
         </is>
       </c>
       <c r="I9" t="n">
-        <v>2.4</v>
+        <v>1.4</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -1217,7 +1217,7 @@
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 21972-2023</t>
+          <t>A 34984-2024</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1231,10 +1231,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>45068</v>
+        <v>45527</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1247,7 +1247,7 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>1.5</v>
+        <v>4.1</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
@@ -1290,7 +1290,7 @@
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 10263-2024</t>
+          <t>A 1621-2026</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1304,10 +1304,10 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>45365</v>
+        <v>46034</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1317,11 +1317,6 @@
       <c r="G11" t="inlineStr">
         <is>
           <t>HALLSTAHAMMAR</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
         </is>
       </c>
       <c r="I11" t="n">
@@ -1368,7 +1363,7 @@
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 55562-2022</t>
+          <t>A 1622-2026</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1382,10 +1377,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>44888</v>
+        <v>46034</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1398,7 +1393,7 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>0.8</v>
+        <v>1.4</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -1441,7 +1436,7 @@
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 37407-2023</t>
+          <t>A 22072-2023</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1455,10 +1450,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>45156</v>
+        <v>45069</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1471,7 +1466,7 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
@@ -1514,7 +1509,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 12077-2022</t>
+          <t>A 42991-2025</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1528,10 +1523,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>44636</v>
+        <v>45909</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1544,7 +1539,7 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>2.1</v>
+        <v>7.2</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -1587,7 +1582,7 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 37072-2025</t>
+          <t>A 43448-2025</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1601,10 +1596,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>45875</v>
+        <v>45911</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1617,7 +1612,7 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>1.5</v>
+        <v>1.2</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -1660,7 +1655,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 37076-2025</t>
+          <t>A 44192-2025</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1674,10 +1669,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45875</v>
+        <v>45915</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1690,7 +1685,7 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>2.4</v>
+        <v>0.8</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -1733,7 +1728,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 13510-2025</t>
+          <t>A 55562-2022</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1747,10 +1742,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>45736</v>
+        <v>44888</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1763,7 +1758,7 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>2.5</v>
+        <v>0.8</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -1806,7 +1801,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 42991-2025</t>
+          <t>A 10069-2026</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1820,10 +1815,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>45909</v>
+        <v>46073</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -1835,8 +1830,13 @@
           <t>HALLSTAHAMMAR</t>
         </is>
       </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I18" t="n">
-        <v>7.2</v>
+        <v>13</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -1879,7 +1879,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 43448-2025</t>
+          <t>A 15224-2026</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1893,10 +1893,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>45911</v>
+        <v>46105</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -1908,8 +1908,13 @@
           <t>HALLSTAHAMMAR</t>
         </is>
       </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I19" t="n">
-        <v>1.2</v>
+        <v>1.5</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -1952,7 +1957,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 44192-2025</t>
+          <t>A 15230-2026</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1966,10 +1971,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>45915</v>
+        <v>46105</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -1981,8 +1986,13 @@
           <t>HALLSTAHAMMAR</t>
         </is>
       </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I20" t="n">
-        <v>0.8</v>
+        <v>1.5</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2025,7 +2035,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 14149-2022</t>
+          <t>A 16762-2022</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2039,10 +2049,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>44651</v>
+        <v>44673</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2054,13 +2064,8 @@
           <t>HALLSTAHAMMAR</t>
         </is>
       </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I21" t="n">
-        <v>3.8</v>
+        <v>4.2</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2103,7 +2108,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 53343-2024</t>
+          <t>A 58125-2025</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2117,10 +2122,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>45614</v>
+        <v>45982</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2133,7 +2138,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2176,7 +2181,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 8848-2025</t>
+          <t>A 58109-2025</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2190,10 +2195,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>45713</v>
+        <v>45982</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2206,7 +2211,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2249,7 +2254,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 58109-2025</t>
+          <t>A 58111-2025</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2266,7 +2271,7 @@
         <v>45982</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2279,7 +2284,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>2.5</v>
+        <v>0.6</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2322,7 +2327,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 58111-2025</t>
+          <t>A 21972-2023</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2336,10 +2341,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>45982</v>
+        <v>45068</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2352,7 +2357,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>0.6</v>
+        <v>1.5</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2395,7 +2400,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 58125-2025</t>
+          <t>A 21049-2026</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2409,10 +2414,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>45982</v>
+        <v>46146</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2425,7 +2430,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>0.8</v>
+        <v>2.9</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2468,7 +2473,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 21049-2026</t>
+          <t>A 54207-2025</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2482,10 +2487,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>46146</v>
+        <v>45964</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2498,7 +2503,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>2.9</v>
+        <v>2.1</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -2541,7 +2546,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 8436-2023</t>
+          <t>A 35036-2024</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2555,10 +2560,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>44977</v>
+        <v>45527</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2570,13 +2575,8 @@
           <t>HALLSTAHAMMAR</t>
         </is>
       </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I28" t="n">
-        <v>4</v>
+        <v>1.7</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -2619,7 +2619,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 54207-2025</t>
+          <t>A 62831-2023</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2633,10 +2633,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>45964</v>
+        <v>45270</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2649,7 +2649,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>2.1</v>
+        <v>1.1</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -2692,7 +2692,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 7245-2025</t>
+          <t>A 8848-2025</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2706,10 +2706,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>45702</v>
+        <v>45713</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -2722,7 +2722,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -2765,7 +2765,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 1622-2026</t>
+          <t>A 37072-2025</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2779,10 +2779,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>46034</v>
+        <v>45875</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -2795,7 +2795,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -2838,7 +2838,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 1621-2026</t>
+          <t>A 37076-2025</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2852,10 +2852,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>46034</v>
+        <v>45875</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -2868,7 +2868,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>1.4</v>
+        <v>2.4</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -2911,7 +2911,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 34984-2024</t>
+          <t>A 13510-2025</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2925,10 +2925,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>45527</v>
+        <v>45736</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -2941,7 +2941,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>4.1</v>
+        <v>2.5</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -2984,7 +2984,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 10069-2026</t>
+          <t>A 26059-2026</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2998,10 +2998,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>46073</v>
+        <v>46181</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3013,13 +3013,8 @@
           <t>HALLSTAHAMMAR</t>
         </is>
       </c>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I34" t="n">
-        <v>13</v>
+        <v>4.7</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3062,7 +3057,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 16762-2022</t>
+          <t>A 26060-2026</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3076,10 +3071,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>44673</v>
+        <v>46181</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3092,7 +3087,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>4.2</v>
+        <v>3.6</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3135,7 +3130,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 15224-2026</t>
+          <t>A 30766-2022</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3149,10 +3144,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>46105</v>
+        <v>44764</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3164,13 +3159,8 @@
           <t>HALLSTAHAMMAR</t>
         </is>
       </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I36" t="n">
-        <v>1.5</v>
+        <v>0.6</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3213,7 +3203,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 15230-2026</t>
+          <t>A 7245-2025</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3227,10 +3217,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>46105</v>
+        <v>45702</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3242,13 +3232,8 @@
           <t>HALLSTAHAMMAR</t>
         </is>
       </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I37" t="n">
-        <v>1.5</v>
+        <v>4</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3291,7 +3276,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 22072-2023</t>
+          <t>A 35238-2026</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3301,14 +3286,14 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45069</v>
+        <v>46260</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3321,7 +3306,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3364,7 +3349,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 30766-2022</t>
+          <t>A 37109-2026</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3378,10 +3363,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>44764</v>
+        <v>46274</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3394,7 +3379,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>0.6</v>
+        <v>3</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3437,7 +3422,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 35036-2024</t>
+          <t>A 8436-2023</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3451,10 +3436,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45527</v>
+        <v>44977</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3466,8 +3451,13 @@
           <t>HALLSTAHAMMAR</t>
         </is>
       </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I40" t="n">
-        <v>1.7</v>
+        <v>4</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -3510,7 +3500,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 26059-2026</t>
+          <t>A 21264-2022</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3524,10 +3514,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>46181</v>
+        <v>44705</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3539,8 +3529,13 @@
           <t>HALLSTAHAMMAR</t>
         </is>
       </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I41" t="n">
-        <v>4.7</v>
+        <v>2.4</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -3583,7 +3578,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 26060-2026</t>
+          <t>A 12077-2022</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3597,10 +3592,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>46181</v>
+        <v>44636</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3613,7 +3608,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>3.6</v>
+        <v>2.1</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -3656,7 +3651,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 35238-2026</t>
+          <t>A 37407-2023</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3666,14 +3661,14 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>46260</v>
+        <v>45156</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -3729,7 +3724,7 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 62831-2023</t>
+          <t>A 14149-2022</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3743,10 +3738,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45270</v>
+        <v>44651</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -3758,8 +3753,13 @@
           <t>HALLSTAHAMMAR</t>
         </is>
       </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I44" t="n">
-        <v>1.1</v>
+        <v>3.8</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -3802,7 +3802,7 @@
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 37109-2026</t>
+          <t>A 53343-2024</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3816,10 +3816,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>46274</v>
+        <v>45614</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -3832,7 +3832,7 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>3</v>
+        <v>0.9</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -3892,7 +3892,7 @@
         <v>46091</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -3965,7 +3965,7 @@
         <v>46111</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46290</v>
+        <v>46291</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>

--- a/Översikt HALLSTAHAMMAR.xlsx
+++ b/Översikt HALLSTAHAMMAR.xlsx
@@ -601,7 +601,7 @@
         <v>45978</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -713,7 +713,7 @@
         <v>44635</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -791,7 +791,7 @@
         <v>44887</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -864,7 +864,7 @@
         <v>44502</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -937,7 +937,7 @@
         <v>44502</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1010,7 +1010,7 @@
         <v>44739</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1083,7 +1083,7 @@
         <v>44502</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1156,7 +1156,7 @@
         <v>45365</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1234,7 +1234,7 @@
         <v>45527</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1307,7 +1307,7 @@
         <v>46034</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1380,7 +1380,7 @@
         <v>46034</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1453,7 +1453,7 @@
         <v>45069</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1526,7 +1526,7 @@
         <v>45909</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1599,7 +1599,7 @@
         <v>45911</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1672,7 +1672,7 @@
         <v>45915</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1745,7 +1745,7 @@
         <v>44888</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1818,7 +1818,7 @@
         <v>46073</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -1896,7 +1896,7 @@
         <v>46105</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -1974,7 +1974,7 @@
         <v>46105</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2052,7 +2052,7 @@
         <v>44673</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2125,7 +2125,7 @@
         <v>45982</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2198,7 +2198,7 @@
         <v>45982</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2271,7 +2271,7 @@
         <v>45982</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2344,7 +2344,7 @@
         <v>45068</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2417,7 +2417,7 @@
         <v>46146</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2490,7 +2490,7 @@
         <v>45964</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2563,7 +2563,7 @@
         <v>45527</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2636,7 +2636,7 @@
         <v>45270</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2709,7 +2709,7 @@
         <v>45713</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -2782,7 +2782,7 @@
         <v>45875</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -2855,7 +2855,7 @@
         <v>45875</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -2928,7 +2928,7 @@
         <v>45736</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3001,7 +3001,7 @@
         <v>46181</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3074,7 +3074,7 @@
         <v>46181</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3147,7 +3147,7 @@
         <v>44764</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3220,7 +3220,7 @@
         <v>45702</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3293,7 +3293,7 @@
         <v>46260</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3366,7 +3366,7 @@
         <v>46274</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3439,7 +3439,7 @@
         <v>44977</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3517,7 +3517,7 @@
         <v>44705</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3595,7 +3595,7 @@
         <v>44636</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3668,7 +3668,7 @@
         <v>45156</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -3741,7 +3741,7 @@
         <v>44651</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -3819,7 +3819,7 @@
         <v>45614</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -3892,7 +3892,7 @@
         <v>46091</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -3965,7 +3965,7 @@
         <v>46111</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>

--- a/Översikt HALLSTAHAMMAR.xlsx
+++ b/Översikt HALLSTAHAMMAR.xlsx
@@ -601,7 +601,7 @@
         <v>45978</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -713,7 +713,7 @@
         <v>44635</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -791,7 +791,7 @@
         <v>44887</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -864,7 +864,7 @@
         <v>44502</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -937,7 +937,7 @@
         <v>44502</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1010,7 +1010,7 @@
         <v>44739</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1083,7 +1083,7 @@
         <v>44502</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1156,7 +1156,7 @@
         <v>45365</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1234,7 +1234,7 @@
         <v>45527</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1307,7 +1307,7 @@
         <v>46034</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1380,7 +1380,7 @@
         <v>46034</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1453,7 +1453,7 @@
         <v>45069</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1526,7 +1526,7 @@
         <v>45909</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1599,7 +1599,7 @@
         <v>45911</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1672,7 +1672,7 @@
         <v>45915</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1745,7 +1745,7 @@
         <v>44888</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1818,7 +1818,7 @@
         <v>46073</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -1896,7 +1896,7 @@
         <v>46105</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -1974,7 +1974,7 @@
         <v>46105</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2052,7 +2052,7 @@
         <v>44673</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2125,7 +2125,7 @@
         <v>45982</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2198,7 +2198,7 @@
         <v>45982</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2271,7 +2271,7 @@
         <v>45982</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2344,7 +2344,7 @@
         <v>45068</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2417,7 +2417,7 @@
         <v>46146</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2490,7 +2490,7 @@
         <v>45964</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2563,7 +2563,7 @@
         <v>45527</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2636,7 +2636,7 @@
         <v>45270</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2709,7 +2709,7 @@
         <v>45713</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -2782,7 +2782,7 @@
         <v>45875</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -2855,7 +2855,7 @@
         <v>45875</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -2928,7 +2928,7 @@
         <v>45736</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3001,7 +3001,7 @@
         <v>46181</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3074,7 +3074,7 @@
         <v>46181</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3147,7 +3147,7 @@
         <v>44764</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3220,7 +3220,7 @@
         <v>45702</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3293,7 +3293,7 @@
         <v>46260</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3366,7 +3366,7 @@
         <v>46274</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3439,7 +3439,7 @@
         <v>44977</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3517,7 +3517,7 @@
         <v>44705</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3595,7 +3595,7 @@
         <v>44636</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3668,7 +3668,7 @@
         <v>45156</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -3741,7 +3741,7 @@
         <v>44651</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -3819,7 +3819,7 @@
         <v>45614</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -3892,7 +3892,7 @@
         <v>46091</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -3965,7 +3965,7 @@
         <v>46111</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>

--- a/Översikt HALLSTAHAMMAR.xlsx
+++ b/Översikt HALLSTAHAMMAR.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE47"/>
+  <dimension ref="A1:AE45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="0" ht="15" customHeight="1"/>
@@ -601,7 +601,7 @@
         <v>45978</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -713,7 +713,7 @@
         <v>44635</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -791,7 +791,7 @@
         <v>44887</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -864,7 +864,7 @@
         <v>44502</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -937,7 +937,7 @@
         <v>44502</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1010,7 +1010,7 @@
         <v>44739</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1083,7 +1083,7 @@
         <v>44502</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1139,7 +1139,7 @@
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 10263-2024</t>
+          <t>A 21264-2022</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1153,10 +1153,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>45365</v>
+        <v>44705</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1170,11 +1170,11 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Kyrkan</t>
+          <t>Allmännings- och besparingsskogar</t>
         </is>
       </c>
       <c r="I9" t="n">
-        <v>1.4</v>
+        <v>2.4</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -1217,7 +1217,7 @@
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 34984-2024</t>
+          <t>A 21972-2023</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1231,10 +1231,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>45527</v>
+        <v>45068</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1247,7 +1247,7 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>4.1</v>
+        <v>1.5</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
@@ -1290,7 +1290,7 @@
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 1621-2026</t>
+          <t>A 10263-2024</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1304,10 +1304,10 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>46034</v>
+        <v>45365</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1317,6 +1317,11 @@
       <c r="G11" t="inlineStr">
         <is>
           <t>HALLSTAHAMMAR</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
         </is>
       </c>
       <c r="I11" t="n">
@@ -1363,7 +1368,7 @@
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 1622-2026</t>
+          <t>A 42991-2025</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1377,10 +1382,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>46034</v>
+        <v>45909</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1393,7 +1398,7 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>1.4</v>
+        <v>7.2</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -1436,7 +1441,7 @@
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 22072-2023</t>
+          <t>A 43448-2025</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1450,10 +1455,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>45069</v>
+        <v>45911</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1466,7 +1471,7 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>3.5</v>
+        <v>1.2</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
@@ -1509,7 +1514,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 42991-2025</t>
+          <t>A 55562-2022</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1523,10 +1528,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>45909</v>
+        <v>44888</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1539,7 +1544,7 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>7.2</v>
+        <v>0.8</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -1582,7 +1587,7 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 43448-2025</t>
+          <t>A 44192-2025</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1596,10 +1601,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>45911</v>
+        <v>45915</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1612,7 +1617,7 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>1.2</v>
+        <v>0.8</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -1655,7 +1660,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 44192-2025</t>
+          <t>A 12077-2022</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1669,10 +1674,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45915</v>
+        <v>44636</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1685,7 +1690,7 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>0.8</v>
+        <v>2.1</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -1728,7 +1733,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 55562-2022</t>
+          <t>A 37072-2025</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1742,10 +1747,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>44888</v>
+        <v>45875</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1758,7 +1763,7 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>0.8</v>
+        <v>1.5</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -1801,7 +1806,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 10069-2026</t>
+          <t>A 37076-2025</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1815,10 +1820,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>46073</v>
+        <v>45875</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -1830,13 +1835,8 @@
           <t>HALLSTAHAMMAR</t>
         </is>
       </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I18" t="n">
-        <v>13</v>
+        <v>2.4</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -1879,7 +1879,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 15224-2026</t>
+          <t>A 1622-2026</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1893,10 +1893,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>46105</v>
+        <v>46034</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -1908,13 +1908,8 @@
           <t>HALLSTAHAMMAR</t>
         </is>
       </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I19" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -1957,7 +1952,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 15230-2026</t>
+          <t>A 1621-2026</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1971,10 +1966,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>46105</v>
+        <v>46034</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -1986,13 +1981,8 @@
           <t>HALLSTAHAMMAR</t>
         </is>
       </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I20" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2035,7 +2025,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 16762-2022</t>
+          <t>A 13510-2025</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2049,10 +2039,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>44673</v>
+        <v>45736</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2065,7 +2055,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>4.2</v>
+        <v>2.5</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2108,7 +2098,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 58125-2025</t>
+          <t>A 37407-2023</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2122,10 +2112,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>45982</v>
+        <v>45156</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2138,7 +2128,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>0.8</v>
+        <v>3.3</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2198,7 +2188,7 @@
         <v>45982</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2271,7 +2261,7 @@
         <v>45982</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2327,7 +2317,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 21972-2023</t>
+          <t>A 58125-2025</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2341,10 +2331,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>45068</v>
+        <v>45982</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2357,7 +2347,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>1.5</v>
+        <v>0.8</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2400,7 +2390,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 21049-2026</t>
+          <t>A 10069-2026</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2414,10 +2404,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>46146</v>
+        <v>46073</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2429,8 +2419,13 @@
           <t>HALLSTAHAMMAR</t>
         </is>
       </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I26" t="n">
-        <v>2.9</v>
+        <v>13</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2473,7 +2468,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 54207-2025</t>
+          <t>A 14149-2022</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2487,10 +2482,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>45964</v>
+        <v>44651</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2502,8 +2497,13 @@
           <t>HALLSTAHAMMAR</t>
         </is>
       </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I27" t="n">
-        <v>2.1</v>
+        <v>3.8</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -2546,7 +2546,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 35036-2024</t>
+          <t>A 53343-2024</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2560,10 +2560,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>45527</v>
+        <v>45614</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2576,7 +2576,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>1.7</v>
+        <v>0.9</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -2619,7 +2619,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 62831-2023</t>
+          <t>A 8848-2025</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2633,10 +2633,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>45270</v>
+        <v>45713</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2649,7 +2649,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>1.1</v>
+        <v>2</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -2692,7 +2692,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 8848-2025</t>
+          <t>A 8436-2023</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2706,10 +2706,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>45713</v>
+        <v>44977</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -2721,8 +2721,13 @@
           <t>HALLSTAHAMMAR</t>
         </is>
       </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I30" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -2765,7 +2770,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 37072-2025</t>
+          <t>A 7245-2025</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2779,10 +2784,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45875</v>
+        <v>45702</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -2795,7 +2800,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>1.5</v>
+        <v>4</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -2838,7 +2843,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 37076-2025</t>
+          <t>A 34984-2024</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2852,10 +2857,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>45875</v>
+        <v>45527</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -2868,7 +2873,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>2.4</v>
+        <v>4.1</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -2911,7 +2916,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 13510-2025</t>
+          <t>A 21049-2026</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2925,10 +2930,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>45736</v>
+        <v>46146</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -2941,7 +2946,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>2.5</v>
+        <v>2.9</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -2984,7 +2989,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 26059-2026</t>
+          <t>A 54207-2025</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2998,10 +3003,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>46181</v>
+        <v>45964</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3014,7 +3019,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>4.7</v>
+        <v>2.1</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3057,7 +3062,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 26060-2026</t>
+          <t>A 16762-2022</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3071,10 +3076,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>46181</v>
+        <v>44673</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3087,7 +3092,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>3.6</v>
+        <v>4.2</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3130,7 +3135,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 30766-2022</t>
+          <t>A 22072-2023</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3144,10 +3149,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>44764</v>
+        <v>45069</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3160,7 +3165,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>0.6</v>
+        <v>3.5</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3203,7 +3208,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 7245-2025</t>
+          <t>A 30766-2022</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3217,10 +3222,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45702</v>
+        <v>44764</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3233,7 +3238,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>4</v>
+        <v>0.6</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3276,7 +3281,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 35238-2026</t>
+          <t>A 35036-2024</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3286,14 +3291,14 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>46260</v>
+        <v>45527</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3306,7 +3311,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>3.3</v>
+        <v>1.7</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3349,7 +3354,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 37109-2026</t>
+          <t>A 26059-2026</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3363,10 +3368,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>46274</v>
+        <v>46181</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3379,7 +3384,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>3</v>
+        <v>4.7</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3422,7 +3427,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 8436-2023</t>
+          <t>A 26060-2026</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3436,10 +3441,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>44977</v>
+        <v>46181</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3451,13 +3456,8 @@
           <t>HALLSTAHAMMAR</t>
         </is>
       </c>
-      <c r="H40" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I40" t="n">
-        <v>4</v>
+        <v>3.6</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -3500,7 +3500,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 21264-2022</t>
+          <t>A 35238-2026</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3510,14 +3510,14 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>44705</v>
+        <v>46260</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3529,13 +3529,8 @@
           <t>HALLSTAHAMMAR</t>
         </is>
       </c>
-      <c r="H41" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I41" t="n">
-        <v>2.4</v>
+        <v>3.3</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -3578,7 +3573,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 12077-2022</t>
+          <t>A 62831-2023</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3592,10 +3587,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>44636</v>
+        <v>45270</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3608,7 +3603,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>2.1</v>
+        <v>1.1</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -3651,7 +3646,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 37407-2023</t>
+          <t>A 37109-2026</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3665,10 +3660,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45156</v>
+        <v>46274</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -3681,7 +3676,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>3.3</v>
+        <v>3</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -3724,24 +3719,24 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 14149-2022</t>
+          <t>S 697-2026</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>avverkningsanmälan</t>
+          <t>samrådsanmälan</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Skogsgödsling</t>
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>44651</v>
+        <v>46091</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -3753,86 +3748,86 @@
           <t>HALLSTAHAMMAR</t>
         </is>
       </c>
-      <c r="H44" t="inlineStr">
+      <c r="I44" t="n">
+        <v>32.5</v>
+      </c>
+      <c r="J44" t="n">
+        <v>0</v>
+      </c>
+      <c r="K44" t="n">
+        <v>0</v>
+      </c>
+      <c r="L44" t="n">
+        <v>0</v>
+      </c>
+      <c r="M44" t="n">
+        <v>0</v>
+      </c>
+      <c r="N44" t="n">
+        <v>0</v>
+      </c>
+      <c r="O44" t="n">
+        <v>0</v>
+      </c>
+      <c r="P44" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q44" t="n">
+        <v>0</v>
+      </c>
+      <c r="R44" t="n">
+        <v>0</v>
+      </c>
+      <c r="S44" t="n">
+        <v>0</v>
+      </c>
+      <c r="T44" t="n">
+        <v>0</v>
+      </c>
+      <c r="U44" t="n">
+        <v>0</v>
+      </c>
+      <c r="V44" s="2" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>S 924-2026</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>samrådsanmälan</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Skogsgödsling</t>
+        </is>
+      </c>
+      <c r="D45" s="1" t="n">
+        <v>46111</v>
+      </c>
+      <c r="E45" s="1" t="n">
+        <v>46294</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>VÄSTMANLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>HALLSTAHAMMAR</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
         <is>
           <t>Allmännings- och besparingsskogar</t>
         </is>
       </c>
-      <c r="I44" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="J44" t="n">
-        <v>0</v>
-      </c>
-      <c r="K44" t="n">
-        <v>0</v>
-      </c>
-      <c r="L44" t="n">
-        <v>0</v>
-      </c>
-      <c r="M44" t="n">
-        <v>0</v>
-      </c>
-      <c r="N44" t="n">
-        <v>0</v>
-      </c>
-      <c r="O44" t="n">
-        <v>0</v>
-      </c>
-      <c r="P44" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q44" t="n">
-        <v>0</v>
-      </c>
-      <c r="R44" t="n">
-        <v>0</v>
-      </c>
-      <c r="S44" t="n">
-        <v>0</v>
-      </c>
-      <c r="T44" t="n">
-        <v>0</v>
-      </c>
-      <c r="U44" t="n">
-        <v>0</v>
-      </c>
-      <c r="V44" s="2" t="inlineStr"/>
-    </row>
-    <row r="45" ht="15" customHeight="1">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>A 53343-2024</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D45" s="1" t="n">
-        <v>45614</v>
-      </c>
-      <c r="E45" s="1" t="n">
-        <v>46293</v>
-      </c>
-      <c r="F45" t="inlineStr">
-        <is>
-          <t>VÄSTMANLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G45" t="inlineStr">
-        <is>
-          <t>HALLSTAHAMMAR</t>
-        </is>
-      </c>
       <c r="I45" t="n">
-        <v>0.9</v>
+        <v>48.8</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -3871,157 +3866,6 @@
         <v>0</v>
       </c>
       <c r="V45" s="2" t="inlineStr"/>
-    </row>
-    <row r="46" ht="15" customHeight="1">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>S 697-2026</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>samrådsanmälan</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>Skogsgödsling</t>
-        </is>
-      </c>
-      <c r="D46" s="1" t="n">
-        <v>46091</v>
-      </c>
-      <c r="E46" s="1" t="n">
-        <v>46293</v>
-      </c>
-      <c r="F46" t="inlineStr">
-        <is>
-          <t>VÄSTMANLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G46" t="inlineStr">
-        <is>
-          <t>HALLSTAHAMMAR</t>
-        </is>
-      </c>
-      <c r="I46" t="n">
-        <v>32.5</v>
-      </c>
-      <c r="J46" t="n">
-        <v>0</v>
-      </c>
-      <c r="K46" t="n">
-        <v>0</v>
-      </c>
-      <c r="L46" t="n">
-        <v>0</v>
-      </c>
-      <c r="M46" t="n">
-        <v>0</v>
-      </c>
-      <c r="N46" t="n">
-        <v>0</v>
-      </c>
-      <c r="O46" t="n">
-        <v>0</v>
-      </c>
-      <c r="P46" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q46" t="n">
-        <v>0</v>
-      </c>
-      <c r="R46" t="n">
-        <v>0</v>
-      </c>
-      <c r="S46" t="n">
-        <v>0</v>
-      </c>
-      <c r="T46" t="n">
-        <v>0</v>
-      </c>
-      <c r="U46" t="n">
-        <v>0</v>
-      </c>
-      <c r="V46" s="2" t="inlineStr"/>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>S 924-2026</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>samrådsanmälan</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>Skogsgödsling</t>
-        </is>
-      </c>
-      <c r="D47" s="1" t="n">
-        <v>46111</v>
-      </c>
-      <c r="E47" s="1" t="n">
-        <v>46293</v>
-      </c>
-      <c r="F47" t="inlineStr">
-        <is>
-          <t>VÄSTMANLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G47" t="inlineStr">
-        <is>
-          <t>HALLSTAHAMMAR</t>
-        </is>
-      </c>
-      <c r="H47" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
-      <c r="I47" t="n">
-        <v>48.8</v>
-      </c>
-      <c r="J47" t="n">
-        <v>0</v>
-      </c>
-      <c r="K47" t="n">
-        <v>0</v>
-      </c>
-      <c r="L47" t="n">
-        <v>0</v>
-      </c>
-      <c r="M47" t="n">
-        <v>0</v>
-      </c>
-      <c r="N47" t="n">
-        <v>0</v>
-      </c>
-      <c r="O47" t="n">
-        <v>0</v>
-      </c>
-      <c r="P47" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q47" t="n">
-        <v>0</v>
-      </c>
-      <c r="R47" t="n">
-        <v>0</v>
-      </c>
-      <c r="S47" t="n">
-        <v>0</v>
-      </c>
-      <c r="T47" t="n">
-        <v>0</v>
-      </c>
-      <c r="U47" t="n">
-        <v>0</v>
-      </c>
-      <c r="V47" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Översikt HALLSTAHAMMAR.xlsx
+++ b/Översikt HALLSTAHAMMAR.xlsx
@@ -601,7 +601,7 @@
         <v>45978</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -713,7 +713,7 @@
         <v>44635</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -791,7 +791,7 @@
         <v>44887</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -864,7 +864,7 @@
         <v>44502</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -937,7 +937,7 @@
         <v>44502</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1010,7 +1010,7 @@
         <v>44739</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1083,7 +1083,7 @@
         <v>44502</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1139,7 +1139,7 @@
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 21264-2022</t>
+          <t>A 10263-2024</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1153,10 +1153,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>44705</v>
+        <v>45365</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1170,11 +1170,11 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Allmännings- och besparingsskogar</t>
+          <t>Kyrkan</t>
         </is>
       </c>
       <c r="I9" t="n">
-        <v>2.4</v>
+        <v>1.4</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -1217,7 +1217,7 @@
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 21972-2023</t>
+          <t>A 34984-2024</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1231,10 +1231,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>45068</v>
+        <v>45527</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1247,7 +1247,7 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>1.5</v>
+        <v>4.1</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
@@ -1290,7 +1290,7 @@
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 10263-2024</t>
+          <t>A 22072-2023</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1304,10 +1304,10 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>45365</v>
+        <v>45069</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1319,13 +1319,8 @@
           <t>HALLSTAHAMMAR</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I11" t="n">
-        <v>1.4</v>
+        <v>3.5</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -1368,7 +1363,7 @@
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 42991-2025</t>
+          <t>A 1621-2026</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1382,10 +1377,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>45909</v>
+        <v>46034</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1398,7 +1393,7 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>7.2</v>
+        <v>1.4</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -1441,7 +1436,7 @@
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 43448-2025</t>
+          <t>A 42991-2025</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1455,10 +1450,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>45911</v>
+        <v>45909</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1471,7 +1466,7 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>1.2</v>
+        <v>7.2</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
@@ -1514,7 +1509,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 55562-2022</t>
+          <t>A 43448-2025</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1528,10 +1523,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>44888</v>
+        <v>45911</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1544,7 +1539,7 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>0.8</v>
+        <v>1.2</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -1587,7 +1582,7 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 44192-2025</t>
+          <t>A 1622-2026</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1601,10 +1596,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>45915</v>
+        <v>46034</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1617,7 +1612,7 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>0.8</v>
+        <v>1.4</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -1660,7 +1655,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 12077-2022</t>
+          <t>A 44192-2025</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1674,10 +1669,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>44636</v>
+        <v>45915</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1690,7 +1685,7 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>2.1</v>
+        <v>0.8</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -1733,7 +1728,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 37072-2025</t>
+          <t>A 55562-2022</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1747,10 +1742,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>45875</v>
+        <v>44888</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1763,7 +1758,7 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>1.5</v>
+        <v>0.8</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -1806,7 +1801,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 37076-2025</t>
+          <t>A 16762-2022</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1820,10 +1815,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>45875</v>
+        <v>44673</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -1836,7 +1831,7 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>2.4</v>
+        <v>4.2</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -1879,7 +1874,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 1622-2026</t>
+          <t>A 37072-2025</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1893,10 +1888,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>46034</v>
+        <v>45875</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -1909,7 +1904,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -1952,7 +1947,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 1621-2026</t>
+          <t>A 37076-2025</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1966,10 +1961,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>46034</v>
+        <v>45875</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -1982,7 +1977,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>1.4</v>
+        <v>2.4</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2042,7 +2037,7 @@
         <v>45736</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2098,7 +2093,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 37407-2023</t>
+          <t>A 58125-2025</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2112,10 +2107,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>45156</v>
+        <v>45982</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2128,7 +2123,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>3.3</v>
+        <v>0.8</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2188,7 +2183,7 @@
         <v>45982</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2261,7 +2256,7 @@
         <v>45982</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2317,7 +2312,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 58125-2025</t>
+          <t>A 10069-2026</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2331,10 +2326,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>45982</v>
+        <v>46073</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2346,8 +2341,13 @@
           <t>HALLSTAHAMMAR</t>
         </is>
       </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I25" t="n">
-        <v>0.8</v>
+        <v>13</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2390,7 +2390,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 10069-2026</t>
+          <t>A 21972-2023</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2404,10 +2404,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>46073</v>
+        <v>45068</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2419,13 +2419,8 @@
           <t>HALLSTAHAMMAR</t>
         </is>
       </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I26" t="n">
-        <v>13</v>
+        <v>1.5</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2468,7 +2463,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 14149-2022</t>
+          <t>A 35036-2024</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2482,10 +2477,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>44651</v>
+        <v>45527</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2497,13 +2492,8 @@
           <t>HALLSTAHAMMAR</t>
         </is>
       </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I27" t="n">
-        <v>3.8</v>
+        <v>1.7</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -2546,7 +2536,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 53343-2024</t>
+          <t>A 62831-2023</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2560,10 +2550,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>45614</v>
+        <v>45270</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2576,7 +2566,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>0.9</v>
+        <v>1.1</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -2636,7 +2626,7 @@
         <v>45713</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2692,7 +2682,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 8436-2023</t>
+          <t>A 21049-2026</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2706,10 +2696,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>44977</v>
+        <v>46146</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -2721,13 +2711,8 @@
           <t>HALLSTAHAMMAR</t>
         </is>
       </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I30" t="n">
-        <v>4</v>
+        <v>2.9</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -2770,7 +2755,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 7245-2025</t>
+          <t>A 30766-2022</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2784,10 +2769,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45702</v>
+        <v>44764</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -2800,7 +2785,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>4</v>
+        <v>0.6</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -2843,7 +2828,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 34984-2024</t>
+          <t>A 54207-2025</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2857,10 +2842,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>45527</v>
+        <v>45964</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -2873,7 +2858,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>4.1</v>
+        <v>2.1</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -2916,7 +2901,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 21049-2026</t>
+          <t>A 7245-2025</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2930,10 +2915,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>46146</v>
+        <v>45702</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -2946,7 +2931,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>2.9</v>
+        <v>4</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -2989,7 +2974,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 54207-2025</t>
+          <t>A 26059-2026</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3003,10 +2988,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>45964</v>
+        <v>46181</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3019,7 +3004,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>2.1</v>
+        <v>4.7</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3062,7 +3047,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 16762-2022</t>
+          <t>A 26060-2026</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3076,10 +3061,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>44673</v>
+        <v>46181</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3092,7 +3077,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>4.2</v>
+        <v>3.6</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3135,7 +3120,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 22072-2023</t>
+          <t>A 8436-2023</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3149,10 +3134,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45069</v>
+        <v>44977</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3164,8 +3149,13 @@
           <t>HALLSTAHAMMAR</t>
         </is>
       </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I36" t="n">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3208,7 +3198,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 30766-2022</t>
+          <t>A 21264-2022</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3222,10 +3212,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>44764</v>
+        <v>44705</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3237,8 +3227,13 @@
           <t>HALLSTAHAMMAR</t>
         </is>
       </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I37" t="n">
-        <v>0.6</v>
+        <v>2.4</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3281,7 +3276,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 35036-2024</t>
+          <t>A 12077-2022</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3295,10 +3290,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45527</v>
+        <v>44636</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3311,7 +3306,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>1.7</v>
+        <v>2.1</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3354,7 +3349,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 26059-2026</t>
+          <t>A 37407-2023</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3368,10 +3363,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>46181</v>
+        <v>45156</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3384,7 +3379,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>4.7</v>
+        <v>3.3</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3427,7 +3422,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 26060-2026</t>
+          <t>A 35238-2026</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3437,14 +3432,14 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>46181</v>
+        <v>46260</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3457,7 +3452,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>3.6</v>
+        <v>3.3</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -3500,7 +3495,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 35238-2026</t>
+          <t>A 14149-2022</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3510,14 +3505,14 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>46260</v>
+        <v>44651</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3529,8 +3524,13 @@
           <t>HALLSTAHAMMAR</t>
         </is>
       </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I41" t="n">
-        <v>3.3</v>
+        <v>3.8</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -3573,7 +3573,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 62831-2023</t>
+          <t>A 37109-2026</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3587,10 +3587,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>45270</v>
+        <v>46274</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3603,7 +3603,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>1.1</v>
+        <v>3</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -3646,7 +3646,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 37109-2026</t>
+          <t>A 53343-2024</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3660,10 +3660,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>46274</v>
+        <v>45614</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -3676,7 +3676,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>3</v>
+        <v>0.9</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -3736,7 +3736,7 @@
         <v>46091</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -3809,7 +3809,7 @@
         <v>46111</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>

--- a/Översikt HALLSTAHAMMAR.xlsx
+++ b/Översikt HALLSTAHAMMAR.xlsx
@@ -601,7 +601,7 @@
         <v>45978</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -713,7 +713,7 @@
         <v>44635</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -791,7 +791,7 @@
         <v>44887</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -847,7 +847,7 @@
     <row r="5" ht="15" customHeight="1">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A 68619-2021</t>
+          <t>A 26702-2022</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -861,10 +861,10 @@
         </is>
       </c>
       <c r="D5" s="1" t="n">
-        <v>44502</v>
+        <v>44739</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -877,7 +877,7 @@
         </is>
       </c>
       <c r="I5" t="n">
-        <v>13.5</v>
+        <v>3.8</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
@@ -937,7 +937,7 @@
         <v>44502</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -993,7 +993,7 @@
     <row r="7" ht="15" customHeight="1">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A 26702-2022</t>
+          <t>A 68619-2021</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1007,10 +1007,10 @@
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>44739</v>
+        <v>44502</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1023,7 +1023,7 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>3.8</v>
+        <v>13.5</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
@@ -1083,7 +1083,7 @@
         <v>44502</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1139,7 +1139,7 @@
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 10263-2024</t>
+          <t>A 21264-2022</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1153,10 +1153,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>45365</v>
+        <v>44705</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1170,11 +1170,11 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Kyrkan</t>
+          <t>Allmännings- och besparingsskogar</t>
         </is>
       </c>
       <c r="I9" t="n">
-        <v>1.4</v>
+        <v>2.4</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -1217,7 +1217,7 @@
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 34984-2024</t>
+          <t>A 37407-2023</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1231,10 +1231,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>45527</v>
+        <v>45156</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1247,7 +1247,7 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>4.1</v>
+        <v>3.3</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
@@ -1290,7 +1290,7 @@
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 22072-2023</t>
+          <t>A 21972-2023</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1304,10 +1304,10 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>45069</v>
+        <v>45068</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1320,7 +1320,7 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>3.5</v>
+        <v>1.5</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -1363,7 +1363,7 @@
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 1621-2026</t>
+          <t>A 16762-2022</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1377,10 +1377,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>46034</v>
+        <v>44673</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1393,7 +1393,7 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>1.4</v>
+        <v>4.2</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -1436,7 +1436,7 @@
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 42991-2025</t>
+          <t>A 62831-2023</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1450,10 +1450,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>45909</v>
+        <v>45270</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1466,7 +1466,7 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>7.2</v>
+        <v>1.1</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
@@ -1509,7 +1509,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 43448-2025</t>
+          <t>A 22072-2023</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1523,10 +1523,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>45911</v>
+        <v>45069</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1539,7 +1539,7 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>1.2</v>
+        <v>3.5</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -1582,7 +1582,7 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 1622-2026</t>
+          <t>A 30766-2022</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1596,10 +1596,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>46034</v>
+        <v>44764</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1612,7 +1612,7 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>1.4</v>
+        <v>0.6</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -1655,7 +1655,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 44192-2025</t>
+          <t>A 14149-2022</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1669,10 +1669,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45915</v>
+        <v>44651</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1684,8 +1684,13 @@
           <t>HALLSTAHAMMAR</t>
         </is>
       </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I16" t="n">
-        <v>0.8</v>
+        <v>3.8</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -1728,7 +1733,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 55562-2022</t>
+          <t>A 53343-2024</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1742,10 +1747,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>44888</v>
+        <v>45614</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1758,7 +1763,7 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -1801,7 +1806,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 16762-2022</t>
+          <t>A 10263-2024</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1815,10 +1820,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>44673</v>
+        <v>45365</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -1830,8 +1835,13 @@
           <t>HALLSTAHAMMAR</t>
         </is>
       </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I18" t="n">
-        <v>4.2</v>
+        <v>1.4</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -1874,7 +1884,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 37072-2025</t>
+          <t>A 35036-2024</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1888,10 +1898,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>45875</v>
+        <v>45527</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -1904,7 +1914,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>1.5</v>
+        <v>1.7</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -1947,7 +1957,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 37076-2025</t>
+          <t>A 8848-2025</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1961,10 +1971,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>45875</v>
+        <v>45713</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -1977,7 +1987,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>2.4</v>
+        <v>2</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2020,7 +2030,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 13510-2025</t>
+          <t>A 55562-2022</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2034,10 +2044,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>45736</v>
+        <v>44888</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2050,7 +2060,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>2.5</v>
+        <v>0.8</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2093,7 +2103,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 58125-2025</t>
+          <t>A 8436-2023</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2107,10 +2117,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>45982</v>
+        <v>44977</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2122,8 +2132,13 @@
           <t>HALLSTAHAMMAR</t>
         </is>
       </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I22" t="n">
-        <v>0.8</v>
+        <v>4</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2166,7 +2181,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 58109-2025</t>
+          <t>A 7245-2025</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2180,10 +2195,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>45982</v>
+        <v>45702</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2196,7 +2211,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>2.5</v>
+        <v>4</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2239,7 +2254,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 58111-2025</t>
+          <t>A 34984-2024</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2253,10 +2268,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45982</v>
+        <v>45527</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2269,7 +2284,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>0.6</v>
+        <v>4.1</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2312,7 +2327,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 10069-2026</t>
+          <t>A 37072-2025</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2326,10 +2341,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>46073</v>
+        <v>45875</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2341,13 +2356,8 @@
           <t>HALLSTAHAMMAR</t>
         </is>
       </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I25" t="n">
-        <v>13</v>
+        <v>1.5</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2390,7 +2400,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 21972-2023</t>
+          <t>A 37076-2025</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2404,10 +2414,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>45068</v>
+        <v>45875</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2420,7 +2430,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>1.5</v>
+        <v>2.4</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2463,7 +2473,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 35036-2024</t>
+          <t>A 12077-2022</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2477,10 +2487,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>45527</v>
+        <v>44636</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2493,7 +2503,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>1.7</v>
+        <v>2.1</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -2536,7 +2546,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 62831-2023</t>
+          <t>A 13510-2025</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2550,10 +2560,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>45270</v>
+        <v>45736</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2566,7 +2576,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>1.1</v>
+        <v>2.5</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -2609,7 +2619,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 8848-2025</t>
+          <t>A 42991-2025</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2623,10 +2633,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>45713</v>
+        <v>45909</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2639,7 +2649,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>2</v>
+        <v>7.2</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -2682,7 +2692,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 21049-2026</t>
+          <t>A 43448-2025</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2696,10 +2706,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>46146</v>
+        <v>45911</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -2712,7 +2722,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>2.9</v>
+        <v>1.2</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -2755,7 +2765,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 30766-2022</t>
+          <t>A 44192-2025</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2769,10 +2779,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>44764</v>
+        <v>45915</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -2785,7 +2795,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -2828,7 +2838,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 54207-2025</t>
+          <t>A 58109-2025</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2842,10 +2852,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>45964</v>
+        <v>45982</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -2858,7 +2868,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>2.1</v>
+        <v>2.5</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -2901,7 +2911,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 7245-2025</t>
+          <t>A 58111-2025</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2915,10 +2925,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>45702</v>
+        <v>45982</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -2931,7 +2941,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>4</v>
+        <v>0.6</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -2974,7 +2984,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 26059-2026</t>
+          <t>A 58125-2025</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2988,10 +2998,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>46181</v>
+        <v>45982</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3004,7 +3014,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>4.7</v>
+        <v>0.8</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3047,7 +3057,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 26060-2026</t>
+          <t>A 1622-2026</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3061,10 +3071,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>46181</v>
+        <v>46034</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3077,7 +3087,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>3.6</v>
+        <v>1.4</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3120,7 +3130,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 8436-2023</t>
+          <t>A 1621-2026</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3134,10 +3144,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>44977</v>
+        <v>46034</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3149,13 +3159,8 @@
           <t>HALLSTAHAMMAR</t>
         </is>
       </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I36" t="n">
-        <v>4</v>
+        <v>1.4</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3198,7 +3203,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 21264-2022</t>
+          <t>A 10069-2026</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3212,10 +3217,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>44705</v>
+        <v>46073</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3233,7 +3238,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>2.4</v>
+        <v>13</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3276,7 +3281,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 12077-2022</t>
+          <t>A 21049-2026</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3290,10 +3295,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>44636</v>
+        <v>46146</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3306,7 +3311,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>2.1</v>
+        <v>2.9</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3349,7 +3354,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 37407-2023</t>
+          <t>A 54207-2025</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3363,10 +3368,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45156</v>
+        <v>45964</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3379,7 +3384,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>3.3</v>
+        <v>2.1</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3422,7 +3427,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 35238-2026</t>
+          <t>A 26059-2026</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3432,14 +3437,14 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>46260</v>
+        <v>46181</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3452,7 +3457,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>3.3</v>
+        <v>4.7</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -3495,7 +3500,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 14149-2022</t>
+          <t>A 26060-2026</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3509,10 +3514,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>44651</v>
+        <v>46181</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3524,13 +3529,8 @@
           <t>HALLSTAHAMMAR</t>
         </is>
       </c>
-      <c r="H41" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I41" t="n">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -3573,7 +3573,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 37109-2026</t>
+          <t>A 35238-2026</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3583,14 +3583,14 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>46274</v>
+        <v>46260</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3603,7 +3603,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>3</v>
+        <v>3.3</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -3646,7 +3646,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 53343-2024</t>
+          <t>A 37109-2026</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3660,10 +3660,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45614</v>
+        <v>46274</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -3676,7 +3676,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>0.9</v>
+        <v>3</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -3736,7 +3736,7 @@
         <v>46091</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -3809,7 +3809,7 @@
         <v>46111</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>

--- a/Översikt HALLSTAHAMMAR.xlsx
+++ b/Översikt HALLSTAHAMMAR.xlsx
@@ -601,7 +601,7 @@
         <v>45978</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -713,7 +713,7 @@
         <v>44635</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -791,7 +791,7 @@
         <v>44887</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -847,7 +847,7 @@
     <row r="5" ht="15" customHeight="1">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A 26702-2022</t>
+          <t>A 68619-2021</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -861,10 +861,10 @@
         </is>
       </c>
       <c r="D5" s="1" t="n">
-        <v>44739</v>
+        <v>44502</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -877,7 +877,7 @@
         </is>
       </c>
       <c r="I5" t="n">
-        <v>3.8</v>
+        <v>13.5</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
@@ -937,7 +937,7 @@
         <v>44502</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -993,7 +993,7 @@
     <row r="7" ht="15" customHeight="1">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A 68619-2021</t>
+          <t>A 26702-2022</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1007,10 +1007,10 @@
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>44502</v>
+        <v>44739</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1023,7 +1023,7 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>13.5</v>
+        <v>3.8</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
@@ -1083,7 +1083,7 @@
         <v>44502</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1139,7 +1139,7 @@
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 21264-2022</t>
+          <t>A 10263-2024</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1153,10 +1153,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>44705</v>
+        <v>45365</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1170,11 +1170,11 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Allmännings- och besparingsskogar</t>
+          <t>Kyrkan</t>
         </is>
       </c>
       <c r="I9" t="n">
-        <v>2.4</v>
+        <v>1.4</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -1217,7 +1217,7 @@
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 37407-2023</t>
+          <t>A 1621-2026</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1231,10 +1231,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>45156</v>
+        <v>46034</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1247,7 +1247,7 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>3.3</v>
+        <v>1.4</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
@@ -1290,7 +1290,7 @@
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 21972-2023</t>
+          <t>A 1622-2026</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1304,10 +1304,10 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>45068</v>
+        <v>46034</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1320,7 +1320,7 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -1363,7 +1363,7 @@
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 16762-2022</t>
+          <t>A 34984-2024</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1377,10 +1377,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>44673</v>
+        <v>45527</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1393,7 +1393,7 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -1436,7 +1436,7 @@
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 62831-2023</t>
+          <t>A 22072-2023</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1450,10 +1450,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>45270</v>
+        <v>45069</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1466,7 +1466,7 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>1.1</v>
+        <v>3.5</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
@@ -1509,7 +1509,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 22072-2023</t>
+          <t>A 42991-2025</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1523,10 +1523,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>45069</v>
+        <v>45909</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1539,7 +1539,7 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>3.5</v>
+        <v>7.2</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -1582,7 +1582,7 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 30766-2022</t>
+          <t>A 43448-2025</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1596,10 +1596,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>44764</v>
+        <v>45911</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1612,7 +1612,7 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>0.6</v>
+        <v>1.2</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -1655,7 +1655,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 14149-2022</t>
+          <t>A 44192-2025</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1669,10 +1669,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>44651</v>
+        <v>45915</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1684,13 +1684,8 @@
           <t>HALLSTAHAMMAR</t>
         </is>
       </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I16" t="n">
-        <v>3.8</v>
+        <v>0.8</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -1733,7 +1728,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 53343-2024</t>
+          <t>A 10069-2026</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1747,10 +1742,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>45614</v>
+        <v>46073</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1762,8 +1757,13 @@
           <t>HALLSTAHAMMAR</t>
         </is>
       </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I17" t="n">
-        <v>0.9</v>
+        <v>13</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -1806,7 +1806,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 10263-2024</t>
+          <t>A 55562-2022</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1820,10 +1820,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>45365</v>
+        <v>44888</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -1835,13 +1835,8 @@
           <t>HALLSTAHAMMAR</t>
         </is>
       </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I18" t="n">
-        <v>1.4</v>
+        <v>0.8</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -1884,7 +1879,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 35036-2024</t>
+          <t>A 16762-2022</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1898,10 +1893,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>45527</v>
+        <v>44673</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -1914,7 +1909,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>1.7</v>
+        <v>4.2</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -1957,7 +1952,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 8848-2025</t>
+          <t>A 58125-2025</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1971,10 +1966,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>45713</v>
+        <v>45982</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -1987,7 +1982,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>2</v>
+        <v>0.8</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2030,7 +2025,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 55562-2022</t>
+          <t>A 58109-2025</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2044,10 +2039,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>44888</v>
+        <v>45982</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2060,7 +2055,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>0.8</v>
+        <v>2.5</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2103,7 +2098,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 8436-2023</t>
+          <t>A 58111-2025</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2117,10 +2112,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>44977</v>
+        <v>45982</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2132,13 +2127,8 @@
           <t>HALLSTAHAMMAR</t>
         </is>
       </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I22" t="n">
-        <v>4</v>
+        <v>0.6</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2181,7 +2171,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 7245-2025</t>
+          <t>A 37072-2025</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2195,10 +2185,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>45702</v>
+        <v>45875</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2211,7 +2201,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>4</v>
+        <v>1.5</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2254,7 +2244,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 34984-2024</t>
+          <t>A 37076-2025</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2268,10 +2258,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45527</v>
+        <v>45875</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2284,7 +2274,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>4.1</v>
+        <v>2.4</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2327,7 +2317,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 37072-2025</t>
+          <t>A 13510-2025</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2341,10 +2331,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>45875</v>
+        <v>45736</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2357,7 +2347,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>1.5</v>
+        <v>2.5</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2400,7 +2390,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 37076-2025</t>
+          <t>A 21972-2023</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2414,10 +2404,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>45875</v>
+        <v>45068</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2430,7 +2420,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>2.4</v>
+        <v>1.5</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2473,7 +2463,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 12077-2022</t>
+          <t>A 21049-2026</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2487,10 +2477,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>44636</v>
+        <v>46146</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2503,7 +2493,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>2.1</v>
+        <v>2.9</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -2546,7 +2536,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 13510-2025</t>
+          <t>A 54207-2025</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2560,10 +2550,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>45736</v>
+        <v>45964</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2576,7 +2566,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>2.5</v>
+        <v>2.1</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -2619,7 +2609,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 42991-2025</t>
+          <t>A 35036-2024</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2633,10 +2623,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>45909</v>
+        <v>45527</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2649,7 +2639,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>7.2</v>
+        <v>1.7</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -2692,7 +2682,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 43448-2025</t>
+          <t>A 62831-2023</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2706,10 +2696,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>45911</v>
+        <v>45270</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -2722,7 +2712,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -2765,7 +2755,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 44192-2025</t>
+          <t>A 8848-2025</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2779,10 +2769,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45915</v>
+        <v>45713</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -2795,7 +2785,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>0.8</v>
+        <v>2</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -2838,7 +2828,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 58109-2025</t>
+          <t>A 30766-2022</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2852,10 +2842,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>45982</v>
+        <v>44764</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -2868,7 +2858,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>2.5</v>
+        <v>0.6</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -2911,7 +2901,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 58111-2025</t>
+          <t>A 26059-2026</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2925,10 +2915,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>45982</v>
+        <v>46181</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -2941,7 +2931,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>0.6</v>
+        <v>4.7</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -2984,7 +2974,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 58125-2025</t>
+          <t>A 26060-2026</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2998,10 +2988,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>45982</v>
+        <v>46181</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3014,7 +3004,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>0.8</v>
+        <v>3.6</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3057,7 +3047,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 1622-2026</t>
+          <t>A 7245-2025</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3071,10 +3061,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>46034</v>
+        <v>45702</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3087,7 +3077,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>1.4</v>
+        <v>4</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3130,7 +3120,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 1621-2026</t>
+          <t>A 35238-2026</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3140,14 +3130,14 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>46034</v>
+        <v>46260</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3160,7 +3150,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>1.4</v>
+        <v>3.3</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3203,7 +3193,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 10069-2026</t>
+          <t>A 8436-2023</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3217,10 +3207,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>46073</v>
+        <v>44977</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3234,11 +3224,11 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Allmännings- och besparingsskogar</t>
+          <t>Kyrkan</t>
         </is>
       </c>
       <c r="I37" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3281,7 +3271,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 21049-2026</t>
+          <t>A 37109-2026</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3295,10 +3285,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>46146</v>
+        <v>46274</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3311,7 +3301,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3354,7 +3344,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 54207-2025</t>
+          <t>A 21264-2022</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3368,10 +3358,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45964</v>
+        <v>44705</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3383,8 +3373,13 @@
           <t>HALLSTAHAMMAR</t>
         </is>
       </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I39" t="n">
-        <v>2.1</v>
+        <v>2.4</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3427,7 +3422,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 26059-2026</t>
+          <t>A 12077-2022</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3441,10 +3436,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>46181</v>
+        <v>44636</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3457,7 +3452,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>4.7</v>
+        <v>2.1</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -3500,7 +3495,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 26060-2026</t>
+          <t>A 37407-2023</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3514,10 +3509,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>46181</v>
+        <v>45156</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3530,7 +3525,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>3.6</v>
+        <v>3.3</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -3573,7 +3568,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 35238-2026</t>
+          <t>A 14149-2022</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3583,14 +3578,14 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>46260</v>
+        <v>44651</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3602,8 +3597,13 @@
           <t>HALLSTAHAMMAR</t>
         </is>
       </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I42" t="n">
-        <v>3.3</v>
+        <v>3.8</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -3646,7 +3646,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 37109-2026</t>
+          <t>A 53343-2024</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3660,10 +3660,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>46274</v>
+        <v>45614</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -3676,7 +3676,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>3</v>
+        <v>0.9</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -3736,7 +3736,7 @@
         <v>46091</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -3809,7 +3809,7 @@
         <v>46111</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46296</v>
+        <v>46297</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>

--- a/Översikt HALLSTAHAMMAR.xlsx
+++ b/Översikt HALLSTAHAMMAR.xlsx
@@ -601,7 +601,7 @@
         <v>45978</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -713,7 +713,7 @@
         <v>44635</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -791,7 +791,7 @@
         <v>44887</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -864,7 +864,7 @@
         <v>44502</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -937,7 +937,7 @@
         <v>44502</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1010,7 +1010,7 @@
         <v>44739</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1083,7 +1083,7 @@
         <v>44502</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1139,7 +1139,7 @@
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 10263-2024</t>
+          <t>A 21972-2023</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1153,10 +1153,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>45365</v>
+        <v>45068</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1168,13 +1168,8 @@
           <t>HALLSTAHAMMAR</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I9" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -1217,7 +1212,7 @@
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 1621-2026</t>
+          <t>A 21264-2022</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1231,10 +1226,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>46034</v>
+        <v>44705</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1246,8 +1241,13 @@
           <t>HALLSTAHAMMAR</t>
         </is>
       </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I10" t="n">
-        <v>1.4</v>
+        <v>2.4</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
@@ -1290,7 +1290,7 @@
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 1622-2026</t>
+          <t>A 10263-2024</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1304,10 +1304,10 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>46034</v>
+        <v>45365</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1317,6 +1317,11 @@
       <c r="G11" t="inlineStr">
         <is>
           <t>HALLSTAHAMMAR</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
         </is>
       </c>
       <c r="I11" t="n">
@@ -1363,7 +1368,7 @@
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 34984-2024</t>
+          <t>A 1622-2026</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1377,10 +1382,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>45527</v>
+        <v>46034</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1393,7 +1398,7 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>4.1</v>
+        <v>1.4</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -1436,7 +1441,7 @@
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 22072-2023</t>
+          <t>A 1621-2026</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1450,10 +1455,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>45069</v>
+        <v>46034</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1466,7 +1471,7 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>3.5</v>
+        <v>1.4</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
@@ -1509,7 +1514,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 42991-2025</t>
+          <t>A 55562-2022</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1523,10 +1528,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>45909</v>
+        <v>44888</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1539,7 +1544,7 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>7.2</v>
+        <v>0.8</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -1582,7 +1587,7 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 43448-2025</t>
+          <t>A 42991-2025</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1596,10 +1601,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>45911</v>
+        <v>45909</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1612,7 +1617,7 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>1.2</v>
+        <v>7.2</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -1655,7 +1660,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 44192-2025</t>
+          <t>A 43448-2025</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1669,10 +1674,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45915</v>
+        <v>45911</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1685,7 +1690,7 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>0.8</v>
+        <v>1.2</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -1728,7 +1733,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 10069-2026</t>
+          <t>A 44192-2025</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1742,10 +1747,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>46073</v>
+        <v>45915</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1757,13 +1762,8 @@
           <t>HALLSTAHAMMAR</t>
         </is>
       </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I17" t="n">
-        <v>13</v>
+        <v>0.8</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -1806,7 +1806,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 55562-2022</t>
+          <t>A 12077-2022</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1820,10 +1820,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>44888</v>
+        <v>44636</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -1836,7 +1836,7 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>0.8</v>
+        <v>2.1</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -1879,7 +1879,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 16762-2022</t>
+          <t>A 10069-2026</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1893,10 +1893,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>44673</v>
+        <v>46073</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -1908,8 +1908,13 @@
           <t>HALLSTAHAMMAR</t>
         </is>
       </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I19" t="n">
-        <v>4.2</v>
+        <v>13</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -1952,7 +1957,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 58125-2025</t>
+          <t>A 37407-2023</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1966,10 +1971,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>45982</v>
+        <v>45156</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -1982,7 +1987,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>0.8</v>
+        <v>3.3</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2042,7 +2047,7 @@
         <v>45982</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2115,7 +2120,7 @@
         <v>45982</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2171,7 +2176,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 37072-2025</t>
+          <t>A 58125-2025</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2185,10 +2190,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>45875</v>
+        <v>45982</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2201,7 +2206,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>1.5</v>
+        <v>0.8</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2244,7 +2249,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 37076-2025</t>
+          <t>A 14149-2022</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2258,10 +2263,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45875</v>
+        <v>44651</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2273,8 +2278,13 @@
           <t>HALLSTAHAMMAR</t>
         </is>
       </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I24" t="n">
-        <v>2.4</v>
+        <v>3.8</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2317,7 +2327,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 13510-2025</t>
+          <t>A 53343-2024</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2331,10 +2341,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>45736</v>
+        <v>45614</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2347,7 +2357,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>2.5</v>
+        <v>0.9</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2390,7 +2400,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 21972-2023</t>
+          <t>A 8848-2025</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2404,10 +2414,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>45068</v>
+        <v>45713</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2420,7 +2430,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2480,7 +2490,7 @@
         <v>46146</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2536,7 +2546,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 54207-2025</t>
+          <t>A 8436-2023</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2550,10 +2560,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>45964</v>
+        <v>44977</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2565,8 +2575,13 @@
           <t>HALLSTAHAMMAR</t>
         </is>
       </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I28" t="n">
-        <v>2.1</v>
+        <v>4</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -2609,7 +2624,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 35036-2024</t>
+          <t>A 37072-2025</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2623,10 +2638,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>45527</v>
+        <v>45875</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2639,7 +2654,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>1.7</v>
+        <v>1.5</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -2682,7 +2697,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 62831-2023</t>
+          <t>A 54207-2025</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2696,10 +2711,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>45270</v>
+        <v>45964</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -2712,7 +2727,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>1.1</v>
+        <v>2.1</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -2755,7 +2770,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 8848-2025</t>
+          <t>A 37076-2025</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2769,10 +2784,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45713</v>
+        <v>45875</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -2785,7 +2800,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>2</v>
+        <v>2.4</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -2828,7 +2843,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 30766-2022</t>
+          <t>A 7245-2025</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2842,10 +2857,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>44764</v>
+        <v>45702</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -2858,7 +2873,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>0.6</v>
+        <v>4</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -2901,7 +2916,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 26059-2026</t>
+          <t>A 13510-2025</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2915,10 +2930,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>46181</v>
+        <v>45736</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -2931,7 +2946,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>4.7</v>
+        <v>2.5</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -2974,7 +2989,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 26060-2026</t>
+          <t>A 34984-2024</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2988,10 +3003,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>46181</v>
+        <v>45527</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3004,7 +3019,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>3.6</v>
+        <v>4.1</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3047,7 +3062,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 7245-2025</t>
+          <t>A 26059-2026</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3061,10 +3076,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>45702</v>
+        <v>46181</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3077,7 +3092,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>4</v>
+        <v>4.7</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3120,7 +3135,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 35238-2026</t>
+          <t>A 26060-2026</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3130,14 +3145,14 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>46260</v>
+        <v>46181</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3150,7 +3165,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>3.3</v>
+        <v>3.6</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3193,7 +3208,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 8436-2023</t>
+          <t>A 16762-2022</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3207,10 +3222,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>44977</v>
+        <v>44673</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3222,13 +3237,8 @@
           <t>HALLSTAHAMMAR</t>
         </is>
       </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I37" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3271,7 +3281,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 37109-2026</t>
+          <t>A 22072-2023</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3285,10 +3295,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>46274</v>
+        <v>45069</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3301,7 +3311,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3344,7 +3354,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 21264-2022</t>
+          <t>A 30766-2022</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3358,10 +3368,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>44705</v>
+        <v>44764</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3373,13 +3383,8 @@
           <t>HALLSTAHAMMAR</t>
         </is>
       </c>
-      <c r="H39" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I39" t="n">
-        <v>2.4</v>
+        <v>0.6</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3422,7 +3427,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 12077-2022</t>
+          <t>A 35238-2026</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3432,14 +3437,14 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>44636</v>
+        <v>46260</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3452,7 +3457,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>2.1</v>
+        <v>3.3</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -3495,7 +3500,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 37407-2023</t>
+          <t>A 37109-2026</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3509,10 +3514,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45156</v>
+        <v>46274</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3525,7 +3530,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>3.3</v>
+        <v>3</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -3568,7 +3573,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 14149-2022</t>
+          <t>A 35036-2024</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3582,10 +3587,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>44651</v>
+        <v>45527</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3597,13 +3602,8 @@
           <t>HALLSTAHAMMAR</t>
         </is>
       </c>
-      <c r="H42" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I42" t="n">
-        <v>3.8</v>
+        <v>1.7</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -3646,7 +3646,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 53343-2024</t>
+          <t>A 62831-2023</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3660,10 +3660,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45614</v>
+        <v>45270</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -3676,7 +3676,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>0.9</v>
+        <v>1.1</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -3736,7 +3736,7 @@
         <v>46091</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -3809,7 +3809,7 @@
         <v>46111</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46297</v>
+        <v>46298</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>

--- a/Översikt HALLSTAHAMMAR.xlsx
+++ b/Översikt HALLSTAHAMMAR.xlsx
@@ -601,7 +601,7 @@
         <v>45978</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -713,7 +713,7 @@
         <v>44635</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -791,7 +791,7 @@
         <v>44887</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -864,7 +864,7 @@
         <v>44502</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -937,7 +937,7 @@
         <v>44502</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1010,7 +1010,7 @@
         <v>44739</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1083,7 +1083,7 @@
         <v>44502</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1156,7 +1156,7 @@
         <v>45068</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1229,7 +1229,7 @@
         <v>44705</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1307,7 +1307,7 @@
         <v>45365</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1385,7 +1385,7 @@
         <v>46034</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1458,7 +1458,7 @@
         <v>46034</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1531,7 +1531,7 @@
         <v>44888</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1604,7 +1604,7 @@
         <v>45909</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1677,7 +1677,7 @@
         <v>45911</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1750,7 +1750,7 @@
         <v>45915</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1823,7 +1823,7 @@
         <v>44636</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -1896,7 +1896,7 @@
         <v>46073</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -1974,7 +1974,7 @@
         <v>45156</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2047,7 +2047,7 @@
         <v>45982</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2120,7 +2120,7 @@
         <v>45982</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2193,7 +2193,7 @@
         <v>45982</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2266,7 +2266,7 @@
         <v>44651</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2344,7 +2344,7 @@
         <v>45614</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2417,7 +2417,7 @@
         <v>45713</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2490,7 +2490,7 @@
         <v>46146</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2563,7 +2563,7 @@
         <v>44977</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2641,7 +2641,7 @@
         <v>45875</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2714,7 +2714,7 @@
         <v>45964</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -2787,7 +2787,7 @@
         <v>45875</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -2860,7 +2860,7 @@
         <v>45702</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -2933,7 +2933,7 @@
         <v>45736</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3006,7 +3006,7 @@
         <v>45527</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3079,7 +3079,7 @@
         <v>46181</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3152,7 +3152,7 @@
         <v>46181</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3225,7 +3225,7 @@
         <v>44673</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3298,7 +3298,7 @@
         <v>45069</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3371,7 +3371,7 @@
         <v>44764</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3444,7 +3444,7 @@
         <v>46260</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3517,7 +3517,7 @@
         <v>46274</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3590,7 +3590,7 @@
         <v>45527</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3663,7 +3663,7 @@
         <v>45270</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -3736,7 +3736,7 @@
         <v>46091</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -3809,7 +3809,7 @@
         <v>46111</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>

--- a/Översikt HALLSTAHAMMAR.xlsx
+++ b/Översikt HALLSTAHAMMAR.xlsx
@@ -601,7 +601,7 @@
         <v>45978</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -713,7 +713,7 @@
         <v>44635</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -791,7 +791,7 @@
         <v>44887</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -864,7 +864,7 @@
         <v>44502</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -937,7 +937,7 @@
         <v>44502</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1010,7 +1010,7 @@
         <v>44739</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1083,7 +1083,7 @@
         <v>44502</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1156,7 +1156,7 @@
         <v>45068</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1229,7 +1229,7 @@
         <v>44705</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1307,7 +1307,7 @@
         <v>45365</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1385,7 +1385,7 @@
         <v>46034</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1458,7 +1458,7 @@
         <v>46034</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1531,7 +1531,7 @@
         <v>44888</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1604,7 +1604,7 @@
         <v>45909</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1677,7 +1677,7 @@
         <v>45911</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1750,7 +1750,7 @@
         <v>45915</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1823,7 +1823,7 @@
         <v>44636</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -1896,7 +1896,7 @@
         <v>46073</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -1974,7 +1974,7 @@
         <v>45156</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2047,7 +2047,7 @@
         <v>45982</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2120,7 +2120,7 @@
         <v>45982</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2193,7 +2193,7 @@
         <v>45982</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2266,7 +2266,7 @@
         <v>44651</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2344,7 +2344,7 @@
         <v>45614</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2417,7 +2417,7 @@
         <v>45713</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2490,7 +2490,7 @@
         <v>46146</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2563,7 +2563,7 @@
         <v>44977</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2641,7 +2641,7 @@
         <v>45875</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2714,7 +2714,7 @@
         <v>45964</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -2787,7 +2787,7 @@
         <v>45875</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -2860,7 +2860,7 @@
         <v>45702</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -2933,7 +2933,7 @@
         <v>45736</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3006,7 +3006,7 @@
         <v>45527</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3079,7 +3079,7 @@
         <v>46181</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3152,7 +3152,7 @@
         <v>46181</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3225,7 +3225,7 @@
         <v>44673</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3298,7 +3298,7 @@
         <v>45069</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3371,7 +3371,7 @@
         <v>44764</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3444,7 +3444,7 @@
         <v>46260</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3517,7 +3517,7 @@
         <v>46274</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3590,7 +3590,7 @@
         <v>45527</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3663,7 +3663,7 @@
         <v>45270</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -3736,7 +3736,7 @@
         <v>46091</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -3809,7 +3809,7 @@
         <v>46111</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>

--- a/Översikt HALLSTAHAMMAR.xlsx
+++ b/Översikt HALLSTAHAMMAR.xlsx
@@ -601,7 +601,7 @@
         <v>45978</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -713,7 +713,7 @@
         <v>44635</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -791,7 +791,7 @@
         <v>44887</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -864,7 +864,7 @@
         <v>44502</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -937,7 +937,7 @@
         <v>44502</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1010,7 +1010,7 @@
         <v>44739</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1083,7 +1083,7 @@
         <v>44502</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1139,7 +1139,7 @@
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 21972-2023</t>
+          <t>A 10263-2024</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1153,10 +1153,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>45068</v>
+        <v>45365</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1168,8 +1168,13 @@
           <t>HALLSTAHAMMAR</t>
         </is>
       </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I9" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -1212,7 +1217,7 @@
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 21264-2022</t>
+          <t>A 34984-2024</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1226,10 +1231,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>44705</v>
+        <v>45527</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1241,13 +1246,8 @@
           <t>HALLSTAHAMMAR</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I10" t="n">
-        <v>2.4</v>
+        <v>4.1</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
@@ -1290,7 +1290,7 @@
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 10263-2024</t>
+          <t>A 22072-2023</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1304,10 +1304,10 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>45365</v>
+        <v>45069</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1319,13 +1319,8 @@
           <t>HALLSTAHAMMAR</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I11" t="n">
-        <v>1.4</v>
+        <v>3.5</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -1368,7 +1363,7 @@
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 1622-2026</t>
+          <t>A 55562-2022</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1382,10 +1377,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>46034</v>
+        <v>44888</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1398,7 +1393,7 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>1.4</v>
+        <v>0.8</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -1441,7 +1436,7 @@
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 1621-2026</t>
+          <t>A 42991-2025</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1455,10 +1450,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>46034</v>
+        <v>45909</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1471,7 +1466,7 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>1.4</v>
+        <v>7.2</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
@@ -1514,7 +1509,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 55562-2022</t>
+          <t>A 43448-2025</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1528,10 +1523,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>44888</v>
+        <v>45911</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1544,7 +1539,7 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>0.8</v>
+        <v>1.2</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -1587,7 +1582,7 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 42991-2025</t>
+          <t>A 44192-2025</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1601,10 +1596,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>45909</v>
+        <v>45915</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1617,7 +1612,7 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>7.2</v>
+        <v>0.8</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -1660,7 +1655,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 43448-2025</t>
+          <t>A 16762-2022</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1674,10 +1669,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45911</v>
+        <v>44673</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1690,7 +1685,7 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>1.2</v>
+        <v>4.2</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -1733,7 +1728,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 44192-2025</t>
+          <t>A 37072-2025</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1747,10 +1742,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>45915</v>
+        <v>45875</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1763,7 +1758,7 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>0.8</v>
+        <v>1.5</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -1806,7 +1801,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 12077-2022</t>
+          <t>A 37076-2025</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1820,10 +1815,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>44636</v>
+        <v>45875</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -1836,7 +1831,7 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>2.1</v>
+        <v>2.4</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -1879,7 +1874,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 10069-2026</t>
+          <t>A 13510-2025</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1893,10 +1888,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>46073</v>
+        <v>45736</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -1908,13 +1903,8 @@
           <t>HALLSTAHAMMAR</t>
         </is>
       </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I19" t="n">
-        <v>13</v>
+        <v>2.5</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -1957,7 +1947,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 37407-2023</t>
+          <t>A 10069-2026</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1971,10 +1961,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>45156</v>
+        <v>46073</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -1986,8 +1976,13 @@
           <t>HALLSTAHAMMAR</t>
         </is>
       </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I20" t="n">
-        <v>3.3</v>
+        <v>13</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2030,7 +2025,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 58109-2025</t>
+          <t>A 58125-2025</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,7 +2042,7 @@
         <v>45982</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2060,7 +2055,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>2.5</v>
+        <v>0.8</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2103,7 +2098,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 58111-2025</t>
+          <t>A 58109-2025</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2120,7 +2115,7 @@
         <v>45982</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2133,7 +2128,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>0.6</v>
+        <v>2.5</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2176,7 +2171,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 58125-2025</t>
+          <t>A 58111-2025</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2193,7 +2188,7 @@
         <v>45982</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2206,7 +2201,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2249,7 +2244,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 14149-2022</t>
+          <t>A 21972-2023</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2263,10 +2258,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>44651</v>
+        <v>45068</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2278,13 +2273,8 @@
           <t>HALLSTAHAMMAR</t>
         </is>
       </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I24" t="n">
-        <v>3.8</v>
+        <v>1.5</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2327,7 +2317,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 53343-2024</t>
+          <t>A 1621-2026</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2341,10 +2331,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>45614</v>
+        <v>46034</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2357,7 +2347,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>0.9</v>
+        <v>1.4</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2400,7 +2390,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 8848-2025</t>
+          <t>A 1622-2026</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2414,10 +2404,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>45713</v>
+        <v>46034</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2430,7 +2420,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>2</v>
+        <v>1.4</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2473,7 +2463,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 21049-2026</t>
+          <t>A 35036-2024</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2487,10 +2477,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>46146</v>
+        <v>45527</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2503,7 +2493,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>2.9</v>
+        <v>1.7</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -2546,7 +2536,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 8436-2023</t>
+          <t>A 62831-2023</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2560,10 +2550,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>44977</v>
+        <v>45270</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2575,13 +2565,8 @@
           <t>HALLSTAHAMMAR</t>
         </is>
       </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I28" t="n">
-        <v>4</v>
+        <v>1.1</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -2624,7 +2609,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 37072-2025</t>
+          <t>A 8848-2025</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2638,10 +2623,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>45875</v>
+        <v>45713</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2654,7 +2639,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -2697,7 +2682,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 54207-2025</t>
+          <t>A 21049-2026</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2711,10 +2696,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>45964</v>
+        <v>46146</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -2727,7 +2712,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>2.1</v>
+        <v>2.9</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -2770,7 +2755,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 37076-2025</t>
+          <t>A 54207-2025</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2784,10 +2769,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45875</v>
+        <v>45964</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -2800,7 +2785,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>2.4</v>
+        <v>2.1</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -2843,7 +2828,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 7245-2025</t>
+          <t>A 30766-2022</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2857,10 +2842,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>45702</v>
+        <v>44764</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -2873,7 +2858,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>4</v>
+        <v>0.6</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -2916,7 +2901,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 13510-2025</t>
+          <t>A 7245-2025</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2930,10 +2915,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>45736</v>
+        <v>45702</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -2946,7 +2931,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>2.5</v>
+        <v>4</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -2989,7 +2974,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 34984-2024</t>
+          <t>A 26059-2026</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3003,10 +2988,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>45527</v>
+        <v>46181</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3019,7 +3004,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>4.1</v>
+        <v>4.7</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3062,7 +3047,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 26059-2026</t>
+          <t>A 26060-2026</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3079,7 +3064,7 @@
         <v>46181</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3092,7 +3077,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>4.7</v>
+        <v>3.6</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3135,7 +3120,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 26060-2026</t>
+          <t>A 8436-2023</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3149,10 +3134,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>46181</v>
+        <v>44977</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3164,8 +3149,13 @@
           <t>HALLSTAHAMMAR</t>
         </is>
       </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I36" t="n">
-        <v>3.6</v>
+        <v>4</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3208,7 +3198,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 16762-2022</t>
+          <t>A 35238-2026</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3218,14 +3208,14 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>44673</v>
+        <v>46260</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3238,7 +3228,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>4.2</v>
+        <v>3.3</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3281,7 +3271,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 22072-2023</t>
+          <t>A 21264-2022</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3295,10 +3285,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45069</v>
+        <v>44705</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3310,8 +3300,13 @@
           <t>HALLSTAHAMMAR</t>
         </is>
       </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I38" t="n">
-        <v>3.5</v>
+        <v>2.4</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3354,7 +3349,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 30766-2022</t>
+          <t>A 12077-2022</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3368,10 +3363,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>44764</v>
+        <v>44636</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3384,7 +3379,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>0.6</v>
+        <v>2.1</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3427,7 +3422,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 35238-2026</t>
+          <t>A 37407-2023</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3437,14 +3432,14 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>46260</v>
+        <v>45156</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3517,7 +3512,7 @@
         <v>46274</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3573,7 +3568,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 35036-2024</t>
+          <t>A 14149-2022</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3587,10 +3582,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>45527</v>
+        <v>44651</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3602,8 +3597,13 @@
           <t>HALLSTAHAMMAR</t>
         </is>
       </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I42" t="n">
-        <v>1.7</v>
+        <v>3.8</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -3646,7 +3646,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 62831-2023</t>
+          <t>A 53343-2024</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3660,10 +3660,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45270</v>
+        <v>45614</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -3676,7 +3676,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>1.1</v>
+        <v>0.9</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -3736,7 +3736,7 @@
         <v>46091</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -3809,7 +3809,7 @@
         <v>46111</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>

--- a/Översikt HALLSTAHAMMAR.xlsx
+++ b/Översikt HALLSTAHAMMAR.xlsx
@@ -601,7 +601,7 @@
         <v>45978</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -713,7 +713,7 @@
         <v>44635</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -791,7 +791,7 @@
         <v>44887</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -864,7 +864,7 @@
         <v>44502</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -937,7 +937,7 @@
         <v>44502</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1010,7 +1010,7 @@
         <v>44739</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1083,7 +1083,7 @@
         <v>44502</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1139,7 +1139,7 @@
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 10263-2024</t>
+          <t>A 21264-2022</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1153,10 +1153,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>45365</v>
+        <v>44705</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1170,11 +1170,11 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Kyrkan</t>
+          <t>Allmännings- och besparingsskogar</t>
         </is>
       </c>
       <c r="I9" t="n">
-        <v>1.4</v>
+        <v>2.4</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -1217,7 +1217,7 @@
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 34984-2024</t>
+          <t>A 21972-2023</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1231,10 +1231,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>45527</v>
+        <v>45068</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1247,7 +1247,7 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>4.1</v>
+        <v>1.5</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
@@ -1290,7 +1290,7 @@
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 22072-2023</t>
+          <t>A 10263-2024</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1304,10 +1304,10 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>45069</v>
+        <v>45365</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1319,8 +1319,13 @@
           <t>HALLSTAHAMMAR</t>
         </is>
       </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I11" t="n">
-        <v>3.5</v>
+        <v>1.4</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -1380,7 +1385,7 @@
         <v>44888</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1436,7 +1441,7 @@
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 42991-2025</t>
+          <t>A 1622-2026</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1450,10 +1455,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>45909</v>
+        <v>46034</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1466,7 +1471,7 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>7.2</v>
+        <v>1.4</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
@@ -1509,7 +1514,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 43448-2025</t>
+          <t>A 1621-2026</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1523,10 +1528,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>45911</v>
+        <v>46034</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1539,7 +1544,7 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -1582,7 +1587,7 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 44192-2025</t>
+          <t>A 12077-2022</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1596,10 +1601,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>45915</v>
+        <v>44636</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1612,7 +1617,7 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>0.8</v>
+        <v>2.1</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -1655,7 +1660,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 16762-2022</t>
+          <t>A 42991-2025</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1669,10 +1674,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>44673</v>
+        <v>45909</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1685,7 +1690,7 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>4.2</v>
+        <v>7.2</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -1728,7 +1733,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 37072-2025</t>
+          <t>A 43448-2025</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1742,10 +1747,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>45875</v>
+        <v>45911</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1758,7 +1763,7 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>1.5</v>
+        <v>1.2</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -1801,7 +1806,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 37076-2025</t>
+          <t>A 44192-2025</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1815,10 +1820,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>45875</v>
+        <v>45915</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -1831,7 +1836,7 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>2.4</v>
+        <v>0.8</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -1874,7 +1879,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 13510-2025</t>
+          <t>A 10069-2026</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1888,10 +1893,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>45736</v>
+        <v>46073</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -1903,8 +1908,13 @@
           <t>HALLSTAHAMMAR</t>
         </is>
       </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I19" t="n">
-        <v>2.5</v>
+        <v>13</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -1947,7 +1957,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 10069-2026</t>
+          <t>A 37407-2023</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1961,10 +1971,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>46073</v>
+        <v>45156</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -1976,13 +1986,8 @@
           <t>HALLSTAHAMMAR</t>
         </is>
       </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I20" t="n">
-        <v>13</v>
+        <v>3.3</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2025,7 +2030,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 58125-2025</t>
+          <t>A 37072-2025</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2039,10 +2044,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>45982</v>
+        <v>45875</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2055,7 +2060,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>0.8</v>
+        <v>1.5</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2098,7 +2103,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 58109-2025</t>
+          <t>A 37076-2025</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2112,10 +2117,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>45982</v>
+        <v>45875</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2128,7 +2133,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2171,7 +2176,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 58111-2025</t>
+          <t>A 13510-2025</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2185,10 +2190,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>45982</v>
+        <v>45736</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2201,7 +2206,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>0.6</v>
+        <v>2.5</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2244,7 +2249,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 21972-2023</t>
+          <t>A 58109-2025</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2258,10 +2263,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45068</v>
+        <v>45982</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2274,7 +2279,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>1.5</v>
+        <v>2.5</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2317,7 +2322,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 1621-2026</t>
+          <t>A 58111-2025</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2331,10 +2336,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>46034</v>
+        <v>45982</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2347,7 +2352,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>1.4</v>
+        <v>0.6</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2390,7 +2395,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 1622-2026</t>
+          <t>A 58125-2025</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2404,10 +2409,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>46034</v>
+        <v>45982</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2420,7 +2425,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>1.4</v>
+        <v>0.8</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2463,7 +2468,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 35036-2024</t>
+          <t>A 21049-2026</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2477,10 +2482,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>45527</v>
+        <v>46146</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2493,7 +2498,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>1.7</v>
+        <v>2.9</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -2536,7 +2541,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 62831-2023</t>
+          <t>A 54207-2025</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2550,10 +2555,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>45270</v>
+        <v>45964</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2566,7 +2571,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>1.1</v>
+        <v>2.1</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -2609,7 +2614,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 8848-2025</t>
+          <t>A 14149-2022</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2623,10 +2628,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>45713</v>
+        <v>44651</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2638,8 +2643,13 @@
           <t>HALLSTAHAMMAR</t>
         </is>
       </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I29" t="n">
-        <v>2</v>
+        <v>3.8</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -2682,7 +2692,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 21049-2026</t>
+          <t>A 53343-2024</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2696,10 +2706,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>46146</v>
+        <v>45614</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -2712,7 +2722,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>2.9</v>
+        <v>0.9</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -2755,7 +2765,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 54207-2025</t>
+          <t>A 8848-2025</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2769,10 +2779,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45964</v>
+        <v>45713</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -2785,7 +2795,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -2828,7 +2838,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 30766-2022</t>
+          <t>A 26059-2026</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2842,10 +2852,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>44764</v>
+        <v>46181</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -2858,7 +2868,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>0.6</v>
+        <v>4.7</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -2901,7 +2911,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 7245-2025</t>
+          <t>A 26060-2026</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2915,10 +2925,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>45702</v>
+        <v>46181</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -2931,7 +2941,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>4</v>
+        <v>3.6</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -2974,7 +2984,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 26059-2026</t>
+          <t>A 8436-2023</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2988,10 +2998,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>46181</v>
+        <v>44977</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3003,8 +3013,13 @@
           <t>HALLSTAHAMMAR</t>
         </is>
       </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I34" t="n">
-        <v>4.7</v>
+        <v>4</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3047,7 +3062,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 26060-2026</t>
+          <t>A 7245-2025</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3061,10 +3076,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>46181</v>
+        <v>45702</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3077,7 +3092,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>3.6</v>
+        <v>4</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3120,7 +3135,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 8436-2023</t>
+          <t>A 34984-2024</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3134,10 +3149,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>44977</v>
+        <v>45527</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3149,13 +3164,8 @@
           <t>HALLSTAHAMMAR</t>
         </is>
       </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I36" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3215,7 +3225,7 @@
         <v>46260</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3271,7 +3281,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 21264-2022</t>
+          <t>A 16762-2022</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3285,10 +3295,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>44705</v>
+        <v>44673</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3300,13 +3310,8 @@
           <t>HALLSTAHAMMAR</t>
         </is>
       </c>
-      <c r="H38" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I38" t="n">
-        <v>2.4</v>
+        <v>4.2</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3349,7 +3354,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 12077-2022</t>
+          <t>A 37109-2026</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3363,10 +3368,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>44636</v>
+        <v>46274</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3379,7 +3384,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>2.1</v>
+        <v>3</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3422,7 +3427,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 37407-2023</t>
+          <t>A 22072-2023</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3436,10 +3441,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45156</v>
+        <v>45069</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3452,7 +3457,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -3495,7 +3500,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 37109-2026</t>
+          <t>A 30766-2022</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3509,10 +3514,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>46274</v>
+        <v>44764</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3525,7 +3530,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>3</v>
+        <v>0.6</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -3568,7 +3573,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 14149-2022</t>
+          <t>A 35036-2024</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3582,10 +3587,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>44651</v>
+        <v>45527</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3597,13 +3602,8 @@
           <t>HALLSTAHAMMAR</t>
         </is>
       </c>
-      <c r="H42" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I42" t="n">
-        <v>3.8</v>
+        <v>1.7</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -3646,7 +3646,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 53343-2024</t>
+          <t>A 62831-2023</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3660,10 +3660,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45614</v>
+        <v>45270</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -3676,7 +3676,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>0.9</v>
+        <v>1.1</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -3736,7 +3736,7 @@
         <v>46091</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -3809,7 +3809,7 @@
         <v>46111</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46301</v>
+        <v>46302</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>

--- a/Översikt HALLSTAHAMMAR.xlsx
+++ b/Översikt HALLSTAHAMMAR.xlsx
@@ -601,7 +601,7 @@
         <v>45978</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -713,7 +713,7 @@
         <v>44635</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -791,7 +791,7 @@
         <v>44887</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -864,7 +864,7 @@
         <v>44502</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -937,7 +937,7 @@
         <v>44502</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1010,7 +1010,7 @@
         <v>44739</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1083,7 +1083,7 @@
         <v>44502</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1139,7 +1139,7 @@
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 21264-2022</t>
+          <t>A 53343-2024</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1153,10 +1153,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>44705</v>
+        <v>45614</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1168,13 +1168,8 @@
           <t>HALLSTAHAMMAR</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I9" t="n">
-        <v>2.4</v>
+        <v>0.9</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -1217,7 +1212,7 @@
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 21972-2023</t>
+          <t>A 10263-2024</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1231,10 +1226,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>45068</v>
+        <v>45365</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1246,8 +1241,13 @@
           <t>HALLSTAHAMMAR</t>
         </is>
       </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I10" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
@@ -1290,7 +1290,7 @@
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 10263-2024</t>
+          <t>A 21972-2023</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1304,10 +1304,10 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>45365</v>
+        <v>45068</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1319,13 +1319,8 @@
           <t>HALLSTAHAMMAR</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I11" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -1368,7 +1363,7 @@
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 55562-2022</t>
+          <t>A 42991-2025</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1382,10 +1377,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>44888</v>
+        <v>45909</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1398,7 +1393,7 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>0.8</v>
+        <v>7.2</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -1441,7 +1436,7 @@
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 1622-2026</t>
+          <t>A 43448-2025</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1455,10 +1450,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>46034</v>
+        <v>45911</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1471,7 +1466,7 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>1.4</v>
+        <v>1.2</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
@@ -1514,7 +1509,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 1621-2026</t>
+          <t>A 44192-2025</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1528,10 +1523,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>46034</v>
+        <v>45915</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1544,7 +1539,7 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>1.4</v>
+        <v>0.8</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -1587,7 +1582,7 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 12077-2022</t>
+          <t>A 34984-2024</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1601,10 +1596,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>44636</v>
+        <v>45527</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1617,7 +1612,7 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>2.1</v>
+        <v>4.1</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -1660,7 +1655,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 42991-2025</t>
+          <t>A 35036-2024</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1674,10 +1669,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45909</v>
+        <v>45527</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1690,7 +1685,7 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>7.2</v>
+        <v>1.7</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -1733,7 +1728,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 43448-2025</t>
+          <t>A 62831-2023</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1747,10 +1742,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>45911</v>
+        <v>45270</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1763,7 +1758,7 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -1806,7 +1801,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 44192-2025</t>
+          <t>A 8848-2025</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1820,10 +1815,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>45915</v>
+        <v>45713</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -1836,7 +1831,7 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>0.8</v>
+        <v>2</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -1879,7 +1874,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 10069-2026</t>
+          <t>A 22072-2023</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1893,10 +1888,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>46073</v>
+        <v>45069</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -1908,13 +1903,8 @@
           <t>HALLSTAHAMMAR</t>
         </is>
       </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I19" t="n">
-        <v>13</v>
+        <v>3.5</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -1957,7 +1947,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 37407-2023</t>
+          <t>A 55562-2022</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1971,10 +1961,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>45156</v>
+        <v>44888</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -1987,7 +1977,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>3.3</v>
+        <v>0.8</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2047,7 +2037,7 @@
         <v>45875</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2120,7 +2110,7 @@
         <v>45875</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2193,7 +2183,7 @@
         <v>45736</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2249,7 +2239,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 58109-2025</t>
+          <t>A 30766-2022</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2263,10 +2253,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45982</v>
+        <v>44764</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2279,7 +2269,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>2.5</v>
+        <v>0.6</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2322,7 +2312,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 58111-2025</t>
+          <t>A 58125-2025</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2339,7 +2329,7 @@
         <v>45982</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2352,7 +2342,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2395,7 +2385,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 58125-2025</t>
+          <t>A 58109-2025</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2412,7 +2402,7 @@
         <v>45982</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2425,7 +2415,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>0.8</v>
+        <v>2.5</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2468,7 +2458,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 21049-2026</t>
+          <t>A 58111-2025</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2482,10 +2472,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>46146</v>
+        <v>45982</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2498,7 +2488,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>2.9</v>
+        <v>0.6</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -2541,7 +2531,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 54207-2025</t>
+          <t>A 16762-2022</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2555,10 +2545,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>45964</v>
+        <v>44673</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2571,7 +2561,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>2.1</v>
+        <v>4.2</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -2614,7 +2604,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 14149-2022</t>
+          <t>A 21049-2026</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2628,10 +2618,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>44651</v>
+        <v>46146</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2643,13 +2633,8 @@
           <t>HALLSTAHAMMAR</t>
         </is>
       </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I29" t="n">
-        <v>3.8</v>
+        <v>2.9</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -2692,7 +2677,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 53343-2024</t>
+          <t>A 7245-2025</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2706,10 +2691,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>45614</v>
+        <v>45702</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -2722,7 +2707,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>0.9</v>
+        <v>4</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -2765,7 +2750,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 8848-2025</t>
+          <t>A 54207-2025</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2779,10 +2764,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45713</v>
+        <v>45964</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -2795,7 +2780,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -2838,7 +2823,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 26059-2026</t>
+          <t>A 1621-2026</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2852,10 +2837,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>46181</v>
+        <v>46034</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -2868,7 +2853,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>4.7</v>
+        <v>1.4</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -2911,7 +2896,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 26060-2026</t>
+          <t>A 1622-2026</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2925,10 +2910,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>46181</v>
+        <v>46034</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -2941,7 +2926,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>3.6</v>
+        <v>1.4</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -3001,7 +2986,7 @@
         <v>44977</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3062,7 +3047,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 7245-2025</t>
+          <t>A 10069-2026</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3076,10 +3061,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>45702</v>
+        <v>46073</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3091,8 +3076,13 @@
           <t>HALLSTAHAMMAR</t>
         </is>
       </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I35" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3135,7 +3125,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 34984-2024</t>
+          <t>A 26059-2026</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3149,10 +3139,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45527</v>
+        <v>46181</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3165,7 +3155,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>4.1</v>
+        <v>4.7</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3208,7 +3198,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 35238-2026</t>
+          <t>A 26060-2026</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3218,14 +3208,14 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>46260</v>
+        <v>46181</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3238,7 +3228,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>3.3</v>
+        <v>3.6</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3281,7 +3271,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 16762-2022</t>
+          <t>A 21264-2022</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3295,10 +3285,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>44673</v>
+        <v>44705</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3310,8 +3300,13 @@
           <t>HALLSTAHAMMAR</t>
         </is>
       </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I38" t="n">
-        <v>4.2</v>
+        <v>2.4</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3354,7 +3349,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 37109-2026</t>
+          <t>A 12077-2022</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3368,10 +3363,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>46274</v>
+        <v>44636</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3384,7 +3379,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>3</v>
+        <v>2.1</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3427,7 +3422,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 22072-2023</t>
+          <t>A 37407-2023</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3441,10 +3436,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45069</v>
+        <v>45156</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3457,7 +3452,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -3500,7 +3495,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 30766-2022</t>
+          <t>A 14149-2022</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3514,10 +3509,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>44764</v>
+        <v>44651</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3529,8 +3524,13 @@
           <t>HALLSTAHAMMAR</t>
         </is>
       </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I41" t="n">
-        <v>0.6</v>
+        <v>3.8</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -3573,7 +3573,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 35036-2024</t>
+          <t>A 37109-2026</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3587,10 +3587,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>45527</v>
+        <v>46274</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3603,7 +3603,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>1.7</v>
+        <v>3</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -3646,7 +3646,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 62831-2023</t>
+          <t>A 35238-2026</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3656,14 +3656,14 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45270</v>
+        <v>46260</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -3676,7 +3676,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>1.1</v>
+        <v>3.3</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -3736,7 +3736,7 @@
         <v>46091</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -3809,7 +3809,7 @@
         <v>46111</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46302</v>
+        <v>46303</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>

--- a/Översikt HALLSTAHAMMAR.xlsx
+++ b/Översikt HALLSTAHAMMAR.xlsx
@@ -601,7 +601,7 @@
         <v>45978</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -713,7 +713,7 @@
         <v>44635</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -791,7 +791,7 @@
         <v>44887</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -864,7 +864,7 @@
         <v>44502</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -937,7 +937,7 @@
         <v>44502</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1010,7 +1010,7 @@
         <v>44739</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1083,7 +1083,7 @@
         <v>44502</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1139,7 +1139,7 @@
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 53343-2024</t>
+          <t>A 21972-2023</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1153,10 +1153,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>45614</v>
+        <v>45068</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1169,7 +1169,7 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>0.9</v>
+        <v>1.5</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -1212,7 +1212,7 @@
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 10263-2024</t>
+          <t>A 21264-2022</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1226,10 +1226,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>45365</v>
+        <v>44705</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1243,11 +1243,11 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Kyrkan</t>
+          <t>Allmännings- och besparingsskogar</t>
         </is>
       </c>
       <c r="I10" t="n">
-        <v>1.4</v>
+        <v>2.4</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
@@ -1290,7 +1290,7 @@
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 21972-2023</t>
+          <t>A 10263-2024</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1304,10 +1304,10 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>45068</v>
+        <v>45365</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1319,8 +1319,13 @@
           <t>HALLSTAHAMMAR</t>
         </is>
       </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I11" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -1363,7 +1368,7 @@
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 42991-2025</t>
+          <t>A 55562-2022</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1377,10 +1382,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>45909</v>
+        <v>44888</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1393,7 +1398,7 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>7.2</v>
+        <v>0.8</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -1436,7 +1441,7 @@
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 43448-2025</t>
+          <t>A 12077-2022</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1450,10 +1455,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>45911</v>
+        <v>44636</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1466,7 +1471,7 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>1.2</v>
+        <v>2.1</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
@@ -1509,7 +1514,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 44192-2025</t>
+          <t>A 37407-2023</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1523,10 +1528,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>45915</v>
+        <v>45156</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1539,7 +1544,7 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>0.8</v>
+        <v>3.3</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -1582,7 +1587,7 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 34984-2024</t>
+          <t>A 37072-2025</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1596,10 +1601,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>45527</v>
+        <v>45875</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1612,7 +1617,7 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>4.1</v>
+        <v>1.5</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -1655,7 +1660,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 35036-2024</t>
+          <t>A 37076-2025</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1669,10 +1674,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45527</v>
+        <v>45875</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1685,7 +1690,7 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>1.7</v>
+        <v>2.4</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -1728,7 +1733,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 62831-2023</t>
+          <t>A 13510-2025</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1742,10 +1747,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>45270</v>
+        <v>45736</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1758,7 +1763,7 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>1.1</v>
+        <v>2.5</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -1801,7 +1806,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 8848-2025</t>
+          <t>A 42991-2025</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1815,10 +1820,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>45713</v>
+        <v>45909</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -1831,7 +1836,7 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>2</v>
+        <v>7.2</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -1874,7 +1879,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 22072-2023</t>
+          <t>A 43448-2025</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1888,10 +1893,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>45069</v>
+        <v>45911</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -1904,7 +1909,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>3.5</v>
+        <v>1.2</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -1947,7 +1952,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 55562-2022</t>
+          <t>A 44192-2025</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1961,10 +1966,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>44888</v>
+        <v>45915</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2020,7 +2025,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 37072-2025</t>
+          <t>A 14149-2022</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2034,10 +2039,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>45875</v>
+        <v>44651</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2049,8 +2054,13 @@
           <t>HALLSTAHAMMAR</t>
         </is>
       </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I21" t="n">
-        <v>1.5</v>
+        <v>3.8</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2093,7 +2103,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 37076-2025</t>
+          <t>A 53343-2024</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2107,10 +2117,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>45875</v>
+        <v>45614</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2123,7 +2133,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>2.4</v>
+        <v>0.9</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2166,7 +2176,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 13510-2025</t>
+          <t>A 8848-2025</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2180,10 +2190,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>45736</v>
+        <v>45713</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2196,7 +2206,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2239,7 +2249,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 30766-2022</t>
+          <t>A 58109-2025</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2253,10 +2263,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>44764</v>
+        <v>45982</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2269,7 +2279,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>0.6</v>
+        <v>2.5</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2312,7 +2322,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 58125-2025</t>
+          <t>A 58111-2025</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2329,7 +2339,7 @@
         <v>45982</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2342,7 +2352,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2385,7 +2395,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 58109-2025</t>
+          <t>A 58125-2025</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2402,7 +2412,7 @@
         <v>45982</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2415,7 +2425,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>2.5</v>
+        <v>0.8</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2458,7 +2468,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 58111-2025</t>
+          <t>A 8436-2023</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2472,10 +2482,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>45982</v>
+        <v>44977</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2487,8 +2497,13 @@
           <t>HALLSTAHAMMAR</t>
         </is>
       </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I27" t="n">
-        <v>0.6</v>
+        <v>4</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -2531,7 +2546,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 16762-2022</t>
+          <t>A 7245-2025</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2545,10 +2560,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>44673</v>
+        <v>45702</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2561,7 +2576,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -2604,7 +2619,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 21049-2026</t>
+          <t>A 1621-2026</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2618,10 +2633,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>46146</v>
+        <v>46034</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2634,7 +2649,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>2.9</v>
+        <v>1.4</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -2677,7 +2692,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 7245-2025</t>
+          <t>A 34984-2024</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2691,10 +2706,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>45702</v>
+        <v>45527</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -2707,7 +2722,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -2750,7 +2765,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 54207-2025</t>
+          <t>A 10069-2026</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2764,10 +2779,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45964</v>
+        <v>46073</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -2779,8 +2794,13 @@
           <t>HALLSTAHAMMAR</t>
         </is>
       </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I31" t="n">
-        <v>2.1</v>
+        <v>13</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -2823,7 +2843,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 1621-2026</t>
+          <t>A 21049-2026</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2837,10 +2857,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>46034</v>
+        <v>46146</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -2853,7 +2873,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>1.4</v>
+        <v>2.9</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -2896,7 +2916,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 1622-2026</t>
+          <t>A 16762-2022</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2910,10 +2930,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>46034</v>
+        <v>44673</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -2926,7 +2946,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>1.4</v>
+        <v>4.2</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -2969,7 +2989,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 8436-2023</t>
+          <t>A 54207-2025</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2983,10 +3003,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>44977</v>
+        <v>45964</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -2998,13 +3018,8 @@
           <t>HALLSTAHAMMAR</t>
         </is>
       </c>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I34" t="n">
-        <v>4</v>
+        <v>2.1</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3047,7 +3062,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 10069-2026</t>
+          <t>A 22072-2023</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3061,10 +3076,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>46073</v>
+        <v>45069</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3076,13 +3091,8 @@
           <t>HALLSTAHAMMAR</t>
         </is>
       </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I35" t="n">
-        <v>13</v>
+        <v>3.5</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3125,7 +3135,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 26059-2026</t>
+          <t>A 30766-2022</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3139,10 +3149,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>46181</v>
+        <v>44764</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3155,7 +3165,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>4.7</v>
+        <v>0.6</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3198,7 +3208,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 26060-2026</t>
+          <t>A 35036-2024</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3212,10 +3222,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>46181</v>
+        <v>45527</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3228,7 +3238,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>3.6</v>
+        <v>1.7</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3271,7 +3281,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 21264-2022</t>
+          <t>A 26059-2026</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3285,10 +3295,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>44705</v>
+        <v>46181</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3300,13 +3310,8 @@
           <t>HALLSTAHAMMAR</t>
         </is>
       </c>
-      <c r="H38" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I38" t="n">
-        <v>2.4</v>
+        <v>4.7</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3349,7 +3354,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 12077-2022</t>
+          <t>A 26060-2026</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3363,10 +3368,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>44636</v>
+        <v>46181</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3379,7 +3384,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>2.1</v>
+        <v>3.6</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3422,7 +3427,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 37407-2023</t>
+          <t>A 62831-2023</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3436,10 +3441,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45156</v>
+        <v>45270</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3452,7 +3457,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>3.3</v>
+        <v>1.1</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -3495,7 +3500,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 14149-2022</t>
+          <t>A 37109-2026</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3509,10 +3514,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>44651</v>
+        <v>46274</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3524,13 +3529,8 @@
           <t>HALLSTAHAMMAR</t>
         </is>
       </c>
-      <c r="H41" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I41" t="n">
-        <v>3.8</v>
+        <v>3</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -3573,7 +3573,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 37109-2026</t>
+          <t>A 41863-2026</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3587,10 +3587,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>46274</v>
+        <v>46303</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3603,7 +3603,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>3</v>
+        <v>1.9</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -3663,7 +3663,7 @@
         <v>46260</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -3736,7 +3736,7 @@
         <v>46091</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -3809,7 +3809,7 @@
         <v>46111</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>

--- a/Översikt HALLSTAHAMMAR.xlsx
+++ b/Översikt HALLSTAHAMMAR.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE45"/>
+  <dimension ref="A1:AE43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="0" ht="15" customHeight="1"/>
@@ -601,7 +601,7 @@
         <v>45978</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -713,7 +713,7 @@
         <v>44635</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -791,7 +791,7 @@
         <v>44887</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -864,7 +864,7 @@
         <v>44502</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -920,7 +920,7 @@
     <row r="6" ht="15" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A 68624-2021</t>
+          <t>A 26702-2022</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -934,10 +934,10 @@
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>44502</v>
+        <v>44739</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -950,7 +950,7 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>5.5</v>
+        <v>3.8</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
@@ -993,7 +993,7 @@
     <row r="7" ht="15" customHeight="1">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A 26702-2022</t>
+          <t>A 68624-2021</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1007,10 +1007,10 @@
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>44739</v>
+        <v>44502</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1023,7 +1023,7 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>3.8</v>
+        <v>5.5</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
@@ -1083,7 +1083,7 @@
         <v>44502</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1139,7 +1139,7 @@
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 21972-2023</t>
+          <t>A 10263-2024</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1153,10 +1153,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>45068</v>
+        <v>45365</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1168,8 +1168,13 @@
           <t>HALLSTAHAMMAR</t>
         </is>
       </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I9" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -1212,7 +1217,7 @@
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 21264-2022</t>
+          <t>A 37407-2023</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1226,10 +1231,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>44705</v>
+        <v>45156</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1241,13 +1246,8 @@
           <t>HALLSTAHAMMAR</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I10" t="n">
-        <v>2.4</v>
+        <v>3.3</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
@@ -1290,7 +1290,7 @@
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 10263-2024</t>
+          <t>A 35036-2024</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1304,10 +1304,10 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>45365</v>
+        <v>45527</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1319,13 +1319,8 @@
           <t>HALLSTAHAMMAR</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I11" t="n">
-        <v>1.4</v>
+        <v>1.7</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -1368,7 +1363,7 @@
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 55562-2022</t>
+          <t>A 62831-2023</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1382,10 +1377,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>44888</v>
+        <v>45270</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1398,7 +1393,7 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>0.8</v>
+        <v>1.1</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -1441,7 +1436,7 @@
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 12077-2022</t>
+          <t>A 14149-2022</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1455,10 +1450,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>44636</v>
+        <v>44651</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1470,8 +1465,13 @@
           <t>HALLSTAHAMMAR</t>
         </is>
       </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I13" t="n">
-        <v>2.1</v>
+        <v>3.8</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
@@ -1514,7 +1514,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 37407-2023</t>
+          <t>A 34984-2024</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1528,10 +1528,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>45156</v>
+        <v>45527</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1544,7 +1544,7 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>3.3</v>
+        <v>4.1</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -1587,7 +1587,7 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 37072-2025</t>
+          <t>A 53343-2024</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1601,10 +1601,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>45875</v>
+        <v>45614</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1617,7 +1617,7 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>1.5</v>
+        <v>0.9</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -1660,7 +1660,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 37076-2025</t>
+          <t>A 22072-2023</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1674,10 +1674,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45875</v>
+        <v>45069</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1690,7 +1690,7 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>2.4</v>
+        <v>3.5</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -1733,7 +1733,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 13510-2025</t>
+          <t>A 42991-2025</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1747,10 +1747,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>45736</v>
+        <v>45909</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1763,7 +1763,7 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>2.5</v>
+        <v>7.2</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -1806,7 +1806,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 42991-2025</t>
+          <t>A 43448-2025</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1820,10 +1820,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>45909</v>
+        <v>45911</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -1836,7 +1836,7 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>7.2</v>
+        <v>1.2</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -1879,7 +1879,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 43448-2025</t>
+          <t>A 8848-2025</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1893,10 +1893,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>45911</v>
+        <v>45713</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -1909,7 +1909,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>1.2</v>
+        <v>2</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -1969,7 +1969,7 @@
         <v>45915</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2025,7 +2025,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 14149-2022</t>
+          <t>A 55562-2022</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2039,10 +2039,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>44651</v>
+        <v>44888</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2054,13 +2054,8 @@
           <t>HALLSTAHAMMAR</t>
         </is>
       </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I21" t="n">
-        <v>3.8</v>
+        <v>0.8</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2103,7 +2098,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 53343-2024</t>
+          <t>A 30766-2022</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2117,10 +2112,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>45614</v>
+        <v>44764</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2133,7 +2128,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>0.9</v>
+        <v>0.6</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2176,7 +2171,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 8848-2025</t>
+          <t>A 16762-2022</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2190,10 +2185,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>45713</v>
+        <v>44673</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2206,7 +2201,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>2</v>
+        <v>4.2</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2249,7 +2244,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 58109-2025</t>
+          <t>A 7245-2025</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2263,10 +2258,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45982</v>
+        <v>45702</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2279,7 +2274,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>2.5</v>
+        <v>4</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2322,7 +2317,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 58111-2025</t>
+          <t>A 37072-2025</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2336,10 +2331,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>45982</v>
+        <v>45875</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2352,7 +2347,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>0.6</v>
+        <v>1.5</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2395,7 +2390,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 58125-2025</t>
+          <t>A 37076-2025</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2409,10 +2404,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>45982</v>
+        <v>45875</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2425,7 +2420,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>0.8</v>
+        <v>2.4</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2468,7 +2463,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 8436-2023</t>
+          <t>A 58125-2025</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2482,10 +2477,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>44977</v>
+        <v>45982</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2497,13 +2492,8 @@
           <t>HALLSTAHAMMAR</t>
         </is>
       </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I27" t="n">
-        <v>4</v>
+        <v>0.8</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -2546,7 +2536,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 7245-2025</t>
+          <t>A 13510-2025</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2560,10 +2550,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>45702</v>
+        <v>45736</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2576,7 +2566,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>4</v>
+        <v>2.5</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -2619,7 +2609,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 1621-2026</t>
+          <t>A 58109-2025</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2633,10 +2623,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>46034</v>
+        <v>45982</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2649,7 +2639,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>1.4</v>
+        <v>2.5</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -2692,7 +2682,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 34984-2024</t>
+          <t>A 58111-2025</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2706,10 +2696,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>45527</v>
+        <v>45982</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -2722,7 +2712,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>4.1</v>
+        <v>0.6</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -2765,7 +2755,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 10069-2026</t>
+          <t>A 21972-2023</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2779,10 +2769,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>46073</v>
+        <v>45068</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -2794,13 +2784,8 @@
           <t>HALLSTAHAMMAR</t>
         </is>
       </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I31" t="n">
-        <v>13</v>
+        <v>1.5</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -2843,7 +2828,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 21049-2026</t>
+          <t>A 8436-2023</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2857,10 +2842,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>46146</v>
+        <v>44977</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -2872,8 +2857,13 @@
           <t>HALLSTAHAMMAR</t>
         </is>
       </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I32" t="n">
-        <v>2.9</v>
+        <v>4</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -2916,7 +2906,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 16762-2022</t>
+          <t>A 21264-2022</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2930,10 +2920,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>44673</v>
+        <v>44705</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -2945,8 +2935,13 @@
           <t>HALLSTAHAMMAR</t>
         </is>
       </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I33" t="n">
-        <v>4.2</v>
+        <v>2.4</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -2989,7 +2984,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 54207-2025</t>
+          <t>A 12077-2022</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3003,10 +2998,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>45964</v>
+        <v>44636</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3062,7 +3057,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 22072-2023</t>
+          <t>A 21049-2026</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3076,10 +3071,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>45069</v>
+        <v>46146</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3092,7 +3087,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>3.5</v>
+        <v>2.9</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3135,7 +3130,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 30766-2022</t>
+          <t>A 54207-2025</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3149,10 +3144,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>44764</v>
+        <v>45964</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3165,7 +3160,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>0.6</v>
+        <v>2.1</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3208,7 +3203,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 35036-2024</t>
+          <t>A 26059-2026</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3222,10 +3217,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45527</v>
+        <v>46181</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3238,7 +3233,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>1.7</v>
+        <v>4.7</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3281,7 +3276,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 26059-2026</t>
+          <t>A 26060-2026</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3298,7 +3293,7 @@
         <v>46181</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3311,7 +3306,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>4.7</v>
+        <v>3.6</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3354,7 +3349,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 26060-2026</t>
+          <t>A 37109-2026</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3368,10 +3363,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>46181</v>
+        <v>46274</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3384,7 +3379,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>3.6</v>
+        <v>3</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3427,7 +3422,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 62831-2023</t>
+          <t>A 35238-2026</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3437,14 +3432,14 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45270</v>
+        <v>46260</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3457,7 +3452,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>1.1</v>
+        <v>3.3</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -3500,7 +3495,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 37109-2026</t>
+          <t>A 41863-2026</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3514,10 +3509,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>46274</v>
+        <v>46303</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3530,7 +3525,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>3</v>
+        <v>1.9</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -3573,24 +3568,24 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 41863-2026</t>
+          <t>S 697-2026</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>avverkningsanmälan</t>
+          <t>samrådsanmälan</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Skogsgödsling</t>
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>46303</v>
+        <v>46091</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3603,7 +3598,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>1.9</v>
+        <v>32.5</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -3643,27 +3638,27 @@
       </c>
       <c r="V42" s="2" t="inlineStr"/>
     </row>
-    <row r="43" ht="15" customHeight="1">
+    <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 35238-2026</t>
+          <t>S 924-2026</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>avverkningsanmälan</t>
+          <t>samrådsanmälan</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Skogsgödsling</t>
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>46260</v>
+        <v>46111</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46304</v>
+        <v>46305</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -3675,8 +3670,13 @@
           <t>HALLSTAHAMMAR</t>
         </is>
       </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I43" t="n">
-        <v>3.3</v>
+        <v>48.8</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -3715,157 +3715,6 @@
         <v>0</v>
       </c>
       <c r="V43" s="2" t="inlineStr"/>
-    </row>
-    <row r="44" ht="15" customHeight="1">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>S 697-2026</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>samrådsanmälan</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>Skogsgödsling</t>
-        </is>
-      </c>
-      <c r="D44" s="1" t="n">
-        <v>46091</v>
-      </c>
-      <c r="E44" s="1" t="n">
-        <v>46304</v>
-      </c>
-      <c r="F44" t="inlineStr">
-        <is>
-          <t>VÄSTMANLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G44" t="inlineStr">
-        <is>
-          <t>HALLSTAHAMMAR</t>
-        </is>
-      </c>
-      <c r="I44" t="n">
-        <v>32.5</v>
-      </c>
-      <c r="J44" t="n">
-        <v>0</v>
-      </c>
-      <c r="K44" t="n">
-        <v>0</v>
-      </c>
-      <c r="L44" t="n">
-        <v>0</v>
-      </c>
-      <c r="M44" t="n">
-        <v>0</v>
-      </c>
-      <c r="N44" t="n">
-        <v>0</v>
-      </c>
-      <c r="O44" t="n">
-        <v>0</v>
-      </c>
-      <c r="P44" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q44" t="n">
-        <v>0</v>
-      </c>
-      <c r="R44" t="n">
-        <v>0</v>
-      </c>
-      <c r="S44" t="n">
-        <v>0</v>
-      </c>
-      <c r="T44" t="n">
-        <v>0</v>
-      </c>
-      <c r="U44" t="n">
-        <v>0</v>
-      </c>
-      <c r="V44" s="2" t="inlineStr"/>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>S 924-2026</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>samrådsanmälan</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>Skogsgödsling</t>
-        </is>
-      </c>
-      <c r="D45" s="1" t="n">
-        <v>46111</v>
-      </c>
-      <c r="E45" s="1" t="n">
-        <v>46304</v>
-      </c>
-      <c r="F45" t="inlineStr">
-        <is>
-          <t>VÄSTMANLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G45" t="inlineStr">
-        <is>
-          <t>HALLSTAHAMMAR</t>
-        </is>
-      </c>
-      <c r="H45" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
-      <c r="I45" t="n">
-        <v>48.8</v>
-      </c>
-      <c r="J45" t="n">
-        <v>0</v>
-      </c>
-      <c r="K45" t="n">
-        <v>0</v>
-      </c>
-      <c r="L45" t="n">
-        <v>0</v>
-      </c>
-      <c r="M45" t="n">
-        <v>0</v>
-      </c>
-      <c r="N45" t="n">
-        <v>0</v>
-      </c>
-      <c r="O45" t="n">
-        <v>0</v>
-      </c>
-      <c r="P45" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q45" t="n">
-        <v>0</v>
-      </c>
-      <c r="R45" t="n">
-        <v>0</v>
-      </c>
-      <c r="S45" t="n">
-        <v>0</v>
-      </c>
-      <c r="T45" t="n">
-        <v>0</v>
-      </c>
-      <c r="U45" t="n">
-        <v>0</v>
-      </c>
-      <c r="V45" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Översikt HALLSTAHAMMAR.xlsx
+++ b/Översikt HALLSTAHAMMAR.xlsx
@@ -601,7 +601,7 @@
         <v>45978</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -713,7 +713,7 @@
         <v>44635</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -791,7 +791,7 @@
         <v>44887</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -864,7 +864,7 @@
         <v>44502</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -937,7 +937,7 @@
         <v>44739</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1010,7 +1010,7 @@
         <v>44502</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1083,7 +1083,7 @@
         <v>44502</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1156,7 +1156,7 @@
         <v>45365</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1234,7 +1234,7 @@
         <v>45156</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1307,7 +1307,7 @@
         <v>45527</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1380,7 +1380,7 @@
         <v>45270</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1453,7 +1453,7 @@
         <v>44651</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1531,7 +1531,7 @@
         <v>45527</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1604,7 +1604,7 @@
         <v>45614</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1677,7 +1677,7 @@
         <v>45069</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1750,7 +1750,7 @@
         <v>45909</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1823,7 +1823,7 @@
         <v>45911</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -1896,7 +1896,7 @@
         <v>45713</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -1969,7 +1969,7 @@
         <v>45915</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2042,7 +2042,7 @@
         <v>44888</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2115,7 +2115,7 @@
         <v>44764</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2188,7 +2188,7 @@
         <v>44673</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2261,7 +2261,7 @@
         <v>45702</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2334,7 +2334,7 @@
         <v>45875</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2407,7 +2407,7 @@
         <v>45875</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2480,7 +2480,7 @@
         <v>45982</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2553,7 +2553,7 @@
         <v>45736</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2626,7 +2626,7 @@
         <v>45982</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2699,7 +2699,7 @@
         <v>45982</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -2772,7 +2772,7 @@
         <v>45068</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -2845,7 +2845,7 @@
         <v>44977</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -2923,7 +2923,7 @@
         <v>44705</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3001,7 +3001,7 @@
         <v>44636</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3074,7 +3074,7 @@
         <v>46146</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3147,7 +3147,7 @@
         <v>45964</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3220,7 +3220,7 @@
         <v>46181</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3293,7 +3293,7 @@
         <v>46181</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3366,7 +3366,7 @@
         <v>46274</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3439,7 +3439,7 @@
         <v>46260</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3512,7 +3512,7 @@
         <v>46303</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3585,7 +3585,7 @@
         <v>46091</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3658,7 +3658,7 @@
         <v>46111</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>

--- a/Översikt HALLSTAHAMMAR.xlsx
+++ b/Översikt HALLSTAHAMMAR.xlsx
@@ -601,7 +601,7 @@
         <v>45978</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -713,7 +713,7 @@
         <v>44635</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -791,7 +791,7 @@
         <v>44887</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -864,7 +864,7 @@
         <v>44502</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -937,7 +937,7 @@
         <v>44739</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1010,7 +1010,7 @@
         <v>44502</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1083,7 +1083,7 @@
         <v>44502</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1156,7 +1156,7 @@
         <v>45365</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1234,7 +1234,7 @@
         <v>45156</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1307,7 +1307,7 @@
         <v>45527</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1380,7 +1380,7 @@
         <v>45270</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1453,7 +1453,7 @@
         <v>44651</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1531,7 +1531,7 @@
         <v>45527</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1604,7 +1604,7 @@
         <v>45614</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1677,7 +1677,7 @@
         <v>45069</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1750,7 +1750,7 @@
         <v>45909</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1823,7 +1823,7 @@
         <v>45911</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -1896,7 +1896,7 @@
         <v>45713</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -1969,7 +1969,7 @@
         <v>45915</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2042,7 +2042,7 @@
         <v>44888</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2115,7 +2115,7 @@
         <v>44764</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2188,7 +2188,7 @@
         <v>44673</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2261,7 +2261,7 @@
         <v>45702</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2334,7 +2334,7 @@
         <v>45875</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2407,7 +2407,7 @@
         <v>45875</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2480,7 +2480,7 @@
         <v>45982</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2553,7 +2553,7 @@
         <v>45736</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2626,7 +2626,7 @@
         <v>45982</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2699,7 +2699,7 @@
         <v>45982</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -2772,7 +2772,7 @@
         <v>45068</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -2845,7 +2845,7 @@
         <v>44977</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -2923,7 +2923,7 @@
         <v>44705</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3001,7 +3001,7 @@
         <v>44636</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3074,7 +3074,7 @@
         <v>46146</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3147,7 +3147,7 @@
         <v>45964</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3220,7 +3220,7 @@
         <v>46181</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3293,7 +3293,7 @@
         <v>46181</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3366,7 +3366,7 @@
         <v>46274</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3439,7 +3439,7 @@
         <v>46260</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3512,7 +3512,7 @@
         <v>46303</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3585,7 +3585,7 @@
         <v>46091</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3658,7 +3658,7 @@
         <v>46111</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>

--- a/Översikt HALLSTAHAMMAR.xlsx
+++ b/Översikt HALLSTAHAMMAR.xlsx
@@ -601,7 +601,7 @@
         <v>45978</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -713,7 +713,7 @@
         <v>44635</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -791,7 +791,7 @@
         <v>44887</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -864,7 +864,7 @@
         <v>44502</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -920,7 +920,7 @@
     <row r="6" ht="15" customHeight="1">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A 26702-2022</t>
+          <t>A 68624-2021</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -934,10 +934,10 @@
         </is>
       </c>
       <c r="D6" s="1" t="n">
-        <v>44739</v>
+        <v>44502</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -950,7 +950,7 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>3.8</v>
+        <v>5.5</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
@@ -993,7 +993,7 @@
     <row r="7" ht="15" customHeight="1">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A 68624-2021</t>
+          <t>A 26702-2022</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1007,10 +1007,10 @@
         </is>
       </c>
       <c r="D7" s="1" t="n">
-        <v>44502</v>
+        <v>44739</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1023,7 +1023,7 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>5.5</v>
+        <v>3.8</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
@@ -1083,7 +1083,7 @@
         <v>44502</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1139,7 +1139,7 @@
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 10263-2024</t>
+          <t>A 21264-2022</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1153,10 +1153,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>45365</v>
+        <v>44705</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1170,11 +1170,11 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Kyrkan</t>
+          <t>Allmännings- och besparingsskogar</t>
         </is>
       </c>
       <c r="I9" t="n">
-        <v>1.4</v>
+        <v>2.4</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -1217,7 +1217,7 @@
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 37407-2023</t>
+          <t>A 42991-2025</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1231,10 +1231,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>45156</v>
+        <v>45909</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1247,7 +1247,7 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>3.3</v>
+        <v>7.2</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
@@ -1290,7 +1290,7 @@
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 35036-2024</t>
+          <t>A 43448-2025</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1304,10 +1304,10 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>45527</v>
+        <v>45911</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1320,7 +1320,7 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>1.7</v>
+        <v>1.2</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -1363,7 +1363,7 @@
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 62831-2023</t>
+          <t>A 44192-2025</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1377,10 +1377,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>45270</v>
+        <v>45915</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1393,7 +1393,7 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>1.1</v>
+        <v>0.8</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -1436,7 +1436,7 @@
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 14149-2022</t>
+          <t>A 21972-2023</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1450,10 +1450,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>44651</v>
+        <v>45068</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1465,13 +1465,8 @@
           <t>HALLSTAHAMMAR</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I13" t="n">
-        <v>3.8</v>
+        <v>1.5</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
@@ -1514,7 +1509,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 34984-2024</t>
+          <t>A 62831-2023</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1528,10 +1523,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>45527</v>
+        <v>45270</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1544,7 +1539,7 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>4.1</v>
+        <v>1.1</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -1587,7 +1582,7 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 53343-2024</t>
+          <t>A 26059-2026</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1601,10 +1596,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>45614</v>
+        <v>46181</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1617,7 +1612,7 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>0.9</v>
+        <v>4.7</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -1660,7 +1655,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 22072-2023</t>
+          <t>A 26060-2026</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1674,10 +1669,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45069</v>
+        <v>46181</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1690,7 +1685,7 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -1733,7 +1728,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 42991-2025</t>
+          <t>A 58109-2025</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1747,10 +1742,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>45909</v>
+        <v>45982</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1763,7 +1758,7 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>7.2</v>
+        <v>2.5</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -1806,7 +1801,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 43448-2025</t>
+          <t>A 58111-2025</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1820,10 +1815,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>45911</v>
+        <v>45982</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -1836,7 +1831,7 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>1.2</v>
+        <v>0.6</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -1879,7 +1874,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 8848-2025</t>
+          <t>A 58125-2025</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1893,10 +1888,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>45713</v>
+        <v>45982</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -1909,7 +1904,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>2</v>
+        <v>0.8</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -1952,7 +1947,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 44192-2025</t>
+          <t>A 37109-2026</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1966,10 +1961,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>45915</v>
+        <v>46274</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -1982,7 +1977,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>0.8</v>
+        <v>3</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2025,7 +2020,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 55562-2022</t>
+          <t>A 37072-2025</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2039,10 +2034,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>44888</v>
+        <v>45875</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2055,7 +2050,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>0.8</v>
+        <v>1.5</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2098,7 +2093,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 30766-2022</t>
+          <t>A 37076-2025</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2112,10 +2107,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>44764</v>
+        <v>45875</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2128,7 +2123,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>0.6</v>
+        <v>2.4</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2171,7 +2166,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 16762-2022</t>
+          <t>A 13510-2025</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2185,10 +2180,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>44673</v>
+        <v>45736</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2201,7 +2196,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>4.2</v>
+        <v>2.5</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2244,7 +2239,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 7245-2025</t>
+          <t>A 10263-2024</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2258,10 +2253,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45702</v>
+        <v>45365</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2273,8 +2268,13 @@
           <t>HALLSTAHAMMAR</t>
         </is>
       </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I24" t="n">
-        <v>4</v>
+        <v>1.4</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2317,7 +2317,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 37072-2025</t>
+          <t>A 55562-2022</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2331,10 +2331,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>45875</v>
+        <v>44888</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2347,7 +2347,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>1.5</v>
+        <v>0.8</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2390,7 +2390,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 37076-2025</t>
+          <t>A 41863-2026</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2404,10 +2404,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>45875</v>
+        <v>46303</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2420,7 +2420,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>2.4</v>
+        <v>1.9</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2463,7 +2463,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 58125-2025</t>
+          <t>A 35238-2026</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2473,14 +2473,14 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>45982</v>
+        <v>46260</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2493,7 +2493,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>0.8</v>
+        <v>3.3</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -2536,7 +2536,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 13510-2025</t>
+          <t>A 12077-2022</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2550,10 +2550,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>45736</v>
+        <v>44636</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2566,7 +2566,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>2.5</v>
+        <v>2.1</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -2609,7 +2609,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 58109-2025</t>
+          <t>A 37407-2023</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2623,10 +2623,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>45982</v>
+        <v>45156</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2639,7 +2639,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>2.5</v>
+        <v>3.3</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -2682,7 +2682,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 58111-2025</t>
+          <t>A 21049-2026</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2696,10 +2696,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>45982</v>
+        <v>46146</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -2712,7 +2712,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>0.6</v>
+        <v>2.9</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -2755,7 +2755,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 21972-2023</t>
+          <t>A 54207-2025</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2769,10 +2769,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45068</v>
+        <v>45964</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -2785,7 +2785,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>1.5</v>
+        <v>2.1</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -2828,7 +2828,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 8436-2023</t>
+          <t>A 14149-2022</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2842,10 +2842,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>44977</v>
+        <v>44651</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -2859,11 +2859,11 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Kyrkan</t>
+          <t>Allmännings- och besparingsskogar</t>
         </is>
       </c>
       <c r="I32" t="n">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -2906,7 +2906,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 21264-2022</t>
+          <t>A 53343-2024</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2920,10 +2920,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>44705</v>
+        <v>45614</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -2935,13 +2935,8 @@
           <t>HALLSTAHAMMAR</t>
         </is>
       </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I33" t="n">
-        <v>2.4</v>
+        <v>0.9</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -2984,7 +2979,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 12077-2022</t>
+          <t>A 8848-2025</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2998,10 +2993,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>44636</v>
+        <v>45713</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3014,7 +3009,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3057,7 +3052,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 21049-2026</t>
+          <t>A 8436-2023</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3071,10 +3066,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>46146</v>
+        <v>44977</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3086,8 +3081,13 @@
           <t>HALLSTAHAMMAR</t>
         </is>
       </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I35" t="n">
-        <v>2.9</v>
+        <v>4</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3130,7 +3130,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 54207-2025</t>
+          <t>A 7245-2025</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3144,10 +3144,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45964</v>
+        <v>45702</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3160,7 +3160,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>2.1</v>
+        <v>4</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3203,7 +3203,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 26059-2026</t>
+          <t>A 34984-2024</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3217,10 +3217,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>46181</v>
+        <v>45527</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3233,7 +3233,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>4.7</v>
+        <v>4.1</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3276,7 +3276,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 26060-2026</t>
+          <t>A 16762-2022</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3290,10 +3290,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>46181</v>
+        <v>44673</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3306,7 +3306,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>3.6</v>
+        <v>4.2</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3349,7 +3349,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 37109-2026</t>
+          <t>A 22072-2023</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3363,10 +3363,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>46274</v>
+        <v>45069</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3379,7 +3379,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3422,7 +3422,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 35238-2026</t>
+          <t>A 30766-2022</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3432,14 +3432,14 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>46260</v>
+        <v>44764</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3452,7 +3452,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>3.3</v>
+        <v>0.6</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -3495,7 +3495,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 41863-2026</t>
+          <t>A 35036-2024</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3509,10 +3509,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>46303</v>
+        <v>45527</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3525,7 +3525,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>1.9</v>
+        <v>1.7</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -3585,7 +3585,7 @@
         <v>46091</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3658,7 +3658,7 @@
         <v>46111</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>

--- a/Översikt HALLSTAHAMMAR.xlsx
+++ b/Översikt HALLSTAHAMMAR.xlsx
@@ -601,7 +601,7 @@
         <v>45978</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -713,7 +713,7 @@
         <v>44635</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -791,7 +791,7 @@
         <v>44887</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -864,7 +864,7 @@
         <v>44502</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -937,7 +937,7 @@
         <v>44502</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1010,7 +1010,7 @@
         <v>44739</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1083,7 +1083,7 @@
         <v>44502</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1139,7 +1139,7 @@
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 21264-2022</t>
+          <t>A 10263-2024</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1153,10 +1153,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>44705</v>
+        <v>45365</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1170,11 +1170,11 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Allmännings- och besparingsskogar</t>
+          <t>Kyrkan</t>
         </is>
       </c>
       <c r="I9" t="n">
-        <v>2.4</v>
+        <v>1.4</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -1217,7 +1217,7 @@
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 42991-2025</t>
+          <t>A 34984-2024</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1231,10 +1231,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>45909</v>
+        <v>45527</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1247,7 +1247,7 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>7.2</v>
+        <v>4.1</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
@@ -1290,7 +1290,7 @@
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 43448-2025</t>
+          <t>A 22072-2023</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1304,10 +1304,10 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>45911</v>
+        <v>45069</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1320,7 +1320,7 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>1.2</v>
+        <v>3.5</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -1363,7 +1363,7 @@
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 44192-2025</t>
+          <t>A 42991-2025</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1377,10 +1377,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>45915</v>
+        <v>45909</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1393,7 +1393,7 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>0.8</v>
+        <v>7.2</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -1436,7 +1436,7 @@
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 21972-2023</t>
+          <t>A 43448-2025</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1450,10 +1450,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>45068</v>
+        <v>45911</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1466,7 +1466,7 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>1.5</v>
+        <v>1.2</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
@@ -1509,7 +1509,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 62831-2023</t>
+          <t>A 44192-2025</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1523,10 +1523,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>45270</v>
+        <v>45915</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1539,7 +1539,7 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>1.1</v>
+        <v>0.8</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -1582,7 +1582,7 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 26059-2026</t>
+          <t>A 55562-2022</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1596,10 +1596,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>46181</v>
+        <v>44888</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1612,7 +1612,7 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>4.7</v>
+        <v>0.8</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -1655,7 +1655,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 26060-2026</t>
+          <t>A 37072-2025</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1669,10 +1669,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>46181</v>
+        <v>45875</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1685,7 +1685,7 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>3.6</v>
+        <v>1.5</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -1728,7 +1728,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 58109-2025</t>
+          <t>A 37076-2025</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1742,10 +1742,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>45982</v>
+        <v>45875</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1758,7 +1758,7 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -1801,7 +1801,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 58111-2025</t>
+          <t>A 13510-2025</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1815,10 +1815,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>45982</v>
+        <v>45736</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -1831,7 +1831,7 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>0.6</v>
+        <v>2.5</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -1874,7 +1874,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 58125-2025</t>
+          <t>A 16762-2022</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1888,10 +1888,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>45982</v>
+        <v>44673</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -1904,7 +1904,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>0.8</v>
+        <v>4.2</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -1947,7 +1947,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 37109-2026</t>
+          <t>A 58125-2025</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1961,10 +1961,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>46274</v>
+        <v>45982</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -1977,7 +1977,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>3</v>
+        <v>0.8</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2020,7 +2020,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 37072-2025</t>
+          <t>A 58109-2025</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2034,10 +2034,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>45875</v>
+        <v>45982</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2050,7 +2050,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>1.5</v>
+        <v>2.5</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2093,7 +2093,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 37076-2025</t>
+          <t>A 58111-2025</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2107,10 +2107,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>45875</v>
+        <v>45982</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2123,7 +2123,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>2.4</v>
+        <v>0.6</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2166,7 +2166,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 13510-2025</t>
+          <t>A 21972-2023</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2180,10 +2180,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>45736</v>
+        <v>45068</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2196,7 +2196,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>2.5</v>
+        <v>1.5</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2239,7 +2239,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 10263-2024</t>
+          <t>A 35036-2024</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2253,10 +2253,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45365</v>
+        <v>45527</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2268,13 +2268,8 @@
           <t>HALLSTAHAMMAR</t>
         </is>
       </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I24" t="n">
-        <v>1.4</v>
+        <v>1.7</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2317,7 +2312,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 55562-2022</t>
+          <t>A 62831-2023</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2331,10 +2326,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>44888</v>
+        <v>45270</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2347,7 +2342,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>0.8</v>
+        <v>1.1</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2390,7 +2385,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 41863-2026</t>
+          <t>A 8848-2025</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2404,10 +2399,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>46303</v>
+        <v>45713</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2420,7 +2415,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2463,7 +2458,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 35238-2026</t>
+          <t>A 21049-2026</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2473,14 +2468,14 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>46260</v>
+        <v>46146</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2493,7 +2488,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>3.3</v>
+        <v>2.9</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -2536,7 +2531,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 12077-2022</t>
+          <t>A 54207-2025</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2550,10 +2545,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>44636</v>
+        <v>45964</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2609,7 +2604,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 37407-2023</t>
+          <t>A 30766-2022</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2623,10 +2618,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>45156</v>
+        <v>44764</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2639,7 +2634,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>3.3</v>
+        <v>0.6</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -2682,7 +2677,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 21049-2026</t>
+          <t>A 7245-2025</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2696,10 +2691,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>46146</v>
+        <v>45702</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -2712,7 +2707,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>2.9</v>
+        <v>4</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -2755,7 +2750,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 54207-2025</t>
+          <t>A 26059-2026</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2769,10 +2764,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45964</v>
+        <v>46181</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -2785,7 +2780,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>2.1</v>
+        <v>4.7</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -2828,7 +2823,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 14149-2022</t>
+          <t>A 26060-2026</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2842,10 +2837,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>44651</v>
+        <v>46181</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -2857,13 +2852,8 @@
           <t>HALLSTAHAMMAR</t>
         </is>
       </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I32" t="n">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -2906,7 +2896,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 53343-2024</t>
+          <t>A 8436-2023</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2920,10 +2910,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>45614</v>
+        <v>44977</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -2935,8 +2925,13 @@
           <t>HALLSTAHAMMAR</t>
         </is>
       </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I33" t="n">
-        <v>0.9</v>
+        <v>4</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -2979,7 +2974,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 8848-2025</t>
+          <t>A 21264-2022</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2993,10 +2988,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>45713</v>
+        <v>44705</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3008,8 +3003,13 @@
           <t>HALLSTAHAMMAR</t>
         </is>
       </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I34" t="n">
-        <v>2</v>
+        <v>2.4</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3052,7 +3052,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 8436-2023</t>
+          <t>A 12077-2022</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3066,10 +3066,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>44977</v>
+        <v>44636</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3081,13 +3081,8 @@
           <t>HALLSTAHAMMAR</t>
         </is>
       </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I35" t="n">
-        <v>4</v>
+        <v>2.1</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3130,7 +3125,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 7245-2025</t>
+          <t>A 37407-2023</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3144,10 +3139,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45702</v>
+        <v>45156</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3160,7 +3155,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>4</v>
+        <v>3.3</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3203,7 +3198,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 34984-2024</t>
+          <t>A 37109-2026</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3217,10 +3212,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45527</v>
+        <v>46274</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3233,7 +3228,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>4.1</v>
+        <v>3</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3276,7 +3271,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 16762-2022</t>
+          <t>A 14149-2022</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3290,10 +3285,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>44673</v>
+        <v>44651</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3305,8 +3300,13 @@
           <t>HALLSTAHAMMAR</t>
         </is>
       </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I38" t="n">
-        <v>4.2</v>
+        <v>3.8</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3349,7 +3349,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 22072-2023</t>
+          <t>A 53343-2024</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3363,10 +3363,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45069</v>
+        <v>45614</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3379,7 +3379,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>3.5</v>
+        <v>0.9</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3422,7 +3422,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 30766-2022</t>
+          <t>A 35238-2026</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3432,14 +3432,14 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>44764</v>
+        <v>46260</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3452,7 +3452,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>0.6</v>
+        <v>3.3</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -3495,7 +3495,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 35036-2024</t>
+          <t>A 41863-2026</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3509,10 +3509,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45527</v>
+        <v>46303</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3525,7 +3525,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>1.7</v>
+        <v>1.9</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -3585,7 +3585,7 @@
         <v>46091</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3658,7 +3658,7 @@
         <v>46111</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46308</v>
+        <v>46309</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>

--- a/Översikt HALLSTAHAMMAR.xlsx
+++ b/Översikt HALLSTAHAMMAR.xlsx
@@ -601,7 +601,7 @@
         <v>45978</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -713,7 +713,7 @@
         <v>44635</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -791,7 +791,7 @@
         <v>44887</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -864,7 +864,7 @@
         <v>44502</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -937,7 +937,7 @@
         <v>44502</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1010,7 +1010,7 @@
         <v>44739</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1083,7 +1083,7 @@
         <v>44502</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1139,7 +1139,7 @@
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 10263-2024</t>
+          <t>A 21264-2022</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1153,10 +1153,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>45365</v>
+        <v>44705</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1170,11 +1170,11 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Kyrkan</t>
+          <t>Allmännings- och besparingsskogar</t>
         </is>
       </c>
       <c r="I9" t="n">
-        <v>1.4</v>
+        <v>2.4</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -1217,7 +1217,7 @@
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 34984-2024</t>
+          <t>A 21972-2023</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1231,10 +1231,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>45527</v>
+        <v>45068</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1247,7 +1247,7 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>4.1</v>
+        <v>1.5</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
@@ -1290,7 +1290,7 @@
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 22072-2023</t>
+          <t>A 14149-2022</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1304,10 +1304,10 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>45069</v>
+        <v>44651</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1319,8 +1319,13 @@
           <t>HALLSTAHAMMAR</t>
         </is>
       </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I11" t="n">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -1363,7 +1368,7 @@
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 42991-2025</t>
+          <t>A 53343-2024</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1377,10 +1382,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>45909</v>
+        <v>45614</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1393,7 +1398,7 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>7.2</v>
+        <v>0.9</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -1436,7 +1441,7 @@
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 43448-2025</t>
+          <t>A 8848-2025</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1450,10 +1455,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>45911</v>
+        <v>45713</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1466,7 +1471,7 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>1.2</v>
+        <v>2</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
@@ -1509,7 +1514,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 44192-2025</t>
+          <t>A 42991-2025</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1523,10 +1528,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>45915</v>
+        <v>45909</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1539,7 +1544,7 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>0.8</v>
+        <v>7.2</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -1582,7 +1587,7 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 55562-2022</t>
+          <t>A 43448-2025</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1596,10 +1601,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>44888</v>
+        <v>45911</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1612,7 +1617,7 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>0.8</v>
+        <v>1.2</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -1672,7 +1677,7 @@
         <v>45875</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1745,7 +1750,7 @@
         <v>45875</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1801,7 +1806,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 13510-2025</t>
+          <t>A 44192-2025</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1815,10 +1820,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>45736</v>
+        <v>45915</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -1831,7 +1836,7 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>2.5</v>
+        <v>0.8</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -1874,7 +1879,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 16762-2022</t>
+          <t>A 10263-2024</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1888,10 +1893,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>44673</v>
+        <v>45365</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -1903,8 +1908,13 @@
           <t>HALLSTAHAMMAR</t>
         </is>
       </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I19" t="n">
-        <v>4.2</v>
+        <v>1.4</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -1947,7 +1957,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 58125-2025</t>
+          <t>A 13510-2025</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1961,10 +1971,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>45982</v>
+        <v>45736</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -1977,7 +1987,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>0.8</v>
+        <v>2.5</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2020,7 +2030,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 58109-2025</t>
+          <t>A 55562-2022</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2034,10 +2044,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>45982</v>
+        <v>44888</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2050,7 +2060,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>2.5</v>
+        <v>0.8</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2093,7 +2103,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 58111-2025</t>
+          <t>A 8436-2023</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2107,10 +2117,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>45982</v>
+        <v>44977</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2122,8 +2132,13 @@
           <t>HALLSTAHAMMAR</t>
         </is>
       </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I22" t="n">
-        <v>0.6</v>
+        <v>4</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2166,7 +2181,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 21972-2023</t>
+          <t>A 12077-2022</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2180,10 +2195,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>45068</v>
+        <v>44636</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2196,7 +2211,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>1.5</v>
+        <v>2.1</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2239,7 +2254,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 35036-2024</t>
+          <t>A 58109-2025</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2253,10 +2268,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45527</v>
+        <v>45982</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2269,7 +2284,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>1.7</v>
+        <v>2.5</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2312,7 +2327,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 62831-2023</t>
+          <t>A 58111-2025</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2326,10 +2341,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>45270</v>
+        <v>45982</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2342,7 +2357,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>1.1</v>
+        <v>0.6</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2385,7 +2400,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 8848-2025</t>
+          <t>A 37407-2023</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2399,10 +2414,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>45713</v>
+        <v>45156</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2415,7 +2430,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>2</v>
+        <v>3.3</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2458,7 +2473,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 21049-2026</t>
+          <t>A 58125-2025</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2472,10 +2487,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>46146</v>
+        <v>45982</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2488,7 +2503,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>2.9</v>
+        <v>0.8</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -2531,7 +2546,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 54207-2025</t>
+          <t>A 7245-2025</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2545,10 +2560,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>45964</v>
+        <v>45702</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2561,7 +2576,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>2.1</v>
+        <v>4</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -2604,7 +2619,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 30766-2022</t>
+          <t>A 21049-2026</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2618,10 +2633,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>44764</v>
+        <v>46146</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2634,7 +2649,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>0.6</v>
+        <v>2.9</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -2677,7 +2692,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 7245-2025</t>
+          <t>A 34984-2024</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2691,10 +2706,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>45702</v>
+        <v>45527</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -2707,7 +2722,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -2750,7 +2765,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 26059-2026</t>
+          <t>A 54207-2025</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2764,10 +2779,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>46181</v>
+        <v>45964</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -2780,7 +2795,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>4.7</v>
+        <v>2.1</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -2823,7 +2838,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 26060-2026</t>
+          <t>A 16762-2022</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2837,10 +2852,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>46181</v>
+        <v>44673</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -2853,7 +2868,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>3.6</v>
+        <v>4.2</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -2896,7 +2911,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 8436-2023</t>
+          <t>A 22072-2023</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2910,10 +2925,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>44977</v>
+        <v>45069</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -2925,13 +2940,8 @@
           <t>HALLSTAHAMMAR</t>
         </is>
       </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I33" t="n">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -2974,7 +2984,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 21264-2022</t>
+          <t>A 26059-2026</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2988,10 +2998,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>44705</v>
+        <v>46181</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3003,13 +3013,8 @@
           <t>HALLSTAHAMMAR</t>
         </is>
       </c>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I34" t="n">
-        <v>2.4</v>
+        <v>4.7</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3052,7 +3057,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 12077-2022</t>
+          <t>A 26060-2026</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3066,10 +3071,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>44636</v>
+        <v>46181</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3082,7 +3087,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>2.1</v>
+        <v>3.6</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3125,7 +3130,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 37407-2023</t>
+          <t>A 30766-2022</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3139,10 +3144,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45156</v>
+        <v>44764</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3155,7 +3160,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>3.3</v>
+        <v>0.6</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3198,7 +3203,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 37109-2026</t>
+          <t>A 35036-2024</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3212,10 +3217,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>46274</v>
+        <v>45527</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3228,7 +3233,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>3</v>
+        <v>1.7</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3271,7 +3276,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 14149-2022</t>
+          <t>A 37109-2026</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3285,10 +3290,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>44651</v>
+        <v>46274</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3300,13 +3305,8 @@
           <t>HALLSTAHAMMAR</t>
         </is>
       </c>
-      <c r="H38" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I38" t="n">
-        <v>3.8</v>
+        <v>3</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3349,7 +3349,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 53343-2024</t>
+          <t>A 62831-2023</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3363,10 +3363,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45614</v>
+        <v>45270</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3379,7 +3379,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>0.9</v>
+        <v>1.1</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3439,7 +3439,7 @@
         <v>46260</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3512,7 +3512,7 @@
         <v>46303</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3585,7 +3585,7 @@
         <v>46091</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3658,7 +3658,7 @@
         <v>46111</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46309</v>
+        <v>46310</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>

--- a/Översikt HALLSTAHAMMAR.xlsx
+++ b/Översikt HALLSTAHAMMAR.xlsx
@@ -601,7 +601,7 @@
         <v>45978</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -713,7 +713,7 @@
         <v>44635</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -791,7 +791,7 @@
         <v>44887</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -864,7 +864,7 @@
         <v>44502</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -937,7 +937,7 @@
         <v>44502</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1010,7 +1010,7 @@
         <v>44739</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1083,7 +1083,7 @@
         <v>44502</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1139,7 +1139,7 @@
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 21264-2022</t>
+          <t>A 21972-2023</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1153,10 +1153,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>44705</v>
+        <v>45068</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1168,13 +1168,8 @@
           <t>HALLSTAHAMMAR</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I9" t="n">
-        <v>2.4</v>
+        <v>1.5</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -1217,7 +1212,7 @@
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 21972-2023</t>
+          <t>A 10263-2024</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1231,10 +1226,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>45068</v>
+        <v>45365</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1246,8 +1241,13 @@
           <t>HALLSTAHAMMAR</t>
         </is>
       </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I10" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
@@ -1290,7 +1290,7 @@
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 14149-2022</t>
+          <t>A 34984-2024</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1304,10 +1304,10 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>44651</v>
+        <v>45527</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1319,13 +1319,8 @@
           <t>HALLSTAHAMMAR</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I11" t="n">
-        <v>3.8</v>
+        <v>4.1</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -1368,7 +1363,7 @@
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 53343-2024</t>
+          <t>A 35036-2024</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1382,10 +1377,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>45614</v>
+        <v>45527</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1398,7 +1393,7 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>0.9</v>
+        <v>1.7</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -1441,7 +1436,7 @@
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 8848-2025</t>
+          <t>A 62831-2023</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1455,10 +1450,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>45713</v>
+        <v>45270</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1471,7 +1466,7 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>2</v>
+        <v>1.1</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
@@ -1514,7 +1509,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 42991-2025</t>
+          <t>A 37072-2025</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1528,10 +1523,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>45909</v>
+        <v>45875</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1544,7 +1539,7 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>7.2</v>
+        <v>1.5</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -1587,7 +1582,7 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 43448-2025</t>
+          <t>A 37076-2025</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1601,10 +1596,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>45911</v>
+        <v>45875</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1617,7 +1612,7 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>1.2</v>
+        <v>2.4</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -1660,7 +1655,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 37072-2025</t>
+          <t>A 13510-2025</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1674,10 +1669,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45875</v>
+        <v>45736</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1690,7 +1685,7 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>1.5</v>
+        <v>2.5</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -1733,7 +1728,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 37076-2025</t>
+          <t>A 22072-2023</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1747,10 +1742,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>45875</v>
+        <v>45069</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1763,7 +1758,7 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>2.4</v>
+        <v>3.5</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -1806,7 +1801,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 44192-2025</t>
+          <t>A 8848-2025</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1820,10 +1815,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>45915</v>
+        <v>45713</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -1836,7 +1831,7 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>0.8</v>
+        <v>2</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -1879,7 +1874,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 10263-2024</t>
+          <t>A 55562-2022</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1893,10 +1888,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>45365</v>
+        <v>44888</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -1908,13 +1903,8 @@
           <t>HALLSTAHAMMAR</t>
         </is>
       </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I19" t="n">
-        <v>1.4</v>
+        <v>0.8</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -1957,7 +1947,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 13510-2025</t>
+          <t>A 16762-2022</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1971,10 +1961,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>45736</v>
+        <v>44673</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -1987,7 +1977,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>2.5</v>
+        <v>4.2</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2030,7 +2020,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 55562-2022</t>
+          <t>A 30766-2022</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2044,10 +2034,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>44888</v>
+        <v>44764</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2060,7 +2050,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2103,7 +2093,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 8436-2023</t>
+          <t>A 42991-2025</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2117,10 +2107,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>44977</v>
+        <v>45909</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2132,13 +2122,8 @@
           <t>HALLSTAHAMMAR</t>
         </is>
       </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I22" t="n">
-        <v>4</v>
+        <v>7.2</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2181,7 +2166,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 12077-2022</t>
+          <t>A 43448-2025</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2195,10 +2180,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>44636</v>
+        <v>45911</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2211,7 +2196,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>2.1</v>
+        <v>1.2</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2254,7 +2239,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 58109-2025</t>
+          <t>A 7245-2025</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2268,10 +2253,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45982</v>
+        <v>45702</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2284,7 +2269,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>2.5</v>
+        <v>4</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2327,7 +2312,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 58111-2025</t>
+          <t>A 21049-2026</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2341,10 +2326,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>45982</v>
+        <v>46146</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2357,7 +2342,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>0.6</v>
+        <v>2.9</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2400,7 +2385,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 37407-2023</t>
+          <t>A 44192-2025</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2414,10 +2399,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>45156</v>
+        <v>45915</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2430,7 +2415,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>3.3</v>
+        <v>0.8</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2473,7 +2458,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 58125-2025</t>
+          <t>A 54207-2025</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2487,10 +2472,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>45982</v>
+        <v>45964</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2503,7 +2488,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>0.8</v>
+        <v>2.1</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -2546,7 +2531,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 7245-2025</t>
+          <t>A 8436-2023</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2560,10 +2545,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>45702</v>
+        <v>44977</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2573,6 +2558,11 @@
       <c r="G28" t="inlineStr">
         <is>
           <t>HALLSTAHAMMAR</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
         </is>
       </c>
       <c r="I28" t="n">
@@ -2619,7 +2609,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 21049-2026</t>
+          <t>A 21264-2022</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2633,10 +2623,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>46146</v>
+        <v>44705</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2648,8 +2638,13 @@
           <t>HALLSTAHAMMAR</t>
         </is>
       </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I29" t="n">
-        <v>2.9</v>
+        <v>2.4</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -2692,7 +2687,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 34984-2024</t>
+          <t>A 12077-2022</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2706,10 +2701,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>45527</v>
+        <v>44636</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -2722,7 +2717,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>4.1</v>
+        <v>2.1</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -2765,7 +2760,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 54207-2025</t>
+          <t>A 26059-2026</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2779,10 +2774,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45964</v>
+        <v>46181</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -2795,7 +2790,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>2.1</v>
+        <v>4.7</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -2838,7 +2833,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 16762-2022</t>
+          <t>A 26060-2026</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2852,10 +2847,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>44673</v>
+        <v>46181</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -2868,7 +2863,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>4.2</v>
+        <v>3.6</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -2911,7 +2906,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 22072-2023</t>
+          <t>A 37407-2023</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2925,10 +2920,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>45069</v>
+        <v>45156</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -2941,7 +2936,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -2984,7 +2979,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 26059-2026</t>
+          <t>A 14149-2022</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2998,10 +2993,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>46181</v>
+        <v>44651</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3013,8 +3008,13 @@
           <t>HALLSTAHAMMAR</t>
         </is>
       </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I34" t="n">
-        <v>4.7</v>
+        <v>3.8</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3057,7 +3057,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 26060-2026</t>
+          <t>A 37109-2026</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3071,10 +3071,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>46181</v>
+        <v>46274</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3087,7 +3087,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>3.6</v>
+        <v>3</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3130,7 +3130,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 30766-2022</t>
+          <t>A 58125-2025</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3144,10 +3144,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>44764</v>
+        <v>45982</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3160,7 +3160,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3203,7 +3203,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 35036-2024</t>
+          <t>A 58109-2025</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3217,10 +3217,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45527</v>
+        <v>45982</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3233,7 +3233,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>1.7</v>
+        <v>2.5</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3276,7 +3276,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 37109-2026</t>
+          <t>A 58111-2025</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3290,10 +3290,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>46274</v>
+        <v>45982</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3306,7 +3306,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>3</v>
+        <v>0.6</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3349,7 +3349,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 62831-2023</t>
+          <t>A 53343-2024</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3363,10 +3363,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45270</v>
+        <v>45614</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3379,7 +3379,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>1.1</v>
+        <v>0.9</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3439,7 +3439,7 @@
         <v>46260</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3512,7 +3512,7 @@
         <v>46303</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3585,7 +3585,7 @@
         <v>46091</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3658,7 +3658,7 @@
         <v>46111</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46310</v>
+        <v>46311</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>

--- a/Översikt HALLSTAHAMMAR.xlsx
+++ b/Översikt HALLSTAHAMMAR.xlsx
@@ -601,7 +601,7 @@
         <v>45978</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -713,7 +713,7 @@
         <v>44635</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -791,7 +791,7 @@
         <v>44887</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -864,7 +864,7 @@
         <v>44502</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -937,7 +937,7 @@
         <v>44502</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1010,7 +1010,7 @@
         <v>44739</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1083,7 +1083,7 @@
         <v>44502</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1139,7 +1139,7 @@
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 21972-2023</t>
+          <t>A 21264-2022</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1153,10 +1153,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>45068</v>
+        <v>44705</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1168,8 +1168,13 @@
           <t>HALLSTAHAMMAR</t>
         </is>
       </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I9" t="n">
-        <v>1.5</v>
+        <v>2.4</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -1212,7 +1217,7 @@
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 10263-2024</t>
+          <t>A 21972-2023</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1226,10 +1231,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>45365</v>
+        <v>45068</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1241,13 +1246,8 @@
           <t>HALLSTAHAMMAR</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I10" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
@@ -1290,7 +1290,7 @@
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 34984-2024</t>
+          <t>A 10263-2024</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1304,10 +1304,10 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>45527</v>
+        <v>45365</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1319,8 +1319,13 @@
           <t>HALLSTAHAMMAR</t>
         </is>
       </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I11" t="n">
-        <v>4.1</v>
+        <v>1.4</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -1363,7 +1368,7 @@
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 35036-2024</t>
+          <t>A 55562-2022</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1377,10 +1382,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>45527</v>
+        <v>44888</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1393,7 +1398,7 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>1.7</v>
+        <v>0.8</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -1436,7 +1441,7 @@
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 62831-2023</t>
+          <t>A 12077-2022</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1450,10 +1455,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>45270</v>
+        <v>44636</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1466,7 +1471,7 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>1.1</v>
+        <v>2.1</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
@@ -1509,7 +1514,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 37072-2025</t>
+          <t>A 37407-2023</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1523,10 +1528,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>45875</v>
+        <v>45156</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1539,7 +1544,7 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>1.5</v>
+        <v>3.3</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -1582,7 +1587,7 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 37076-2025</t>
+          <t>A 42991-2025</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1596,10 +1601,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>45875</v>
+        <v>45909</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1612,7 +1617,7 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>2.4</v>
+        <v>7.2</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -1655,7 +1660,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 13510-2025</t>
+          <t>A 43448-2025</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1669,10 +1674,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45736</v>
+        <v>45911</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1685,7 +1690,7 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>2.5</v>
+        <v>1.2</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -1728,7 +1733,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 22072-2023</t>
+          <t>A 44192-2025</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1742,10 +1747,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>45069</v>
+        <v>45915</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1758,7 +1763,7 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>3.5</v>
+        <v>0.8</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -1801,7 +1806,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 8848-2025</t>
+          <t>A 21049-2026</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1815,10 +1820,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>45713</v>
+        <v>46146</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -1831,7 +1836,7 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>2</v>
+        <v>2.9</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -1874,7 +1879,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 55562-2022</t>
+          <t>A 14149-2022</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1888,10 +1893,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>44888</v>
+        <v>44651</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -1903,8 +1908,13 @@
           <t>HALLSTAHAMMAR</t>
         </is>
       </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I19" t="n">
-        <v>0.8</v>
+        <v>3.8</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -1947,7 +1957,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 16762-2022</t>
+          <t>A 53343-2024</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1961,10 +1971,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>44673</v>
+        <v>45614</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -1977,7 +1987,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>4.2</v>
+        <v>0.9</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2020,7 +2030,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 30766-2022</t>
+          <t>A 8848-2025</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2034,10 +2044,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>44764</v>
+        <v>45713</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2050,7 +2060,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>0.6</v>
+        <v>2</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2093,7 +2103,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 42991-2025</t>
+          <t>A 54207-2025</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2107,10 +2117,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>45909</v>
+        <v>45964</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2123,7 +2133,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>7.2</v>
+        <v>2.1</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2166,7 +2176,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 43448-2025</t>
+          <t>A 58109-2025</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2180,10 +2190,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>45911</v>
+        <v>45982</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2196,7 +2206,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>1.2</v>
+        <v>2.5</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2239,7 +2249,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 7245-2025</t>
+          <t>A 58111-2025</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2253,10 +2263,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45702</v>
+        <v>45982</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2269,7 +2279,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>4</v>
+        <v>0.6</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2312,7 +2322,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 21049-2026</t>
+          <t>A 58125-2025</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2326,10 +2336,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>46146</v>
+        <v>45982</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2342,7 +2352,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>2.9</v>
+        <v>0.8</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2385,7 +2395,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 44192-2025</t>
+          <t>A 8436-2023</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2399,10 +2409,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>45915</v>
+        <v>44977</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2414,8 +2424,13 @@
           <t>HALLSTAHAMMAR</t>
         </is>
       </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I26" t="n">
-        <v>0.8</v>
+        <v>4</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2458,7 +2473,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 54207-2025</t>
+          <t>A 7245-2025</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2472,10 +2487,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>45964</v>
+        <v>45702</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2488,7 +2503,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>2.1</v>
+        <v>4</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -2531,7 +2546,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 8436-2023</t>
+          <t>A 34984-2024</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2545,10 +2560,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>44977</v>
+        <v>45527</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2560,13 +2575,8 @@
           <t>HALLSTAHAMMAR</t>
         </is>
       </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I28" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -2609,7 +2619,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 21264-2022</t>
+          <t>A 16762-2022</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2623,10 +2633,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>44705</v>
+        <v>44673</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2638,13 +2648,8 @@
           <t>HALLSTAHAMMAR</t>
         </is>
       </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I29" t="n">
-        <v>2.4</v>
+        <v>4.2</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -2687,7 +2692,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 12077-2022</t>
+          <t>A 22072-2023</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2701,10 +2706,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>44636</v>
+        <v>45069</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -2717,7 +2722,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>2.1</v>
+        <v>3.5</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -2760,7 +2765,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 26059-2026</t>
+          <t>A 30766-2022</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2774,10 +2779,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>46181</v>
+        <v>44764</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -2790,7 +2795,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>4.7</v>
+        <v>0.6</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -2833,7 +2838,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 26060-2026</t>
+          <t>A 26059-2026</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2850,7 +2855,7 @@
         <v>46181</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -2863,7 +2868,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>3.6</v>
+        <v>4.7</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -2906,7 +2911,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 37407-2023</t>
+          <t>A 26060-2026</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2920,10 +2925,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>45156</v>
+        <v>46181</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -2936,7 +2941,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>3.3</v>
+        <v>3.6</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -2979,7 +2984,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 14149-2022</t>
+          <t>A 35036-2024</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2993,10 +2998,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>44651</v>
+        <v>45527</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3008,13 +3013,8 @@
           <t>HALLSTAHAMMAR</t>
         </is>
       </c>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I34" t="n">
-        <v>3.8</v>
+        <v>1.7</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3074,7 +3074,7 @@
         <v>46274</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3130,7 +3130,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 58125-2025</t>
+          <t>A 62831-2023</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3144,10 +3144,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45982</v>
+        <v>45270</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3160,7 +3160,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>0.8</v>
+        <v>1.1</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3203,7 +3203,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 58109-2025</t>
+          <t>A 35238-2026</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3213,14 +3213,14 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45982</v>
+        <v>46260</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3233,7 +3233,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>2.5</v>
+        <v>3.3</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3276,7 +3276,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 58111-2025</t>
+          <t>A 41863-2026</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3290,10 +3290,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45982</v>
+        <v>46303</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3306,7 +3306,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>0.6</v>
+        <v>1.9</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3349,7 +3349,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 53343-2024</t>
+          <t>A 37072-2025</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3363,10 +3363,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45614</v>
+        <v>45875</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3379,7 +3379,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>0.9</v>
+        <v>1.5</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3422,7 +3422,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 35238-2026</t>
+          <t>A 37076-2025</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3432,14 +3432,14 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>46260</v>
+        <v>45875</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3452,7 +3452,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>3.3</v>
+        <v>2.4</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -3495,7 +3495,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 41863-2026</t>
+          <t>A 13510-2025</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3509,10 +3509,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>46303</v>
+        <v>45736</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3525,7 +3525,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>1.9</v>
+        <v>2.5</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -3585,7 +3585,7 @@
         <v>46091</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3658,7 +3658,7 @@
         <v>46111</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46311</v>
+        <v>46312</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>

--- a/Översikt HALLSTAHAMMAR.xlsx
+++ b/Översikt HALLSTAHAMMAR.xlsx
@@ -601,7 +601,7 @@
         <v>45978</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -713,7 +713,7 @@
         <v>44635</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -791,7 +791,7 @@
         <v>44887</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -864,7 +864,7 @@
         <v>44502</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -937,7 +937,7 @@
         <v>44502</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1010,7 +1010,7 @@
         <v>44739</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1083,7 +1083,7 @@
         <v>44502</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1156,7 +1156,7 @@
         <v>44705</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1234,7 +1234,7 @@
         <v>45068</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1307,7 +1307,7 @@
         <v>45365</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1385,7 +1385,7 @@
         <v>44888</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1458,7 +1458,7 @@
         <v>44636</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1531,7 +1531,7 @@
         <v>45156</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1604,7 +1604,7 @@
         <v>45909</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1677,7 +1677,7 @@
         <v>45911</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1750,7 +1750,7 @@
         <v>45915</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1823,7 +1823,7 @@
         <v>46146</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -1896,7 +1896,7 @@
         <v>44651</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -1974,7 +1974,7 @@
         <v>45614</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2047,7 +2047,7 @@
         <v>45713</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2120,7 +2120,7 @@
         <v>45964</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2193,7 +2193,7 @@
         <v>45982</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2266,7 +2266,7 @@
         <v>45982</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2339,7 +2339,7 @@
         <v>45982</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2412,7 +2412,7 @@
         <v>44977</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2490,7 +2490,7 @@
         <v>45702</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2563,7 +2563,7 @@
         <v>45527</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2636,7 +2636,7 @@
         <v>44673</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2709,7 +2709,7 @@
         <v>45069</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -2782,7 +2782,7 @@
         <v>44764</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -2855,7 +2855,7 @@
         <v>46181</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -2928,7 +2928,7 @@
         <v>46181</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3001,7 +3001,7 @@
         <v>45527</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3074,7 +3074,7 @@
         <v>46274</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3147,7 +3147,7 @@
         <v>45270</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3220,7 +3220,7 @@
         <v>46260</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3293,7 +3293,7 @@
         <v>46303</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3366,7 +3366,7 @@
         <v>45875</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3439,7 +3439,7 @@
         <v>45875</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3512,7 +3512,7 @@
         <v>45736</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3585,7 +3585,7 @@
         <v>46091</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3658,7 +3658,7 @@
         <v>46111</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>

--- a/Översikt HALLSTAHAMMAR.xlsx
+++ b/Översikt HALLSTAHAMMAR.xlsx
@@ -601,7 +601,7 @@
         <v>45978</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -713,7 +713,7 @@
         <v>44635</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -791,7 +791,7 @@
         <v>44887</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -864,7 +864,7 @@
         <v>44502</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -937,7 +937,7 @@
         <v>44502</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1010,7 +1010,7 @@
         <v>44739</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1083,7 +1083,7 @@
         <v>44502</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1156,7 +1156,7 @@
         <v>44705</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1234,7 +1234,7 @@
         <v>45068</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1307,7 +1307,7 @@
         <v>45365</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1385,7 +1385,7 @@
         <v>44888</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1458,7 +1458,7 @@
         <v>44636</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1531,7 +1531,7 @@
         <v>45156</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1604,7 +1604,7 @@
         <v>45909</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1677,7 +1677,7 @@
         <v>45911</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1750,7 +1750,7 @@
         <v>45915</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1823,7 +1823,7 @@
         <v>46146</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -1896,7 +1896,7 @@
         <v>44651</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -1974,7 +1974,7 @@
         <v>45614</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2047,7 +2047,7 @@
         <v>45713</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2120,7 +2120,7 @@
         <v>45964</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2193,7 +2193,7 @@
         <v>45982</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2266,7 +2266,7 @@
         <v>45982</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2339,7 +2339,7 @@
         <v>45982</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2412,7 +2412,7 @@
         <v>44977</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2490,7 +2490,7 @@
         <v>45702</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2563,7 +2563,7 @@
         <v>45527</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2636,7 +2636,7 @@
         <v>44673</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2709,7 +2709,7 @@
         <v>45069</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -2782,7 +2782,7 @@
         <v>44764</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -2855,7 +2855,7 @@
         <v>46181</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -2928,7 +2928,7 @@
         <v>46181</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3001,7 +3001,7 @@
         <v>45527</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3074,7 +3074,7 @@
         <v>46274</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3147,7 +3147,7 @@
         <v>45270</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3220,7 +3220,7 @@
         <v>46260</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3293,7 +3293,7 @@
         <v>46303</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3366,7 +3366,7 @@
         <v>45875</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3439,7 +3439,7 @@
         <v>45875</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3512,7 +3512,7 @@
         <v>45736</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3585,7 +3585,7 @@
         <v>46091</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3658,7 +3658,7 @@
         <v>46111</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>

--- a/Översikt HALLSTAHAMMAR.xlsx
+++ b/Översikt HALLSTAHAMMAR.xlsx
@@ -601,7 +601,7 @@
         <v>45978</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -713,7 +713,7 @@
         <v>44635</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -791,7 +791,7 @@
         <v>44887</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -864,7 +864,7 @@
         <v>44502</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -937,7 +937,7 @@
         <v>44502</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1010,7 +1010,7 @@
         <v>44739</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1083,7 +1083,7 @@
         <v>44502</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1139,7 +1139,7 @@
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 21264-2022</t>
+          <t>A 10263-2024</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1153,10 +1153,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>44705</v>
+        <v>45365</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1170,11 +1170,11 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Allmännings- och besparingsskogar</t>
+          <t>Kyrkan</t>
         </is>
       </c>
       <c r="I9" t="n">
-        <v>2.4</v>
+        <v>1.4</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -1217,7 +1217,7 @@
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 21972-2023</t>
+          <t>A 34984-2024</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1231,10 +1231,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>45068</v>
+        <v>45527</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1247,7 +1247,7 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>1.5</v>
+        <v>4.1</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
@@ -1290,7 +1290,7 @@
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 10263-2024</t>
+          <t>A 22072-2023</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1304,10 +1304,10 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>45365</v>
+        <v>45069</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1319,13 +1319,8 @@
           <t>HALLSTAHAMMAR</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I11" t="n">
-        <v>1.4</v>
+        <v>3.5</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -1385,7 +1380,7 @@
         <v>44888</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1441,7 +1436,7 @@
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 12077-2022</t>
+          <t>A 16762-2022</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1455,10 +1450,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>44636</v>
+        <v>44673</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1471,7 +1466,7 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>2.1</v>
+        <v>4.2</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
@@ -1514,7 +1509,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 37407-2023</t>
+          <t>A 42991-2025</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1528,10 +1523,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>45156</v>
+        <v>45909</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1544,7 +1539,7 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>3.3</v>
+        <v>7.2</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -1587,7 +1582,7 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 42991-2025</t>
+          <t>A 43448-2025</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1601,10 +1596,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>45909</v>
+        <v>45911</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1617,7 +1612,7 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>7.2</v>
+        <v>1.2</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -1660,7 +1655,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 43448-2025</t>
+          <t>A 44192-2025</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1674,10 +1669,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45911</v>
+        <v>45915</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1690,7 +1685,7 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>1.2</v>
+        <v>0.8</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -1733,7 +1728,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 44192-2025</t>
+          <t>A 21972-2023</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1747,10 +1742,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>45915</v>
+        <v>45068</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1763,7 +1758,7 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>0.8</v>
+        <v>1.5</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -1823,7 +1818,7 @@
         <v>46146</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -1879,7 +1874,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 14149-2022</t>
+          <t>A 35036-2024</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1893,10 +1888,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>44651</v>
+        <v>45527</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -1908,13 +1903,8 @@
           <t>HALLSTAHAMMAR</t>
         </is>
       </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I19" t="n">
-        <v>3.8</v>
+        <v>1.7</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -1957,7 +1947,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 53343-2024</t>
+          <t>A 62831-2023</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1971,10 +1961,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>45614</v>
+        <v>45270</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -1987,7 +1977,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>0.9</v>
+        <v>1.1</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2030,7 +2020,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 8848-2025</t>
+          <t>A 54207-2025</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2044,10 +2034,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>45713</v>
+        <v>45964</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2060,7 +2050,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2103,7 +2093,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 54207-2025</t>
+          <t>A 58125-2025</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2117,10 +2107,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>45964</v>
+        <v>45982</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2133,7 +2123,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>2.1</v>
+        <v>0.8</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2193,7 +2183,7 @@
         <v>45982</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2266,7 +2256,7 @@
         <v>45982</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2322,7 +2312,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 58125-2025</t>
+          <t>A 8848-2025</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2336,10 +2326,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>45982</v>
+        <v>45713</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2352,7 +2342,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>0.8</v>
+        <v>2</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2395,7 +2385,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 8436-2023</t>
+          <t>A 30766-2022</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2409,10 +2399,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>44977</v>
+        <v>44764</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2424,13 +2414,8 @@
           <t>HALLSTAHAMMAR</t>
         </is>
       </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I26" t="n">
-        <v>4</v>
+        <v>0.6</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2490,7 +2475,7 @@
         <v>45702</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2546,7 +2531,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 34984-2024</t>
+          <t>A 26059-2026</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2560,10 +2545,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>45527</v>
+        <v>46181</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2576,7 +2561,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>4.1</v>
+        <v>4.7</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -2619,7 +2604,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 16762-2022</t>
+          <t>A 26060-2026</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2633,10 +2618,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>44673</v>
+        <v>46181</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2649,7 +2634,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>4.2</v>
+        <v>3.6</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -2692,7 +2677,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 22072-2023</t>
+          <t>A 8436-2023</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2706,10 +2691,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>45069</v>
+        <v>44977</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -2721,8 +2706,13 @@
           <t>HALLSTAHAMMAR</t>
         </is>
       </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I30" t="n">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -2765,7 +2755,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 30766-2022</t>
+          <t>A 21264-2022</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2779,10 +2769,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>44764</v>
+        <v>44705</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -2794,8 +2784,13 @@
           <t>HALLSTAHAMMAR</t>
         </is>
       </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I31" t="n">
-        <v>0.6</v>
+        <v>2.4</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -2838,7 +2833,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 26059-2026</t>
+          <t>A 12077-2022</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2852,10 +2847,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>46181</v>
+        <v>44636</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -2868,7 +2863,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>4.7</v>
+        <v>2.1</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -2911,7 +2906,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 26060-2026</t>
+          <t>A 37407-2023</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2925,10 +2920,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>46181</v>
+        <v>45156</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -2941,7 +2936,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>3.6</v>
+        <v>3.3</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -2984,7 +2979,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 35036-2024</t>
+          <t>A 37109-2026</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2998,10 +2993,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>45527</v>
+        <v>46274</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3014,7 +3009,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>1.7</v>
+        <v>3</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3057,7 +3052,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 37109-2026</t>
+          <t>A 14149-2022</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3071,10 +3066,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>46274</v>
+        <v>44651</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3086,8 +3081,13 @@
           <t>HALLSTAHAMMAR</t>
         </is>
       </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I35" t="n">
-        <v>3</v>
+        <v>3.8</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3130,7 +3130,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 62831-2023</t>
+          <t>A 53343-2024</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3144,10 +3144,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45270</v>
+        <v>45614</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3160,7 +3160,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>1.1</v>
+        <v>0.9</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3220,7 +3220,7 @@
         <v>46260</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3293,7 +3293,7 @@
         <v>46303</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3366,7 +3366,7 @@
         <v>45875</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3439,7 +3439,7 @@
         <v>45875</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3512,7 +3512,7 @@
         <v>45736</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3585,7 +3585,7 @@
         <v>46091</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3658,7 +3658,7 @@
         <v>46111</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>

--- a/Översikt HALLSTAHAMMAR.xlsx
+++ b/Översikt HALLSTAHAMMAR.xlsx
@@ -601,7 +601,7 @@
         <v>45978</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -713,7 +713,7 @@
         <v>44635</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -791,7 +791,7 @@
         <v>44887</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -864,7 +864,7 @@
         <v>44502</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -937,7 +937,7 @@
         <v>44502</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1010,7 +1010,7 @@
         <v>44739</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1083,7 +1083,7 @@
         <v>44502</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1139,7 +1139,7 @@
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 10263-2024</t>
+          <t>A 21972-2023</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1153,10 +1153,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>45365</v>
+        <v>45068</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1168,13 +1168,8 @@
           <t>HALLSTAHAMMAR</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I9" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -1217,7 +1212,7 @@
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 34984-2024</t>
+          <t>A 21264-2022</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1231,10 +1226,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>45527</v>
+        <v>44705</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1246,8 +1241,13 @@
           <t>HALLSTAHAMMAR</t>
         </is>
       </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I10" t="n">
-        <v>4.1</v>
+        <v>2.4</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
@@ -1290,7 +1290,7 @@
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 22072-2023</t>
+          <t>A 10263-2024</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1304,10 +1304,10 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>45069</v>
+        <v>45365</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1319,8 +1319,13 @@
           <t>HALLSTAHAMMAR</t>
         </is>
       </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I11" t="n">
-        <v>3.5</v>
+        <v>1.4</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -1380,7 +1385,7 @@
         <v>44888</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1436,7 +1441,7 @@
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 16762-2022</t>
+          <t>A 42991-2025</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1450,10 +1455,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>44673</v>
+        <v>45909</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1466,7 +1471,7 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>4.2</v>
+        <v>7.2</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
@@ -1509,7 +1514,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 42991-2025</t>
+          <t>A 43448-2025</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1523,10 +1528,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>45909</v>
+        <v>45911</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1539,7 +1544,7 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>7.2</v>
+        <v>1.2</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -1582,7 +1587,7 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 43448-2025</t>
+          <t>A 44192-2025</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1596,10 +1601,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>45911</v>
+        <v>45915</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1612,7 +1617,7 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>1.2</v>
+        <v>0.8</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -1655,7 +1660,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 44192-2025</t>
+          <t>A 12077-2022</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1669,10 +1674,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45915</v>
+        <v>44636</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1685,7 +1690,7 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>0.8</v>
+        <v>2.1</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -1728,7 +1733,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 21972-2023</t>
+          <t>A 37407-2023</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1742,10 +1747,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>45068</v>
+        <v>45156</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1758,7 +1763,7 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>1.5</v>
+        <v>3.3</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -1801,7 +1806,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 21049-2026</t>
+          <t>A 58109-2025</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1815,10 +1820,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>46146</v>
+        <v>45982</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -1831,7 +1836,7 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>2.9</v>
+        <v>2.5</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -1874,7 +1879,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 35036-2024</t>
+          <t>A 58111-2025</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1888,10 +1893,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>45527</v>
+        <v>45982</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -1904,7 +1909,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>1.7</v>
+        <v>0.6</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -1947,7 +1952,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 62831-2023</t>
+          <t>A 58125-2025</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1961,10 +1966,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>45270</v>
+        <v>45982</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -1977,7 +1982,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>1.1</v>
+        <v>0.8</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2020,7 +2025,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 54207-2025</t>
+          <t>A 37072-2025</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2034,10 +2039,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>45964</v>
+        <v>45875</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2050,7 +2055,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>2.1</v>
+        <v>1.5</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2093,7 +2098,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 58125-2025</t>
+          <t>A 37076-2025</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2107,10 +2112,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>45982</v>
+        <v>45875</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2123,7 +2128,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>0.8</v>
+        <v>2.4</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2166,7 +2171,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 58109-2025</t>
+          <t>A 13510-2025</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2180,10 +2185,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>45982</v>
+        <v>45736</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2239,7 +2244,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 58111-2025</t>
+          <t>A 21049-2026</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2253,10 +2258,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45982</v>
+        <v>46146</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2269,7 +2274,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>0.6</v>
+        <v>2.9</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2312,7 +2317,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 8848-2025</t>
+          <t>A 14149-2022</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2326,10 +2331,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>45713</v>
+        <v>44651</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2341,8 +2346,13 @@
           <t>HALLSTAHAMMAR</t>
         </is>
       </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I25" t="n">
-        <v>2</v>
+        <v>3.8</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2385,7 +2395,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 30766-2022</t>
+          <t>A 53343-2024</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2399,10 +2409,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>44764</v>
+        <v>45614</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2415,7 +2425,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>0.6</v>
+        <v>0.9</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2458,7 +2468,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 7245-2025</t>
+          <t>A 8848-2025</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2472,10 +2482,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>45702</v>
+        <v>45713</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2488,7 +2498,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -2531,7 +2541,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 26059-2026</t>
+          <t>A 54207-2025</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2545,10 +2555,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>46181</v>
+        <v>45964</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2561,7 +2571,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>4.7</v>
+        <v>2.1</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -2604,7 +2614,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 26060-2026</t>
+          <t>A 8436-2023</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2618,10 +2628,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>46181</v>
+        <v>44977</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2633,8 +2643,13 @@
           <t>HALLSTAHAMMAR</t>
         </is>
       </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I29" t="n">
-        <v>3.6</v>
+        <v>4</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -2677,7 +2692,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 8436-2023</t>
+          <t>A 7245-2025</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2691,10 +2706,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>44977</v>
+        <v>45702</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -2704,11 +2719,6 @@
       <c r="G30" t="inlineStr">
         <is>
           <t>HALLSTAHAMMAR</t>
-        </is>
-      </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
         </is>
       </c>
       <c r="I30" t="n">
@@ -2755,7 +2765,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 21264-2022</t>
+          <t>A 34984-2024</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2769,10 +2779,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>44705</v>
+        <v>45527</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -2784,13 +2794,8 @@
           <t>HALLSTAHAMMAR</t>
         </is>
       </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I31" t="n">
-        <v>2.4</v>
+        <v>4.1</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -2833,7 +2838,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 12077-2022</t>
+          <t>A 26059-2026</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2847,10 +2852,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>44636</v>
+        <v>46181</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -2863,7 +2868,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>2.1</v>
+        <v>4.7</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -2906,7 +2911,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 37407-2023</t>
+          <t>A 26060-2026</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2920,10 +2925,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>45156</v>
+        <v>46181</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -2936,7 +2941,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>3.3</v>
+        <v>3.6</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -2979,7 +2984,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 37109-2026</t>
+          <t>A 16762-2022</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2993,10 +2998,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>46274</v>
+        <v>44673</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3009,7 +3014,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>3</v>
+        <v>4.2</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3052,7 +3057,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 14149-2022</t>
+          <t>A 37109-2026</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3066,10 +3071,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>44651</v>
+        <v>46274</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3081,13 +3086,8 @@
           <t>HALLSTAHAMMAR</t>
         </is>
       </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I35" t="n">
-        <v>3.8</v>
+        <v>3</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3130,7 +3130,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 53343-2024</t>
+          <t>A 22072-2023</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3144,10 +3144,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45614</v>
+        <v>45069</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3160,7 +3160,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>0.9</v>
+        <v>3.5</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3203,7 +3203,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 35238-2026</t>
+          <t>A 30766-2022</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3213,14 +3213,14 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>46260</v>
+        <v>44764</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3233,7 +3233,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>3.3</v>
+        <v>0.6</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3276,7 +3276,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 41863-2026</t>
+          <t>A 35036-2024</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3290,10 +3290,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>46303</v>
+        <v>45527</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3306,7 +3306,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>1.9</v>
+        <v>1.7</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3349,7 +3349,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 37072-2025</t>
+          <t>A 35238-2026</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3359,14 +3359,14 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45875</v>
+        <v>46260</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3379,7 +3379,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>1.5</v>
+        <v>3.3</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3422,7 +3422,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 37076-2025</t>
+          <t>A 41863-2026</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3436,10 +3436,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45875</v>
+        <v>46303</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3452,7 +3452,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>2.4</v>
+        <v>1.9</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -3495,7 +3495,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 13510-2025</t>
+          <t>A 62831-2023</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3509,10 +3509,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45736</v>
+        <v>45270</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3525,7 +3525,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>2.5</v>
+        <v>1.1</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -3585,7 +3585,7 @@
         <v>46091</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3658,7 +3658,7 @@
         <v>46111</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46315</v>
+        <v>46316</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>

--- a/Översikt HALLSTAHAMMAR.xlsx
+++ b/Översikt HALLSTAHAMMAR.xlsx
@@ -601,7 +601,7 @@
         <v>45978</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -713,7 +713,7 @@
         <v>44635</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -791,7 +791,7 @@
         <v>44887</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -864,7 +864,7 @@
         <v>44502</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -937,7 +937,7 @@
         <v>44502</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1010,7 +1010,7 @@
         <v>44739</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1083,7 +1083,7 @@
         <v>44502</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1139,7 +1139,7 @@
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 21972-2023</t>
+          <t>A 10263-2024</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1153,10 +1153,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>45068</v>
+        <v>45365</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1168,8 +1168,13 @@
           <t>HALLSTAHAMMAR</t>
         </is>
       </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I9" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -1212,7 +1217,7 @@
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 21264-2022</t>
+          <t>A 34984-2024</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1226,10 +1231,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>44705</v>
+        <v>45527</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1241,13 +1246,8 @@
           <t>HALLSTAHAMMAR</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I10" t="n">
-        <v>2.4</v>
+        <v>4.1</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
@@ -1290,7 +1290,7 @@
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 10263-2024</t>
+          <t>A 42991-2025</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1304,10 +1304,10 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>45365</v>
+        <v>45909</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1319,13 +1319,8 @@
           <t>HALLSTAHAMMAR</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I11" t="n">
-        <v>1.4</v>
+        <v>7.2</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -1368,7 +1363,7 @@
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 55562-2022</t>
+          <t>A 43448-2025</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1382,10 +1377,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>44888</v>
+        <v>45911</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1398,7 +1393,7 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>0.8</v>
+        <v>1.2</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -1441,7 +1436,7 @@
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 42991-2025</t>
+          <t>A 22072-2023</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1455,10 +1450,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>45909</v>
+        <v>45069</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1471,7 +1466,7 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>7.2</v>
+        <v>3.5</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
@@ -1514,7 +1509,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 43448-2025</t>
+          <t>A 44192-2025</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1528,10 +1523,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>45911</v>
+        <v>45915</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1544,7 +1539,7 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>1.2</v>
+        <v>0.8</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -1587,7 +1582,7 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 44192-2025</t>
+          <t>A 55562-2022</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1601,10 +1596,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>45915</v>
+        <v>44888</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1660,7 +1655,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 12077-2022</t>
+          <t>A 37072-2025</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1674,10 +1669,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>44636</v>
+        <v>45875</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1690,7 +1685,7 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>2.1</v>
+        <v>1.5</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -1733,7 +1728,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 37407-2023</t>
+          <t>A 37076-2025</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1747,10 +1742,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>45156</v>
+        <v>45875</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1763,7 +1758,7 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>3.3</v>
+        <v>2.4</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -1806,7 +1801,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 58109-2025</t>
+          <t>A 13510-2025</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1820,10 +1815,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>45982</v>
+        <v>45736</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -1879,7 +1874,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 58111-2025</t>
+          <t>A 16762-2022</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1893,10 +1888,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>45982</v>
+        <v>44673</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -1909,7 +1904,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>0.6</v>
+        <v>4.2</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -1969,7 +1964,7 @@
         <v>45982</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2025,7 +2020,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 37072-2025</t>
+          <t>A 58109-2025</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2039,10 +2034,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>45875</v>
+        <v>45982</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2055,7 +2050,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>1.5</v>
+        <v>2.5</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2098,7 +2093,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 37076-2025</t>
+          <t>A 58111-2025</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2112,10 +2107,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>45875</v>
+        <v>45982</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2128,7 +2123,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>2.4</v>
+        <v>0.6</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2171,7 +2166,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 13510-2025</t>
+          <t>A 21972-2023</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2185,10 +2180,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>45736</v>
+        <v>45068</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2201,7 +2196,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>2.5</v>
+        <v>1.5</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2244,7 +2239,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 21049-2026</t>
+          <t>A 35036-2024</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2258,10 +2253,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>46146</v>
+        <v>45527</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2274,7 +2269,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>2.9</v>
+        <v>1.7</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2317,7 +2312,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 14149-2022</t>
+          <t>A 62831-2023</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2331,10 +2326,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>44651</v>
+        <v>45270</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2346,13 +2341,8 @@
           <t>HALLSTAHAMMAR</t>
         </is>
       </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I25" t="n">
-        <v>3.8</v>
+        <v>1.1</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2395,7 +2385,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 53343-2024</t>
+          <t>A 8848-2025</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2409,10 +2399,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>45614</v>
+        <v>45713</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2425,7 +2415,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>0.9</v>
+        <v>2</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2468,7 +2458,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 8848-2025</t>
+          <t>A 21049-2026</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2482,10 +2472,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>45713</v>
+        <v>46146</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2498,7 +2488,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>2</v>
+        <v>2.9</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -2541,7 +2531,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 54207-2025</t>
+          <t>A 30766-2022</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2555,10 +2545,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>45964</v>
+        <v>44764</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2571,7 +2561,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>2.1</v>
+        <v>0.6</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -2614,7 +2604,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 8436-2023</t>
+          <t>A 54207-2025</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2628,10 +2618,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>44977</v>
+        <v>45964</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2643,13 +2633,8 @@
           <t>HALLSTAHAMMAR</t>
         </is>
       </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I29" t="n">
-        <v>4</v>
+        <v>2.1</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -2709,7 +2694,7 @@
         <v>45702</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -2765,7 +2750,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 34984-2024</t>
+          <t>A 26059-2026</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2779,10 +2764,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45527</v>
+        <v>46181</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -2795,7 +2780,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>4.1</v>
+        <v>4.7</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -2838,7 +2823,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 26059-2026</t>
+          <t>A 26060-2026</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2855,7 +2840,7 @@
         <v>46181</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -2868,7 +2853,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>4.7</v>
+        <v>3.6</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -2911,7 +2896,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 26060-2026</t>
+          <t>A 8436-2023</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2925,10 +2910,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>46181</v>
+        <v>44977</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -2940,8 +2925,13 @@
           <t>HALLSTAHAMMAR</t>
         </is>
       </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I33" t="n">
-        <v>3.6</v>
+        <v>4</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -2984,7 +2974,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 16762-2022</t>
+          <t>A 21264-2022</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2998,10 +2988,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>44673</v>
+        <v>44705</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3013,8 +3003,13 @@
           <t>HALLSTAHAMMAR</t>
         </is>
       </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I34" t="n">
-        <v>4.2</v>
+        <v>2.4</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3057,7 +3052,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 37109-2026</t>
+          <t>A 12077-2022</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3071,10 +3066,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>46274</v>
+        <v>44636</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3087,7 +3082,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>3</v>
+        <v>2.1</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3130,7 +3125,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 22072-2023</t>
+          <t>A 37407-2023</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3144,10 +3139,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45069</v>
+        <v>45156</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3160,7 +3155,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3203,7 +3198,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 30766-2022</t>
+          <t>A 14149-2022</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3217,10 +3212,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>44764</v>
+        <v>44651</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3232,8 +3227,13 @@
           <t>HALLSTAHAMMAR</t>
         </is>
       </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I37" t="n">
-        <v>0.6</v>
+        <v>3.8</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3276,7 +3276,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 35036-2024</t>
+          <t>A 53343-2024</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3290,10 +3290,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45527</v>
+        <v>45614</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3306,7 +3306,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>1.7</v>
+        <v>0.9</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3366,7 +3366,7 @@
         <v>46260</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3439,7 +3439,7 @@
         <v>46303</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3495,7 +3495,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 62831-2023</t>
+          <t>A 37109-2026</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3509,10 +3509,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45270</v>
+        <v>46274</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3525,7 +3525,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>1.1</v>
+        <v>3</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -3585,7 +3585,7 @@
         <v>46091</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3658,7 +3658,7 @@
         <v>46111</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>

--- a/Översikt HALLSTAHAMMAR.xlsx
+++ b/Översikt HALLSTAHAMMAR.xlsx
@@ -601,7 +601,7 @@
         <v>45978</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -713,7 +713,7 @@
         <v>44635</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -791,7 +791,7 @@
         <v>44887</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -864,7 +864,7 @@
         <v>44502</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -937,7 +937,7 @@
         <v>44502</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1010,7 +1010,7 @@
         <v>44739</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1083,7 +1083,7 @@
         <v>44502</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1139,7 +1139,7 @@
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 10263-2024</t>
+          <t>A 21264-2022</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1153,10 +1153,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>45365</v>
+        <v>44705</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1170,11 +1170,11 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Kyrkan</t>
+          <t>Allmännings- och besparingsskogar</t>
         </is>
       </c>
       <c r="I9" t="n">
-        <v>1.4</v>
+        <v>2.4</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -1217,7 +1217,7 @@
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 34984-2024</t>
+          <t>A 21972-2023</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1231,10 +1231,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>45527</v>
+        <v>45068</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1247,7 +1247,7 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>4.1</v>
+        <v>1.5</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
@@ -1290,7 +1290,7 @@
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 42991-2025</t>
+          <t>A 16762-2022</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1304,10 +1304,10 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>45909</v>
+        <v>44673</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1320,7 +1320,7 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>7.2</v>
+        <v>4.2</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -1363,7 +1363,7 @@
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 43448-2025</t>
+          <t>A 22072-2023</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1377,10 +1377,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>45911</v>
+        <v>45069</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1393,7 +1393,7 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>1.2</v>
+        <v>3.5</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -1436,7 +1436,7 @@
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 22072-2023</t>
+          <t>A 30766-2022</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1450,10 +1450,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>45069</v>
+        <v>44764</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1466,7 +1466,7 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>3.5</v>
+        <v>0.6</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
@@ -1509,7 +1509,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 44192-2025</t>
+          <t>A 42991-2025</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1523,10 +1523,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>45915</v>
+        <v>45909</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1539,7 +1539,7 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>0.8</v>
+        <v>7.2</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -1582,7 +1582,7 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 55562-2022</t>
+          <t>A 43448-2025</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1596,10 +1596,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>44888</v>
+        <v>45911</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1612,7 +1612,7 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>0.8</v>
+        <v>1.2</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -1655,7 +1655,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 37072-2025</t>
+          <t>A 44192-2025</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1669,10 +1669,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45875</v>
+        <v>45915</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1685,7 +1685,7 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>1.5</v>
+        <v>0.8</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -1728,7 +1728,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 37076-2025</t>
+          <t>A 37072-2025</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1745,7 +1745,7 @@
         <v>45875</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1758,7 +1758,7 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>2.4</v>
+        <v>1.5</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -1801,7 +1801,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 13510-2025</t>
+          <t>A 37076-2025</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1815,10 +1815,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>45736</v>
+        <v>45875</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -1831,7 +1831,7 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -1874,7 +1874,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 16762-2022</t>
+          <t>A 13510-2025</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1888,10 +1888,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>44673</v>
+        <v>45736</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -1904,7 +1904,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>4.2</v>
+        <v>2.5</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -1947,7 +1947,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 58125-2025</t>
+          <t>A 35036-2024</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1961,10 +1961,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>45982</v>
+        <v>45527</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -1977,7 +1977,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>0.8</v>
+        <v>1.7</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2020,7 +2020,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 58109-2025</t>
+          <t>A 10263-2024</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2034,10 +2034,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>45982</v>
+        <v>45365</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2049,8 +2049,13 @@
           <t>HALLSTAHAMMAR</t>
         </is>
       </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I21" t="n">
-        <v>2.5</v>
+        <v>1.4</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2093,7 +2098,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 58111-2025</t>
+          <t>A 21049-2026</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2107,10 +2112,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>45982</v>
+        <v>46146</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2123,7 +2128,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>0.6</v>
+        <v>2.9</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2166,7 +2171,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 21972-2023</t>
+          <t>A 58109-2025</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2180,10 +2185,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>45068</v>
+        <v>45982</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2196,7 +2201,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>1.5</v>
+        <v>2.5</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2239,7 +2244,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 35036-2024</t>
+          <t>A 58111-2025</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2253,10 +2258,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45527</v>
+        <v>45982</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2269,7 +2274,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>1.7</v>
+        <v>0.6</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2312,7 +2317,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 62831-2023</t>
+          <t>A 58125-2025</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2326,10 +2331,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>45270</v>
+        <v>45982</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2342,7 +2347,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>1.1</v>
+        <v>0.8</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2385,7 +2390,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 8848-2025</t>
+          <t>A 54207-2025</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2399,10 +2404,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>45713</v>
+        <v>45964</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2415,7 +2420,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2458,7 +2463,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 21049-2026</t>
+          <t>A 55562-2022</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2472,10 +2477,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>46146</v>
+        <v>44888</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2488,7 +2493,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>2.9</v>
+        <v>0.8</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -2531,7 +2536,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 30766-2022</t>
+          <t>A 62831-2023</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2545,10 +2550,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>44764</v>
+        <v>45270</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2561,7 +2566,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>0.6</v>
+        <v>1.1</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -2604,7 +2609,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 54207-2025</t>
+          <t>A 26059-2026</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2618,10 +2623,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>45964</v>
+        <v>46181</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2634,7 +2639,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>2.1</v>
+        <v>4.7</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -2677,7 +2682,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 7245-2025</t>
+          <t>A 26060-2026</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2691,10 +2696,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>45702</v>
+        <v>46181</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -2707,7 +2712,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>4</v>
+        <v>3.6</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -2750,7 +2755,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 26059-2026</t>
+          <t>A 37109-2026</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2764,10 +2769,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>46181</v>
+        <v>46274</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -2780,7 +2785,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>4.7</v>
+        <v>3</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -2823,7 +2828,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 26060-2026</t>
+          <t>A 12077-2022</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2837,10 +2842,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>46181</v>
+        <v>44636</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -2853,7 +2858,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>3.6</v>
+        <v>2.1</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -2896,7 +2901,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 8436-2023</t>
+          <t>A 37407-2023</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2910,10 +2915,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>44977</v>
+        <v>45156</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -2925,13 +2930,8 @@
           <t>HALLSTAHAMMAR</t>
         </is>
       </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I33" t="n">
-        <v>4</v>
+        <v>3.3</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -2974,7 +2974,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 21264-2022</t>
+          <t>A 14149-2022</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2988,10 +2988,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>44705</v>
+        <v>44651</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3009,7 +3009,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>2.4</v>
+        <v>3.8</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3052,7 +3052,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 12077-2022</t>
+          <t>A 53343-2024</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3066,10 +3066,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>44636</v>
+        <v>45614</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3082,7 +3082,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>2.1</v>
+        <v>0.9</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3125,7 +3125,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 37407-2023</t>
+          <t>A 8848-2025</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3139,10 +3139,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45156</v>
+        <v>45713</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3155,7 +3155,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>3.3</v>
+        <v>2</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3198,7 +3198,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 14149-2022</t>
+          <t>A 35238-2026</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3208,14 +3208,14 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>44651</v>
+        <v>46260</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3227,13 +3227,8 @@
           <t>HALLSTAHAMMAR</t>
         </is>
       </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I37" t="n">
-        <v>3.8</v>
+        <v>3.3</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3276,7 +3271,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 53343-2024</t>
+          <t>A 8436-2023</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3290,10 +3285,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45614</v>
+        <v>44977</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3305,8 +3300,13 @@
           <t>HALLSTAHAMMAR</t>
         </is>
       </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I38" t="n">
-        <v>0.9</v>
+        <v>4</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3349,7 +3349,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 35238-2026</t>
+          <t>A 41863-2026</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3359,14 +3359,14 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>46260</v>
+        <v>46303</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3379,7 +3379,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>3.3</v>
+        <v>1.9</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3422,7 +3422,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 41863-2026</t>
+          <t>A 7245-2025</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3436,10 +3436,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>46303</v>
+        <v>45702</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3452,7 +3452,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>1.9</v>
+        <v>4</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -3495,7 +3495,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 37109-2026</t>
+          <t>A 34984-2024</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3509,10 +3509,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>46274</v>
+        <v>45527</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3525,7 +3525,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>3</v>
+        <v>4.1</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -3585,7 +3585,7 @@
         <v>46091</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3658,7 +3658,7 @@
         <v>46111</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46317</v>
+        <v>46318</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>

--- a/Översikt HALLSTAHAMMAR.xlsx
+++ b/Översikt HALLSTAHAMMAR.xlsx
@@ -601,7 +601,7 @@
         <v>45978</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -713,7 +713,7 @@
         <v>44635</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -791,7 +791,7 @@
         <v>44887</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -864,7 +864,7 @@
         <v>44502</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -937,7 +937,7 @@
         <v>44502</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1010,7 +1010,7 @@
         <v>44739</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1083,7 +1083,7 @@
         <v>44502</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1139,7 +1139,7 @@
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 21264-2022</t>
+          <t>A 8436-2023</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1153,10 +1153,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>44705</v>
+        <v>44977</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1170,11 +1170,11 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Allmännings- och besparingsskogar</t>
+          <t>Kyrkan</t>
         </is>
       </c>
       <c r="I9" t="n">
-        <v>2.4</v>
+        <v>4</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -1217,7 +1217,7 @@
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 21972-2023</t>
+          <t>A 42991-2025</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1231,10 +1231,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>45068</v>
+        <v>45909</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1247,7 +1247,7 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>1.5</v>
+        <v>7.2</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
@@ -1290,7 +1290,7 @@
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 16762-2022</t>
+          <t>A 54207-2025</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1304,10 +1304,10 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>44673</v>
+        <v>45964</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1320,7 +1320,7 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>4.2</v>
+        <v>2.1</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -1363,7 +1363,7 @@
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 22072-2023</t>
+          <t>A 43448-2025</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1377,10 +1377,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>45069</v>
+        <v>45911</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1393,7 +1393,7 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>3.5</v>
+        <v>1.2</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -1436,7 +1436,7 @@
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 30766-2022</t>
+          <t>A 44192-2025</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1450,10 +1450,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>44764</v>
+        <v>45915</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1466,7 +1466,7 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
@@ -1509,7 +1509,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 42991-2025</t>
+          <t>A 10263-2024</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1523,10 +1523,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>45909</v>
+        <v>45365</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1538,8 +1538,13 @@
           <t>HALLSTAHAMMAR</t>
         </is>
       </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I14" t="n">
-        <v>7.2</v>
+        <v>1.4</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -1582,7 +1587,7 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 43448-2025</t>
+          <t>A 21264-2022</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1596,10 +1601,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>45911</v>
+        <v>44705</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1611,8 +1616,13 @@
           <t>HALLSTAHAMMAR</t>
         </is>
       </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I15" t="n">
-        <v>1.2</v>
+        <v>2.4</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -1655,7 +1665,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 44192-2025</t>
+          <t>A 12077-2022</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1669,10 +1679,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>45915</v>
+        <v>44636</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1685,7 +1695,7 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>0.8</v>
+        <v>2.1</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -1728,7 +1738,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 37072-2025</t>
+          <t>A 37407-2023</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1742,10 +1752,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>45875</v>
+        <v>45156</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1758,7 +1768,7 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>1.5</v>
+        <v>3.3</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -1801,7 +1811,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 37076-2025</t>
+          <t>A 14149-2022</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1815,10 +1825,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>45875</v>
+        <v>44651</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -1830,8 +1840,13 @@
           <t>HALLSTAHAMMAR</t>
         </is>
       </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I18" t="n">
-        <v>2.4</v>
+        <v>3.8</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -1874,7 +1889,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 13510-2025</t>
+          <t>A 58125-2025</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1888,10 +1903,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>45736</v>
+        <v>45982</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -1904,7 +1919,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>2.5</v>
+        <v>0.8</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -1947,7 +1962,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 35036-2024</t>
+          <t>A 58109-2025</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1961,10 +1976,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>45527</v>
+        <v>45982</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -1977,7 +1992,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>1.7</v>
+        <v>2.5</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2020,7 +2035,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 10263-2024</t>
+          <t>A 58111-2025</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2034,10 +2049,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>45365</v>
+        <v>45982</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2049,13 +2064,8 @@
           <t>HALLSTAHAMMAR</t>
         </is>
       </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I21" t="n">
-        <v>1.4</v>
+        <v>0.6</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2098,7 +2108,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 21049-2026</t>
+          <t>A 26059-2026</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2112,10 +2122,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>46146</v>
+        <v>46181</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2128,7 +2138,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>2.9</v>
+        <v>4.7</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2171,7 +2181,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 58109-2025</t>
+          <t>A 26060-2026</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2185,10 +2195,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>45982</v>
+        <v>46181</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2201,7 +2211,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>2.5</v>
+        <v>3.6</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2244,7 +2254,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 58111-2025</t>
+          <t>A 53343-2024</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2258,10 +2268,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45982</v>
+        <v>45614</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2274,7 +2284,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>0.6</v>
+        <v>0.9</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2317,7 +2327,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 58125-2025</t>
+          <t>A 34984-2024</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2331,10 +2341,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>45982</v>
+        <v>45527</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2347,7 +2357,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>0.8</v>
+        <v>4.1</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2390,7 +2400,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 54207-2025</t>
+          <t>A 35238-2026</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2400,14 +2410,14 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>45964</v>
+        <v>46260</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2420,7 +2430,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>2.1</v>
+        <v>3.3</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2463,7 +2473,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 55562-2022</t>
+          <t>A 37072-2025</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2477,10 +2487,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>44888</v>
+        <v>45875</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2493,7 +2503,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>0.8</v>
+        <v>1.5</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -2536,7 +2546,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 62831-2023</t>
+          <t>A 37076-2025</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2550,10 +2560,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>45270</v>
+        <v>45875</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2566,7 +2576,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>1.1</v>
+        <v>2.4</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -2609,7 +2619,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 26059-2026</t>
+          <t>A 13510-2025</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2623,10 +2633,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>46181</v>
+        <v>45736</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2639,7 +2649,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>4.7</v>
+        <v>2.5</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -2682,7 +2692,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 26060-2026</t>
+          <t>A 22072-2023</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2696,10 +2706,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>46181</v>
+        <v>45069</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -2712,7 +2722,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -2755,7 +2765,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 37109-2026</t>
+          <t>A 41863-2026</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2769,10 +2779,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>46274</v>
+        <v>46303</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -2785,7 +2795,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>3</v>
+        <v>1.9</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -2828,7 +2838,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 12077-2022</t>
+          <t>A 55562-2022</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2842,10 +2852,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>44636</v>
+        <v>44888</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -2858,7 +2868,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>2.1</v>
+        <v>0.8</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -2901,7 +2911,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 37407-2023</t>
+          <t>A 21049-2026</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2915,10 +2925,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>45156</v>
+        <v>46146</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -2931,7 +2941,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>3.3</v>
+        <v>2.9</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -2974,7 +2984,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 14149-2022</t>
+          <t>A 37109-2026</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2988,10 +2998,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>44651</v>
+        <v>46274</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3003,13 +3013,8 @@
           <t>HALLSTAHAMMAR</t>
         </is>
       </c>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I34" t="n">
-        <v>3.8</v>
+        <v>3</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3052,7 +3057,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 53343-2024</t>
+          <t>A 16762-2022</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3066,10 +3071,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>45614</v>
+        <v>44673</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3082,7 +3087,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>0.9</v>
+        <v>4.2</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3125,7 +3130,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 8848-2025</t>
+          <t>A 21972-2023</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3139,10 +3144,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45713</v>
+        <v>45068</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3155,7 +3160,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3198,7 +3203,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 35238-2026</t>
+          <t>A 35036-2024</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3208,14 +3213,14 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>46260</v>
+        <v>45527</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3228,7 +3233,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>3.3</v>
+        <v>1.7</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3271,7 +3276,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 8436-2023</t>
+          <t>A 62831-2023</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3285,10 +3290,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>44977</v>
+        <v>45270</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3300,13 +3305,8 @@
           <t>HALLSTAHAMMAR</t>
         </is>
       </c>
-      <c r="H38" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I38" t="n">
-        <v>4</v>
+        <v>1.1</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3349,7 +3349,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 41863-2026</t>
+          <t>A 8848-2025</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3363,10 +3363,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>46303</v>
+        <v>45713</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3379,7 +3379,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3422,7 +3422,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 7245-2025</t>
+          <t>A 30766-2022</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3436,10 +3436,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45702</v>
+        <v>44764</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3452,7 +3452,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>4</v>
+        <v>0.6</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -3495,7 +3495,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 34984-2024</t>
+          <t>A 7245-2025</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3509,10 +3509,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45527</v>
+        <v>45702</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3525,7 +3525,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -3585,7 +3585,7 @@
         <v>46091</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3658,7 +3658,7 @@
         <v>46111</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46318</v>
+        <v>46319</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>

--- a/Översikt HALLSTAHAMMAR.xlsx
+++ b/Översikt HALLSTAHAMMAR.xlsx
@@ -601,7 +601,7 @@
         <v>45978</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -713,7 +713,7 @@
         <v>44635</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -791,7 +791,7 @@
         <v>44887</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -864,7 +864,7 @@
         <v>44502</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -937,7 +937,7 @@
         <v>44502</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1010,7 +1010,7 @@
         <v>44739</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1083,7 +1083,7 @@
         <v>44502</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1156,7 +1156,7 @@
         <v>44977</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1234,7 +1234,7 @@
         <v>45909</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1307,7 +1307,7 @@
         <v>45964</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1380,7 +1380,7 @@
         <v>45911</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1453,7 +1453,7 @@
         <v>45915</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1526,7 +1526,7 @@
         <v>45365</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1604,7 +1604,7 @@
         <v>44705</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1682,7 +1682,7 @@
         <v>44636</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1755,7 +1755,7 @@
         <v>45156</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1828,7 +1828,7 @@
         <v>44651</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -1906,7 +1906,7 @@
         <v>45982</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -1979,7 +1979,7 @@
         <v>45982</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2052,7 +2052,7 @@
         <v>45982</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2125,7 +2125,7 @@
         <v>46181</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2198,7 +2198,7 @@
         <v>46181</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2271,7 +2271,7 @@
         <v>45614</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2344,7 +2344,7 @@
         <v>45527</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2417,7 +2417,7 @@
         <v>46260</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2490,7 +2490,7 @@
         <v>45875</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2563,7 +2563,7 @@
         <v>45875</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2636,7 +2636,7 @@
         <v>45736</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2709,7 +2709,7 @@
         <v>45069</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -2782,7 +2782,7 @@
         <v>46303</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -2855,7 +2855,7 @@
         <v>44888</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -2928,7 +2928,7 @@
         <v>46146</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3001,7 +3001,7 @@
         <v>46274</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3074,7 +3074,7 @@
         <v>44673</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3147,7 +3147,7 @@
         <v>45068</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3220,7 +3220,7 @@
         <v>45527</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3293,7 +3293,7 @@
         <v>45270</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3366,7 +3366,7 @@
         <v>45713</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3439,7 +3439,7 @@
         <v>44764</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3512,7 +3512,7 @@
         <v>45702</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3585,7 +3585,7 @@
         <v>46091</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3658,7 +3658,7 @@
         <v>46111</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>

--- a/Översikt HALLSTAHAMMAR.xlsx
+++ b/Översikt HALLSTAHAMMAR.xlsx
@@ -601,7 +601,7 @@
         <v>45978</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -628,7 +628,7 @@
         <v>2</v>
       </c>
       <c r="L2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M2" t="n">
         <v>0</v>
@@ -643,23 +643,24 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R2" t="n">
         <v>0</v>
       </c>
       <c r="S2" t="n">
+        <v>4</v>
+      </c>
+      <c r="T2" t="n">
+        <v>9</v>
+      </c>
+      <c r="U2" t="n">
         <v>3</v>
       </c>
-      <c r="T2" t="n">
-        <v>6</v>
-      </c>
-      <c r="U2" t="n">
-        <v>0</v>
-      </c>
       <c r="V2" s="2" t="inlineStr">
         <is>
           <t>Dofttaggsvamp
+Kandelabersvamp
 Brandticka
 Trådticka</t>
         </is>
@@ -713,7 +714,7 @@
         <v>44635</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -791,7 +792,7 @@
         <v>44887</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -864,7 +865,7 @@
         <v>44502</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -937,7 +938,7 @@
         <v>44502</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1010,7 +1011,7 @@
         <v>44739</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1083,7 +1084,7 @@
         <v>44502</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1156,7 +1157,7 @@
         <v>44977</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1234,7 +1235,7 @@
         <v>45909</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1307,7 +1308,7 @@
         <v>45964</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1380,7 +1381,7 @@
         <v>45911</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1453,7 +1454,7 @@
         <v>45915</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1526,7 +1527,7 @@
         <v>45365</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1604,7 +1605,7 @@
         <v>44705</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1682,7 +1683,7 @@
         <v>44636</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1755,7 +1756,7 @@
         <v>45156</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1828,7 +1829,7 @@
         <v>44651</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -1906,7 +1907,7 @@
         <v>45982</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -1979,7 +1980,7 @@
         <v>45982</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2052,7 +2053,7 @@
         <v>45982</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2125,7 +2126,7 @@
         <v>46181</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2198,7 +2199,7 @@
         <v>46181</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2271,7 +2272,7 @@
         <v>45614</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2344,7 +2345,7 @@
         <v>45527</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2417,7 +2418,7 @@
         <v>46260</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2490,7 +2491,7 @@
         <v>45875</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2563,7 +2564,7 @@
         <v>45875</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2636,7 +2637,7 @@
         <v>45736</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2709,7 +2710,7 @@
         <v>45069</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -2782,7 +2783,7 @@
         <v>46303</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -2855,7 +2856,7 @@
         <v>44888</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -2928,7 +2929,7 @@
         <v>46146</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -3001,7 +3002,7 @@
         <v>46274</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3074,7 +3075,7 @@
         <v>44673</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3147,7 +3148,7 @@
         <v>45068</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3220,7 +3221,7 @@
         <v>45527</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3293,7 +3294,7 @@
         <v>45270</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3366,7 +3367,7 @@
         <v>45713</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3439,7 +3440,7 @@
         <v>44764</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3512,7 +3513,7 @@
         <v>45702</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3585,7 +3586,7 @@
         <v>46091</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3658,7 +3659,7 @@
         <v>46111</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>

--- a/Översikt HALLSTAHAMMAR.xlsx
+++ b/Översikt HALLSTAHAMMAR.xlsx
@@ -601,7 +601,7 @@
         <v>45978</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -714,7 +714,7 @@
         <v>44635</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -792,7 +792,7 @@
         <v>44887</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -865,7 +865,7 @@
         <v>44502</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -938,7 +938,7 @@
         <v>44502</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1011,7 +1011,7 @@
         <v>44739</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1084,7 +1084,7 @@
         <v>44502</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1140,7 +1140,7 @@
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 8436-2023</t>
+          <t>A 21264-2022</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1154,10 +1154,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>44977</v>
+        <v>44705</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1171,11 +1171,11 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Kyrkan</t>
+          <t>Allmännings- och besparingsskogar</t>
         </is>
       </c>
       <c r="I9" t="n">
-        <v>4</v>
+        <v>2.4</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -1218,7 +1218,7 @@
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 42991-2025</t>
+          <t>A 21972-2023</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1232,10 +1232,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>45909</v>
+        <v>45068</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1248,7 +1248,7 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>7.2</v>
+        <v>1.5</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
@@ -1291,7 +1291,7 @@
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 54207-2025</t>
+          <t>A 42991-2025</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1305,10 +1305,10 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>45964</v>
+        <v>45909</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1321,7 +1321,7 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>2.1</v>
+        <v>7.2</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -1381,7 +1381,7 @@
         <v>45911</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1454,7 +1454,7 @@
         <v>45915</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1510,7 +1510,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 10263-2024</t>
+          <t>A 62831-2023</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1524,10 +1524,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>45365</v>
+        <v>45270</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1539,13 +1539,8 @@
           <t>HALLSTAHAMMAR</t>
         </is>
       </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I14" t="n">
-        <v>1.4</v>
+        <v>1.1</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -1588,7 +1583,7 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 21264-2022</t>
+          <t>A 10263-2024</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1602,10 +1597,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>44705</v>
+        <v>45365</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1619,11 +1614,11 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Allmännings- och besparingsskogar</t>
+          <t>Kyrkan</t>
         </is>
       </c>
       <c r="I15" t="n">
-        <v>2.4</v>
+        <v>1.4</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -1666,7 +1661,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 12077-2022</t>
+          <t>A 55562-2022</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1680,10 +1675,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>44636</v>
+        <v>44888</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1696,7 +1691,7 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>2.1</v>
+        <v>0.8</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -1739,7 +1734,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 37407-2023</t>
+          <t>A 58109-2025</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1753,10 +1748,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>45156</v>
+        <v>45982</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1769,7 +1764,7 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>3.3</v>
+        <v>2.5</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -1812,7 +1807,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 14149-2022</t>
+          <t>A 58111-2025</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1826,10 +1821,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>44651</v>
+        <v>45982</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -1841,13 +1836,8 @@
           <t>HALLSTAHAMMAR</t>
         </is>
       </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I18" t="n">
-        <v>3.8</v>
+        <v>0.6</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -1907,7 +1897,7 @@
         <v>45982</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -1963,7 +1953,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 58109-2025</t>
+          <t>A 12077-2022</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1977,10 +1967,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>45982</v>
+        <v>44636</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -1993,7 +1983,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>2.5</v>
+        <v>2.1</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2036,7 +2026,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 58111-2025</t>
+          <t>A 37407-2023</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2050,10 +2040,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>45982</v>
+        <v>45156</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2066,7 +2056,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>0.6</v>
+        <v>3.3</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2126,7 +2116,7 @@
         <v>46181</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2199,7 +2189,7 @@
         <v>46181</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2255,7 +2245,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 53343-2024</t>
+          <t>A 37072-2025</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2269,10 +2259,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45614</v>
+        <v>45875</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2285,7 +2275,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>0.9</v>
+        <v>1.5</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2328,7 +2318,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 34984-2024</t>
+          <t>A 37076-2025</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2342,10 +2332,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>45527</v>
+        <v>45875</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2358,7 +2348,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>4.1</v>
+        <v>2.4</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2401,7 +2391,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 35238-2026</t>
+          <t>A 13510-2025</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2411,14 +2401,14 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>46260</v>
+        <v>45736</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2431,7 +2421,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>3.3</v>
+        <v>2.5</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2474,7 +2464,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 37072-2025</t>
+          <t>A 14149-2022</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2488,10 +2478,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>45875</v>
+        <v>44651</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2503,8 +2493,13 @@
           <t>HALLSTAHAMMAR</t>
         </is>
       </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I27" t="n">
-        <v>1.5</v>
+        <v>3.8</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -2547,7 +2542,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 37076-2025</t>
+          <t>A 53343-2024</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2561,10 +2556,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>45875</v>
+        <v>45614</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2577,7 +2572,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>2.4</v>
+        <v>0.9</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -2620,7 +2615,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 13510-2025</t>
+          <t>A 8436-2023</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2634,10 +2629,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>45736</v>
+        <v>44977</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2649,8 +2644,13 @@
           <t>HALLSTAHAMMAR</t>
         </is>
       </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I29" t="n">
-        <v>2.5</v>
+        <v>4</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -2693,7 +2693,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 22072-2023</t>
+          <t>A 7245-2025</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2707,10 +2707,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>45069</v>
+        <v>45702</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -2723,7 +2723,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>3.5</v>
+        <v>4</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -2766,7 +2766,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 41863-2026</t>
+          <t>A 34984-2024</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2780,10 +2780,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>46303</v>
+        <v>45527</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -2796,7 +2796,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>1.9</v>
+        <v>4.1</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -2839,7 +2839,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 55562-2022</t>
+          <t>A 21049-2026</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2853,10 +2853,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>44888</v>
+        <v>46146</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -2869,7 +2869,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>0.8</v>
+        <v>2.9</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -2912,7 +2912,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 21049-2026</t>
+          <t>A 54207-2025</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2926,10 +2926,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>46146</v>
+        <v>45964</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -2942,7 +2942,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>2.9</v>
+        <v>2.1</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -2985,7 +2985,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 37109-2026</t>
+          <t>A 16762-2022</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2999,10 +2999,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>46274</v>
+        <v>44673</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3015,7 +3015,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>3</v>
+        <v>4.2</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3058,7 +3058,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 16762-2022</t>
+          <t>A 22072-2023</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3072,10 +3072,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>44673</v>
+        <v>45069</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3088,7 +3088,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>4.2</v>
+        <v>3.5</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3131,7 +3131,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 21972-2023</t>
+          <t>A 30766-2022</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3145,10 +3145,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>45068</v>
+        <v>44764</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3161,7 +3161,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>1.5</v>
+        <v>0.6</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3204,7 +3204,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 35036-2024</t>
+          <t>A 35238-2026</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3214,14 +3214,14 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>45527</v>
+        <v>46260</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3234,7 +3234,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>1.7</v>
+        <v>3.3</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3277,7 +3277,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 62831-2023</t>
+          <t>A 35036-2024</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3291,10 +3291,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45270</v>
+        <v>45527</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3307,7 +3307,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>1.1</v>
+        <v>1.7</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3350,7 +3350,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 8848-2025</t>
+          <t>A 41863-2026</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3364,10 +3364,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45713</v>
+        <v>46303</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3380,7 +3380,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3423,7 +3423,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 30766-2022</t>
+          <t>A 37109-2026</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3437,10 +3437,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>44764</v>
+        <v>46274</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3453,7 +3453,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>0.6</v>
+        <v>3</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -3496,7 +3496,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 7245-2025</t>
+          <t>A 8848-2025</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3510,10 +3510,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45702</v>
+        <v>45713</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3526,7 +3526,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -3586,7 +3586,7 @@
         <v>46091</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3659,7 +3659,7 @@
         <v>46111</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46321</v>
+        <v>46322</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>

--- a/Översikt HALLSTAHAMMAR.xlsx
+++ b/Översikt HALLSTAHAMMAR.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE43"/>
+  <dimension ref="A1:AE45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="0" ht="15" customHeight="1"/>
@@ -601,7 +601,7 @@
         <v>45978</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -714,7 +714,7 @@
         <v>44635</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -792,7 +792,7 @@
         <v>44887</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -865,7 +865,7 @@
         <v>44502</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -938,7 +938,7 @@
         <v>44502</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1011,7 +1011,7 @@
         <v>44739</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1067,7 +1067,7 @@
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A 68621-2021</t>
+          <t>A 16762-2022</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1081,10 +1081,10 @@
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>44502</v>
+        <v>44673</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1097,7 +1097,7 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>3.8</v>
+        <v>4.2</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -1140,7 +1140,7 @@
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 21264-2022</t>
+          <t>A 68621-2021</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1154,10 +1154,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>44705</v>
+        <v>44502</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1169,13 +1169,8 @@
           <t>HALLSTAHAMMAR</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I9" t="n">
-        <v>2.4</v>
+        <v>3.8</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -1218,7 +1213,7 @@
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 21972-2023</t>
+          <t>A 14149-2022</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1232,10 +1227,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>45068</v>
+        <v>44651</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1247,8 +1242,13 @@
           <t>HALLSTAHAMMAR</t>
         </is>
       </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I10" t="n">
-        <v>1.5</v>
+        <v>3.8</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
@@ -1291,7 +1291,7 @@
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 42991-2025</t>
+          <t>A 10263-2024</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1305,10 +1305,10 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>45909</v>
+        <v>45365</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1320,8 +1320,13 @@
           <t>HALLSTAHAMMAR</t>
         </is>
       </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I11" t="n">
-        <v>7.2</v>
+        <v>1.4</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -1364,7 +1369,7 @@
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 43448-2025</t>
+          <t>A 53343-2024</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1378,10 +1383,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>45911</v>
+        <v>45614</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1394,7 +1399,7 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>1.2</v>
+        <v>0.9</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -1437,7 +1442,7 @@
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 44192-2025</t>
+          <t>A 34984-2024</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1451,10 +1456,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>45915</v>
+        <v>45527</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1467,7 +1472,7 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>0.8</v>
+        <v>4.1</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
@@ -1510,7 +1515,7 @@
     <row r="14" ht="15" customHeight="1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A 62831-2023</t>
+          <t>A 42991-2025</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1524,10 +1529,10 @@
         </is>
       </c>
       <c r="D14" s="1" t="n">
-        <v>45270</v>
+        <v>45909</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1540,7 +1545,7 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>1.1</v>
+        <v>7.2</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -1583,7 +1588,7 @@
     <row r="15" ht="15" customHeight="1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A 10263-2024</t>
+          <t>A 43448-2025</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1597,10 +1602,10 @@
         </is>
       </c>
       <c r="D15" s="1" t="n">
-        <v>45365</v>
+        <v>45911</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1612,13 +1617,8 @@
           <t>HALLSTAHAMMAR</t>
         </is>
       </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I15" t="n">
-        <v>1.4</v>
+        <v>1.2</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -1661,7 +1661,7 @@
     <row r="16" ht="15" customHeight="1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A 55562-2022</t>
+          <t>A 44192-2025</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1675,10 +1675,10 @@
         </is>
       </c>
       <c r="D16" s="1" t="n">
-        <v>44888</v>
+        <v>45915</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1734,7 +1734,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 58109-2025</t>
+          <t>A 21972-2023</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1748,10 +1748,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>45982</v>
+        <v>45068</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1764,7 +1764,7 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>2.5</v>
+        <v>1.5</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -1807,7 +1807,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 58111-2025</t>
+          <t>A 22072-2023</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1821,10 +1821,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>45982</v>
+        <v>45069</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -1837,7 +1837,7 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>0.6</v>
+        <v>3.5</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -1880,7 +1880,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 58125-2025</t>
+          <t>A 35036-2024</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1894,10 +1894,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>45982</v>
+        <v>45527</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -1910,7 +1910,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>0.8</v>
+        <v>1.7</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -1953,7 +1953,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 12077-2022</t>
+          <t>A 62831-2023</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1967,10 +1967,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>44636</v>
+        <v>45270</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -1983,7 +1983,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>2.1</v>
+        <v>1.1</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2026,7 +2026,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 37407-2023</t>
+          <t>A 55562-2022</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2040,10 +2040,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>45156</v>
+        <v>44888</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2056,7 +2056,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>3.3</v>
+        <v>0.8</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2099,7 +2099,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 26059-2026</t>
+          <t>A 58125-2025</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2113,10 +2113,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>46181</v>
+        <v>45982</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2129,7 +2129,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>4.7</v>
+        <v>0.8</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2172,7 +2172,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 26060-2026</t>
+          <t>A 58109-2025</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2186,10 +2186,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>46181</v>
+        <v>45982</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2202,7 +2202,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>3.6</v>
+        <v>2.5</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2245,7 +2245,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 37072-2025</t>
+          <t>A 58111-2025</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2259,10 +2259,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45875</v>
+        <v>45982</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2275,7 +2275,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>1.5</v>
+        <v>0.6</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2318,7 +2318,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 37076-2025</t>
+          <t>A 30766-2022</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2332,10 +2332,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>45875</v>
+        <v>44764</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2348,7 +2348,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>2.4</v>
+        <v>0.6</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2391,7 +2391,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 13510-2025</t>
+          <t>A 26059-2026</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2405,10 +2405,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>45736</v>
+        <v>46181</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2421,7 +2421,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>2.5</v>
+        <v>4.7</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2464,7 +2464,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 14149-2022</t>
+          <t>A 26060-2026</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2478,10 +2478,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>44651</v>
+        <v>46181</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2493,13 +2493,8 @@
           <t>HALLSTAHAMMAR</t>
         </is>
       </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I27" t="n">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -2542,7 +2537,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 53343-2024</t>
+          <t>A 7245-2025</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2556,10 +2551,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>45614</v>
+        <v>45702</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2572,7 +2567,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>0.9</v>
+        <v>4</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -2632,7 +2627,7 @@
         <v>44977</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2693,7 +2688,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 7245-2025</t>
+          <t>A 35238-2026</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2703,14 +2698,14 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>45702</v>
+        <v>46260</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -2723,7 +2718,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>4</v>
+        <v>3.3</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -2766,7 +2761,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 34984-2024</t>
+          <t>A 21264-2022</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2780,10 +2775,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>45527</v>
+        <v>44705</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -2795,8 +2790,13 @@
           <t>HALLSTAHAMMAR</t>
         </is>
       </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I31" t="n">
-        <v>4.1</v>
+        <v>2.4</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -2839,7 +2839,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 21049-2026</t>
+          <t>A 12077-2022</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2853,10 +2853,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>46146</v>
+        <v>44636</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -2869,7 +2869,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>2.9</v>
+        <v>2.1</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -2912,7 +2912,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 54207-2025</t>
+          <t>A 41863-2026</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2926,10 +2926,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>45964</v>
+        <v>46303</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -2942,7 +2942,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>2.1</v>
+        <v>1.9</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -2985,7 +2985,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 16762-2022</t>
+          <t>A 37407-2023</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2999,10 +2999,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>44673</v>
+        <v>45156</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3015,7 +3015,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>4.2</v>
+        <v>3.3</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3058,7 +3058,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 22072-2023</t>
+          <t>A 21049-2026</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3072,10 +3072,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>45069</v>
+        <v>46146</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3088,7 +3088,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>3.5</v>
+        <v>2.9</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3131,7 +3131,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 30766-2022</t>
+          <t>A 37109-2026</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3145,10 +3145,10 @@
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>44764</v>
+        <v>46274</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3161,7 +3161,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>0.6</v>
+        <v>3</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3204,7 +3204,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 35238-2026</t>
+          <t>A 44661-2026</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3214,14 +3214,14 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>46260</v>
+        <v>46322</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3234,7 +3234,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>3.3</v>
+        <v>0.8</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3277,7 +3277,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 35036-2024</t>
+          <t>A 44636-2026</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3291,10 +3291,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>45527</v>
+        <v>46322</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3307,7 +3307,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3350,7 +3350,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 41863-2026</t>
+          <t>A 8848-2025</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3364,10 +3364,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>46303</v>
+        <v>45713</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3380,7 +3380,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3423,7 +3423,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 37109-2026</t>
+          <t>A 54207-2025</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3437,10 +3437,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>46274</v>
+        <v>45964</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3453,7 +3453,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>3</v>
+        <v>2.1</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -3496,7 +3496,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 8848-2025</t>
+          <t>A 37072-2025</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3510,10 +3510,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45713</v>
+        <v>45875</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3526,7 +3526,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -3569,153 +3569,299 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
+          <t>A 37076-2025</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D42" s="1" t="n">
+        <v>45875</v>
+      </c>
+      <c r="E42" s="1" t="n">
+        <v>46323</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>VÄSTMANLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>HALLSTAHAMMAR</t>
+        </is>
+      </c>
+      <c r="I42" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="J42" t="n">
+        <v>0</v>
+      </c>
+      <c r="K42" t="n">
+        <v>0</v>
+      </c>
+      <c r="L42" t="n">
+        <v>0</v>
+      </c>
+      <c r="M42" t="n">
+        <v>0</v>
+      </c>
+      <c r="N42" t="n">
+        <v>0</v>
+      </c>
+      <c r="O42" t="n">
+        <v>0</v>
+      </c>
+      <c r="P42" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q42" t="n">
+        <v>0</v>
+      </c>
+      <c r="R42" t="n">
+        <v>0</v>
+      </c>
+      <c r="S42" t="n">
+        <v>0</v>
+      </c>
+      <c r="T42" t="n">
+        <v>0</v>
+      </c>
+      <c r="U42" t="n">
+        <v>0</v>
+      </c>
+      <c r="V42" s="2" t="inlineStr"/>
+    </row>
+    <row r="43" ht="15" customHeight="1">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>A 13510-2025</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D43" s="1" t="n">
+        <v>45736</v>
+      </c>
+      <c r="E43" s="1" t="n">
+        <v>46323</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>VÄSTMANLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>HALLSTAHAMMAR</t>
+        </is>
+      </c>
+      <c r="I43" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="J43" t="n">
+        <v>0</v>
+      </c>
+      <c r="K43" t="n">
+        <v>0</v>
+      </c>
+      <c r="L43" t="n">
+        <v>0</v>
+      </c>
+      <c r="M43" t="n">
+        <v>0</v>
+      </c>
+      <c r="N43" t="n">
+        <v>0</v>
+      </c>
+      <c r="O43" t="n">
+        <v>0</v>
+      </c>
+      <c r="P43" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q43" t="n">
+        <v>0</v>
+      </c>
+      <c r="R43" t="n">
+        <v>0</v>
+      </c>
+      <c r="S43" t="n">
+        <v>0</v>
+      </c>
+      <c r="T43" t="n">
+        <v>0</v>
+      </c>
+      <c r="U43" t="n">
+        <v>0</v>
+      </c>
+      <c r="V43" s="2" t="inlineStr"/>
+    </row>
+    <row r="44" ht="15" customHeight="1">
+      <c r="A44" t="inlineStr">
+        <is>
           <t>S 697-2026</t>
         </is>
       </c>
-      <c r="B42" t="inlineStr">
+      <c r="B44" t="inlineStr">
         <is>
           <t>samrådsanmälan</t>
         </is>
       </c>
-      <c r="C42" t="inlineStr">
+      <c r="C44" t="inlineStr">
         <is>
           <t>Skogsgödsling</t>
         </is>
       </c>
-      <c r="D42" s="1" t="n">
+      <c r="D44" s="1" t="n">
         <v>46091</v>
       </c>
-      <c r="E42" s="1" t="n">
-        <v>46322</v>
-      </c>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>VÄSTMANLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G42" t="inlineStr">
-        <is>
-          <t>HALLSTAHAMMAR</t>
-        </is>
-      </c>
-      <c r="I42" t="n">
+      <c r="E44" s="1" t="n">
+        <v>46323</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>VÄSTMANLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>HALLSTAHAMMAR</t>
+        </is>
+      </c>
+      <c r="I44" t="n">
         <v>32.5</v>
       </c>
-      <c r="J42" t="n">
-        <v>0</v>
-      </c>
-      <c r="K42" t="n">
-        <v>0</v>
-      </c>
-      <c r="L42" t="n">
-        <v>0</v>
-      </c>
-      <c r="M42" t="n">
-        <v>0</v>
-      </c>
-      <c r="N42" t="n">
-        <v>0</v>
-      </c>
-      <c r="O42" t="n">
-        <v>0</v>
-      </c>
-      <c r="P42" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q42" t="n">
-        <v>0</v>
-      </c>
-      <c r="R42" t="n">
-        <v>0</v>
-      </c>
-      <c r="S42" t="n">
-        <v>0</v>
-      </c>
-      <c r="T42" t="n">
-        <v>0</v>
-      </c>
-      <c r="U42" t="n">
-        <v>0</v>
-      </c>
-      <c r="V42" s="2" t="inlineStr"/>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
+      <c r="J44" t="n">
+        <v>0</v>
+      </c>
+      <c r="K44" t="n">
+        <v>0</v>
+      </c>
+      <c r="L44" t="n">
+        <v>0</v>
+      </c>
+      <c r="M44" t="n">
+        <v>0</v>
+      </c>
+      <c r="N44" t="n">
+        <v>0</v>
+      </c>
+      <c r="O44" t="n">
+        <v>0</v>
+      </c>
+      <c r="P44" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q44" t="n">
+        <v>0</v>
+      </c>
+      <c r="R44" t="n">
+        <v>0</v>
+      </c>
+      <c r="S44" t="n">
+        <v>0</v>
+      </c>
+      <c r="T44" t="n">
+        <v>0</v>
+      </c>
+      <c r="U44" t="n">
+        <v>0</v>
+      </c>
+      <c r="V44" s="2" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
         <is>
           <t>S 924-2026</t>
         </is>
       </c>
-      <c r="B43" t="inlineStr">
+      <c r="B45" t="inlineStr">
         <is>
           <t>samrådsanmälan</t>
         </is>
       </c>
-      <c r="C43" t="inlineStr">
+      <c r="C45" t="inlineStr">
         <is>
           <t>Skogsgödsling</t>
         </is>
       </c>
-      <c r="D43" s="1" t="n">
+      <c r="D45" s="1" t="n">
         <v>46111</v>
       </c>
-      <c r="E43" s="1" t="n">
-        <v>46322</v>
-      </c>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>VÄSTMANLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G43" t="inlineStr">
-        <is>
-          <t>HALLSTAHAMMAR</t>
-        </is>
-      </c>
-      <c r="H43" t="inlineStr">
+      <c r="E45" s="1" t="n">
+        <v>46323</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>VÄSTMANLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>HALLSTAHAMMAR</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
         <is>
           <t>Allmännings- och besparingsskogar</t>
         </is>
       </c>
-      <c r="I43" t="n">
+      <c r="I45" t="n">
         <v>48.8</v>
       </c>
-      <c r="J43" t="n">
-        <v>0</v>
-      </c>
-      <c r="K43" t="n">
-        <v>0</v>
-      </c>
-      <c r="L43" t="n">
-        <v>0</v>
-      </c>
-      <c r="M43" t="n">
-        <v>0</v>
-      </c>
-      <c r="N43" t="n">
-        <v>0</v>
-      </c>
-      <c r="O43" t="n">
-        <v>0</v>
-      </c>
-      <c r="P43" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q43" t="n">
-        <v>0</v>
-      </c>
-      <c r="R43" t="n">
-        <v>0</v>
-      </c>
-      <c r="S43" t="n">
-        <v>0</v>
-      </c>
-      <c r="T43" t="n">
-        <v>0</v>
-      </c>
-      <c r="U43" t="n">
-        <v>0</v>
-      </c>
-      <c r="V43" s="2" t="inlineStr"/>
+      <c r="J45" t="n">
+        <v>0</v>
+      </c>
+      <c r="K45" t="n">
+        <v>0</v>
+      </c>
+      <c r="L45" t="n">
+        <v>0</v>
+      </c>
+      <c r="M45" t="n">
+        <v>0</v>
+      </c>
+      <c r="N45" t="n">
+        <v>0</v>
+      </c>
+      <c r="O45" t="n">
+        <v>0</v>
+      </c>
+      <c r="P45" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q45" t="n">
+        <v>0</v>
+      </c>
+      <c r="R45" t="n">
+        <v>0</v>
+      </c>
+      <c r="S45" t="n">
+        <v>0</v>
+      </c>
+      <c r="T45" t="n">
+        <v>0</v>
+      </c>
+      <c r="U45" t="n">
+        <v>0</v>
+      </c>
+      <c r="V45" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Översikt HALLSTAHAMMAR.xlsx
+++ b/Översikt HALLSTAHAMMAR.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE45"/>
+  <dimension ref="A1:AE46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="0" ht="15" customHeight="1"/>
@@ -601,7 +601,7 @@
         <v>45978</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -714,7 +714,7 @@
         <v>44635</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -792,7 +792,7 @@
         <v>44887</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -865,7 +865,7 @@
         <v>44502</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -938,7 +938,7 @@
         <v>44502</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1011,7 +1011,7 @@
         <v>44739</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1067,7 +1067,7 @@
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A 16762-2022</t>
+          <t>A 8436-2023</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1081,10 +1081,10 @@
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>44673</v>
+        <v>44977</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1096,8 +1096,13 @@
           <t>HALLSTAHAMMAR</t>
         </is>
       </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I8" t="n">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -1157,7 +1162,7 @@
         <v>44502</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1213,7 +1218,7 @@
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 14149-2022</t>
+          <t>A 7245-2025</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1227,10 +1232,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>44651</v>
+        <v>45702</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1242,13 +1247,8 @@
           <t>HALLSTAHAMMAR</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I10" t="n">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
@@ -1291,7 +1291,7 @@
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 10263-2024</t>
+          <t>A 21264-2022</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1305,10 +1305,10 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>45365</v>
+        <v>44705</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1322,11 +1322,11 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Kyrkan</t>
+          <t>Allmännings- och besparingsskogar</t>
         </is>
       </c>
       <c r="I11" t="n">
-        <v>1.4</v>
+        <v>2.4</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -1369,7 +1369,7 @@
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 53343-2024</t>
+          <t>A 34984-2024</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1383,10 +1383,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>45614</v>
+        <v>45527</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1399,7 +1399,7 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>0.9</v>
+        <v>4.1</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -1442,7 +1442,7 @@
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 34984-2024</t>
+          <t>A 21972-2023</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1456,10 +1456,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>45527</v>
+        <v>45068</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1472,7 +1472,7 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>4.1</v>
+        <v>1.5</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
@@ -1532,7 +1532,7 @@
         <v>45909</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1605,7 +1605,7 @@
         <v>45911</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1678,7 +1678,7 @@
         <v>45915</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1734,7 +1734,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 21972-2023</t>
+          <t>A 16762-2022</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1748,10 +1748,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>45068</v>
+        <v>44673</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1764,7 +1764,7 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>1.5</v>
+        <v>4.2</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -1807,7 +1807,7 @@
     <row r="18" ht="15" customHeight="1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A 22072-2023</t>
+          <t>A 37072-2025</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1821,10 +1821,10 @@
         </is>
       </c>
       <c r="D18" s="1" t="n">
-        <v>45069</v>
+        <v>45875</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -1837,7 +1837,7 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>3.5</v>
+        <v>1.5</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -1880,7 +1880,7 @@
     <row r="19" ht="15" customHeight="1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A 35036-2024</t>
+          <t>A 37076-2025</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1894,10 +1894,10 @@
         </is>
       </c>
       <c r="D19" s="1" t="n">
-        <v>45527</v>
+        <v>45875</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -1910,7 +1910,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>1.7</v>
+        <v>2.4</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -1953,7 +1953,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 62831-2023</t>
+          <t>A 22072-2023</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1967,10 +1967,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>45270</v>
+        <v>45069</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -1983,7 +1983,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>1.1</v>
+        <v>3.5</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2026,7 +2026,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 55562-2022</t>
+          <t>A 13510-2025</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2040,10 +2040,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>44888</v>
+        <v>45736</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2056,7 +2056,7 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>0.8</v>
+        <v>2.5</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -2099,7 +2099,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 58125-2025</t>
+          <t>A 30766-2022</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2113,10 +2113,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>45982</v>
+        <v>44764</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2129,7 +2129,7 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -2172,7 +2172,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 58109-2025</t>
+          <t>A 21049-2026</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2186,10 +2186,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>45982</v>
+        <v>46146</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2202,7 +2202,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>2.5</v>
+        <v>2.9</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2245,7 +2245,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 58111-2025</t>
+          <t>A 35036-2024</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2259,10 +2259,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45982</v>
+        <v>45527</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2275,7 +2275,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>0.6</v>
+        <v>1.7</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2318,7 +2318,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 30766-2022</t>
+          <t>A 58109-2025</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2332,10 +2332,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>44764</v>
+        <v>45982</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2348,7 +2348,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>0.6</v>
+        <v>2.5</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2391,7 +2391,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 26059-2026</t>
+          <t>A 58111-2025</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2405,10 +2405,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>46181</v>
+        <v>45982</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2421,7 +2421,7 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>4.7</v>
+        <v>0.6</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2464,7 +2464,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 26060-2026</t>
+          <t>A 58125-2025</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2478,10 +2478,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>46181</v>
+        <v>45982</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2494,7 +2494,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>3.6</v>
+        <v>0.8</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -2537,7 +2537,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 7245-2025</t>
+          <t>A 54207-2025</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2551,10 +2551,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>45702</v>
+        <v>45964</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2567,7 +2567,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>4</v>
+        <v>2.1</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -2610,7 +2610,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 8436-2023</t>
+          <t>A 10263-2024</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2624,10 +2624,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>44977</v>
+        <v>45365</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2645,7 +2645,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>4</v>
+        <v>1.4</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -2688,7 +2688,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 35238-2026</t>
+          <t>A 55562-2022</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2698,14 +2698,14 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>46260</v>
+        <v>44888</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -2718,7 +2718,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>3.3</v>
+        <v>0.8</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -2761,7 +2761,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 21264-2022</t>
+          <t>A 26059-2026</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2775,10 +2775,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>44705</v>
+        <v>46181</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -2790,13 +2790,8 @@
           <t>HALLSTAHAMMAR</t>
         </is>
       </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I31" t="n">
-        <v>2.4</v>
+        <v>4.7</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -2839,7 +2834,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 12077-2022</t>
+          <t>A 26060-2026</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2853,10 +2848,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>44636</v>
+        <v>46181</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -2869,7 +2864,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>2.1</v>
+        <v>3.6</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -2912,7 +2907,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 41863-2026</t>
+          <t>A 62831-2023</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2926,10 +2921,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>46303</v>
+        <v>45270</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -2942,7 +2937,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>1.9</v>
+        <v>1.1</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -2985,7 +2980,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 37407-2023</t>
+          <t>A 12077-2022</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2999,10 +2994,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>45156</v>
+        <v>44636</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3015,7 +3010,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>3.3</v>
+        <v>2.1</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3058,7 +3053,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 21049-2026</t>
+          <t>A 37407-2023</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3072,10 +3067,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>46146</v>
+        <v>45156</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3088,7 +3083,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>2.9</v>
+        <v>3.3</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3131,7 +3126,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 37109-2026</t>
+          <t>A 35238-2026</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3141,14 +3136,14 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>46274</v>
+        <v>46260</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3161,7 +3156,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>3</v>
+        <v>3.3</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3204,7 +3199,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 44661-2026</t>
+          <t>A 41863-2026</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3218,10 +3213,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>46322</v>
+        <v>46303</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3234,7 +3229,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>0.8</v>
+        <v>1.9</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3277,7 +3272,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 44636-2026</t>
+          <t>A 37109-2026</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3291,10 +3286,10 @@
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>46322</v>
+        <v>46274</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3307,7 +3302,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>1.8</v>
+        <v>3</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3350,7 +3345,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 8848-2025</t>
+          <t>A 14149-2022</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3364,10 +3359,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>45713</v>
+        <v>44651</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3379,8 +3374,13 @@
           <t>HALLSTAHAMMAR</t>
         </is>
       </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I39" t="n">
-        <v>2</v>
+        <v>3.8</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3423,7 +3423,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 54207-2025</t>
+          <t>A 8848-2025</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3437,10 +3437,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45964</v>
+        <v>45713</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3453,7 +3453,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -3496,7 +3496,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 37072-2025</t>
+          <t>A 53343-2024</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3510,10 +3510,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45875</v>
+        <v>45614</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3526,7 +3526,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>1.5</v>
+        <v>0.9</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -3569,7 +3569,7 @@
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 37076-2025</t>
+          <t>A 44661-2026</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3583,10 +3583,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>45875</v>
+        <v>46322</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3599,7 +3599,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>2.4</v>
+        <v>0.8</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -3642,7 +3642,7 @@
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 13510-2025</t>
+          <t>A 44636-2026</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3656,10 +3656,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45736</v>
+        <v>46322</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -3672,7 +3672,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>2.5</v>
+        <v>1.8</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -3715,153 +3715,226 @@
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
+          <t>A 44662-2026</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D44" s="1" t="n">
+        <v>46322</v>
+      </c>
+      <c r="E44" s="1" t="n">
+        <v>46324</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>VÄSTMANLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>HALLSTAHAMMAR</t>
+        </is>
+      </c>
+      <c r="I44" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="J44" t="n">
+        <v>0</v>
+      </c>
+      <c r="K44" t="n">
+        <v>0</v>
+      </c>
+      <c r="L44" t="n">
+        <v>0</v>
+      </c>
+      <c r="M44" t="n">
+        <v>0</v>
+      </c>
+      <c r="N44" t="n">
+        <v>0</v>
+      </c>
+      <c r="O44" t="n">
+        <v>0</v>
+      </c>
+      <c r="P44" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q44" t="n">
+        <v>0</v>
+      </c>
+      <c r="R44" t="n">
+        <v>0</v>
+      </c>
+      <c r="S44" t="n">
+        <v>0</v>
+      </c>
+      <c r="T44" t="n">
+        <v>0</v>
+      </c>
+      <c r="U44" t="n">
+        <v>0</v>
+      </c>
+      <c r="V44" s="2" t="inlineStr"/>
+    </row>
+    <row r="45" ht="15" customHeight="1">
+      <c r="A45" t="inlineStr">
+        <is>
           <t>S 697-2026</t>
         </is>
       </c>
-      <c r="B44" t="inlineStr">
+      <c r="B45" t="inlineStr">
         <is>
           <t>samrådsanmälan</t>
         </is>
       </c>
-      <c r="C44" t="inlineStr">
+      <c r="C45" t="inlineStr">
         <is>
           <t>Skogsgödsling</t>
         </is>
       </c>
-      <c r="D44" s="1" t="n">
+      <c r="D45" s="1" t="n">
         <v>46091</v>
       </c>
-      <c r="E44" s="1" t="n">
-        <v>46323</v>
-      </c>
-      <c r="F44" t="inlineStr">
-        <is>
-          <t>VÄSTMANLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G44" t="inlineStr">
-        <is>
-          <t>HALLSTAHAMMAR</t>
-        </is>
-      </c>
-      <c r="I44" t="n">
+      <c r="E45" s="1" t="n">
+        <v>46324</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>VÄSTMANLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>HALLSTAHAMMAR</t>
+        </is>
+      </c>
+      <c r="I45" t="n">
         <v>32.5</v>
       </c>
-      <c r="J44" t="n">
-        <v>0</v>
-      </c>
-      <c r="K44" t="n">
-        <v>0</v>
-      </c>
-      <c r="L44" t="n">
-        <v>0</v>
-      </c>
-      <c r="M44" t="n">
-        <v>0</v>
-      </c>
-      <c r="N44" t="n">
-        <v>0</v>
-      </c>
-      <c r="O44" t="n">
-        <v>0</v>
-      </c>
-      <c r="P44" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q44" t="n">
-        <v>0</v>
-      </c>
-      <c r="R44" t="n">
-        <v>0</v>
-      </c>
-      <c r="S44" t="n">
-        <v>0</v>
-      </c>
-      <c r="T44" t="n">
-        <v>0</v>
-      </c>
-      <c r="U44" t="n">
-        <v>0</v>
-      </c>
-      <c r="V44" s="2" t="inlineStr"/>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
+      <c r="J45" t="n">
+        <v>0</v>
+      </c>
+      <c r="K45" t="n">
+        <v>0</v>
+      </c>
+      <c r="L45" t="n">
+        <v>0</v>
+      </c>
+      <c r="M45" t="n">
+        <v>0</v>
+      </c>
+      <c r="N45" t="n">
+        <v>0</v>
+      </c>
+      <c r="O45" t="n">
+        <v>0</v>
+      </c>
+      <c r="P45" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q45" t="n">
+        <v>0</v>
+      </c>
+      <c r="R45" t="n">
+        <v>0</v>
+      </c>
+      <c r="S45" t="n">
+        <v>0</v>
+      </c>
+      <c r="T45" t="n">
+        <v>0</v>
+      </c>
+      <c r="U45" t="n">
+        <v>0</v>
+      </c>
+      <c r="V45" s="2" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
         <is>
           <t>S 924-2026</t>
         </is>
       </c>
-      <c r="B45" t="inlineStr">
+      <c r="B46" t="inlineStr">
         <is>
           <t>samrådsanmälan</t>
         </is>
       </c>
-      <c r="C45" t="inlineStr">
+      <c r="C46" t="inlineStr">
         <is>
           <t>Skogsgödsling</t>
         </is>
       </c>
-      <c r="D45" s="1" t="n">
+      <c r="D46" s="1" t="n">
         <v>46111</v>
       </c>
-      <c r="E45" s="1" t="n">
-        <v>46323</v>
-      </c>
-      <c r="F45" t="inlineStr">
-        <is>
-          <t>VÄSTMANLANDS LÄN</t>
-        </is>
-      </c>
-      <c r="G45" t="inlineStr">
-        <is>
-          <t>HALLSTAHAMMAR</t>
-        </is>
-      </c>
-      <c r="H45" t="inlineStr">
+      <c r="E46" s="1" t="n">
+        <v>46324</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>VÄSTMANLANDS LÄN</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>HALLSTAHAMMAR</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
         <is>
           <t>Allmännings- och besparingsskogar</t>
         </is>
       </c>
-      <c r="I45" t="n">
+      <c r="I46" t="n">
         <v>48.8</v>
       </c>
-      <c r="J45" t="n">
-        <v>0</v>
-      </c>
-      <c r="K45" t="n">
-        <v>0</v>
-      </c>
-      <c r="L45" t="n">
-        <v>0</v>
-      </c>
-      <c r="M45" t="n">
-        <v>0</v>
-      </c>
-      <c r="N45" t="n">
-        <v>0</v>
-      </c>
-      <c r="O45" t="n">
-        <v>0</v>
-      </c>
-      <c r="P45" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q45" t="n">
-        <v>0</v>
-      </c>
-      <c r="R45" t="n">
-        <v>0</v>
-      </c>
-      <c r="S45" t="n">
-        <v>0</v>
-      </c>
-      <c r="T45" t="n">
-        <v>0</v>
-      </c>
-      <c r="U45" t="n">
-        <v>0</v>
-      </c>
-      <c r="V45" s="2" t="inlineStr"/>
+      <c r="J46" t="n">
+        <v>0</v>
+      </c>
+      <c r="K46" t="n">
+        <v>0</v>
+      </c>
+      <c r="L46" t="n">
+        <v>0</v>
+      </c>
+      <c r="M46" t="n">
+        <v>0</v>
+      </c>
+      <c r="N46" t="n">
+        <v>0</v>
+      </c>
+      <c r="O46" t="n">
+        <v>0</v>
+      </c>
+      <c r="P46" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q46" t="n">
+        <v>0</v>
+      </c>
+      <c r="R46" t="n">
+        <v>0</v>
+      </c>
+      <c r="S46" t="n">
+        <v>0</v>
+      </c>
+      <c r="T46" t="n">
+        <v>0</v>
+      </c>
+      <c r="U46" t="n">
+        <v>0</v>
+      </c>
+      <c r="V46" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Översikt HALLSTAHAMMAR.xlsx
+++ b/Översikt HALLSTAHAMMAR.xlsx
@@ -601,7 +601,7 @@
         <v>45978</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -714,7 +714,7 @@
         <v>44635</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -792,7 +792,7 @@
         <v>44887</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -865,7 +865,7 @@
         <v>44502</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -938,7 +938,7 @@
         <v>44502</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1011,7 +1011,7 @@
         <v>44739</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1067,7 +1067,7 @@
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A 8436-2023</t>
+          <t>A 68621-2021</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1081,10 +1081,10 @@
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>44977</v>
+        <v>44502</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1096,13 +1096,8 @@
           <t>HALLSTAHAMMAR</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I8" t="n">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -1145,7 +1140,7 @@
     <row r="9" ht="15" customHeight="1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A 68621-2021</t>
+          <t>A 21264-2022</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1159,10 +1154,10 @@
         </is>
       </c>
       <c r="D9" s="1" t="n">
-        <v>44502</v>
+        <v>44705</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1174,8 +1169,13 @@
           <t>HALLSTAHAMMAR</t>
         </is>
       </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I9" t="n">
-        <v>3.8</v>
+        <v>2.4</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -1218,7 +1218,7 @@
     <row r="10" ht="15" customHeight="1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A 7245-2025</t>
+          <t>A 21972-2023</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1232,10 +1232,10 @@
         </is>
       </c>
       <c r="D10" s="1" t="n">
-        <v>45702</v>
+        <v>45068</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1248,7 +1248,7 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>4</v>
+        <v>1.5</v>
       </c>
       <c r="J10" t="n">
         <v>0</v>
@@ -1291,7 +1291,7 @@
     <row r="11" ht="15" customHeight="1">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A 21264-2022</t>
+          <t>A 10263-2024</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1305,10 +1305,10 @@
         </is>
       </c>
       <c r="D11" s="1" t="n">
-        <v>44705</v>
+        <v>45365</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1322,11 +1322,11 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Allmännings- och besparingsskogar</t>
+          <t>Kyrkan</t>
         </is>
       </c>
       <c r="I11" t="n">
-        <v>2.4</v>
+        <v>1.4</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -1369,7 +1369,7 @@
     <row r="12" ht="15" customHeight="1">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A 34984-2024</t>
+          <t>A 55562-2022</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1383,10 +1383,10 @@
         </is>
       </c>
       <c r="D12" s="1" t="n">
-        <v>45527</v>
+        <v>44888</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1399,7 +1399,7 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>4.1</v>
+        <v>0.8</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -1442,7 +1442,7 @@
     <row r="13" ht="15" customHeight="1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A 21972-2023</t>
+          <t>A 12077-2022</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1456,10 +1456,10 @@
         </is>
       </c>
       <c r="D13" s="1" t="n">
-        <v>45068</v>
+        <v>44636</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1472,7 +1472,7 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>1.5</v>
+        <v>2.1</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
@@ -1532,7 +1532,7 @@
         <v>45909</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1605,7 +1605,7 @@
         <v>45911</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1678,7 +1678,7 @@
         <v>45915</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1734,7 +1734,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 16762-2022</t>
+          <t>A 37407-2023</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1748,10 +1748,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>44673</v>
+        <v>45156</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1764,7 +1764,7 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>4.2</v>
+        <v>3.3</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -1824,7 +1824,7 @@
         <v>45875</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -1897,7 +1897,7 @@
         <v>45875</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -1953,7 +1953,7 @@
     <row r="20" ht="15" customHeight="1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A 22072-2023</t>
+          <t>A 13510-2025</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1967,10 +1967,10 @@
         </is>
       </c>
       <c r="D20" s="1" t="n">
-        <v>45069</v>
+        <v>45736</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -1983,7 +1983,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>3.5</v>
+        <v>2.5</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2026,7 +2026,7 @@
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 13510-2025</t>
+          <t>A 58109-2025</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2040,10 +2040,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>45736</v>
+        <v>45982</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2099,7 +2099,7 @@
     <row r="22" ht="15" customHeight="1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A 30766-2022</t>
+          <t>A 58111-2025</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2113,10 +2113,10 @@
         </is>
       </c>
       <c r="D22" s="1" t="n">
-        <v>44764</v>
+        <v>45982</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2172,7 +2172,7 @@
     <row r="23" ht="15" customHeight="1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A 21049-2026</t>
+          <t>A 58125-2025</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2186,10 +2186,10 @@
         </is>
       </c>
       <c r="D23" s="1" t="n">
-        <v>46146</v>
+        <v>45982</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2202,7 +2202,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>2.9</v>
+        <v>0.8</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2245,7 +2245,7 @@
     <row r="24" ht="15" customHeight="1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A 35036-2024</t>
+          <t>A 14149-2022</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2259,10 +2259,10 @@
         </is>
       </c>
       <c r="D24" s="1" t="n">
-        <v>45527</v>
+        <v>44651</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -2274,8 +2274,13 @@
           <t>HALLSTAHAMMAR</t>
         </is>
       </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Allmännings- och besparingsskogar</t>
+        </is>
+      </c>
       <c r="I24" t="n">
-        <v>1.7</v>
+        <v>3.8</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -2318,7 +2323,7 @@
     <row r="25" ht="15" customHeight="1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A 58109-2025</t>
+          <t>A 53343-2024</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2332,10 +2337,10 @@
         </is>
       </c>
       <c r="D25" s="1" t="n">
-        <v>45982</v>
+        <v>45614</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2348,7 +2353,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>2.5</v>
+        <v>0.9</v>
       </c>
       <c r="J25" t="n">
         <v>0</v>
@@ -2391,7 +2396,7 @@
     <row r="26" ht="15" customHeight="1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A 58111-2025</t>
+          <t>A 8436-2023</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2405,10 +2410,10 @@
         </is>
       </c>
       <c r="D26" s="1" t="n">
-        <v>45982</v>
+        <v>44977</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2420,8 +2425,13 @@
           <t>HALLSTAHAMMAR</t>
         </is>
       </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Kyrkan</t>
+        </is>
+      </c>
       <c r="I26" t="n">
-        <v>0.6</v>
+        <v>4</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2464,7 +2474,7 @@
     <row r="27" ht="15" customHeight="1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A 58125-2025</t>
+          <t>A 7245-2025</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2478,10 +2488,10 @@
         </is>
       </c>
       <c r="D27" s="1" t="n">
-        <v>45982</v>
+        <v>45702</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2494,7 +2504,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>0.8</v>
+        <v>4</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -2537,7 +2547,7 @@
     <row r="28" ht="15" customHeight="1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A 54207-2025</t>
+          <t>A 34984-2024</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2551,10 +2561,10 @@
         </is>
       </c>
       <c r="D28" s="1" t="n">
-        <v>45964</v>
+        <v>45527</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2567,7 +2577,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>2.1</v>
+        <v>4.1</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -2610,7 +2620,7 @@
     <row r="29" ht="15" customHeight="1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A 10263-2024</t>
+          <t>A 16762-2022</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2624,10 +2634,10 @@
         </is>
       </c>
       <c r="D29" s="1" t="n">
-        <v>45365</v>
+        <v>44673</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2639,13 +2649,8 @@
           <t>HALLSTAHAMMAR</t>
         </is>
       </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>Kyrkan</t>
-        </is>
-      </c>
       <c r="I29" t="n">
-        <v>1.4</v>
+        <v>4.2</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -2688,7 +2693,7 @@
     <row r="30" ht="15" customHeight="1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A 55562-2022</t>
+          <t>A 21049-2026</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2702,10 +2707,10 @@
         </is>
       </c>
       <c r="D30" s="1" t="n">
-        <v>44888</v>
+        <v>46146</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -2718,7 +2723,7 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>0.8</v>
+        <v>2.9</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -2761,7 +2766,7 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A 26059-2026</t>
+          <t>A 54207-2025</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2775,10 +2780,10 @@
         </is>
       </c>
       <c r="D31" s="1" t="n">
-        <v>46181</v>
+        <v>45964</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -2791,7 +2796,7 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>4.7</v>
+        <v>2.1</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -2834,7 +2839,7 @@
     <row r="32" ht="15" customHeight="1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A 26060-2026</t>
+          <t>A 22072-2023</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2848,10 +2853,10 @@
         </is>
       </c>
       <c r="D32" s="1" t="n">
-        <v>46181</v>
+        <v>45069</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -2864,7 +2869,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -2907,7 +2912,7 @@
     <row r="33" ht="15" customHeight="1">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A 62831-2023</t>
+          <t>A 30766-2022</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2921,10 +2926,10 @@
         </is>
       </c>
       <c r="D33" s="1" t="n">
-        <v>45270</v>
+        <v>44764</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -2937,7 +2942,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>1.1</v>
+        <v>0.6</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -2980,7 +2985,7 @@
     <row r="34" ht="15" customHeight="1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A 12077-2022</t>
+          <t>A 35036-2024</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2994,10 +2999,10 @@
         </is>
       </c>
       <c r="D34" s="1" t="n">
-        <v>44636</v>
+        <v>45527</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -3010,7 +3015,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>2.1</v>
+        <v>1.7</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -3053,7 +3058,7 @@
     <row r="35" ht="15" customHeight="1">
       <c r="A35" t="inlineStr">
         <is>
-          <t>A 37407-2023</t>
+          <t>A 26059-2026</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3067,10 +3072,10 @@
         </is>
       </c>
       <c r="D35" s="1" t="n">
-        <v>45156</v>
+        <v>46181</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -3083,7 +3088,7 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>3.3</v>
+        <v>4.7</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -3126,7 +3131,7 @@
     <row r="36" ht="15" customHeight="1">
       <c r="A36" t="inlineStr">
         <is>
-          <t>A 35238-2026</t>
+          <t>A 26060-2026</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3136,14 +3141,14 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D36" s="1" t="n">
-        <v>46260</v>
+        <v>46181</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -3156,7 +3161,7 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>3.3</v>
+        <v>3.6</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3199,7 +3204,7 @@
     <row r="37" ht="15" customHeight="1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>A 41863-2026</t>
+          <t>A 62831-2023</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3213,10 +3218,10 @@
         </is>
       </c>
       <c r="D37" s="1" t="n">
-        <v>46303</v>
+        <v>45270</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -3229,7 +3234,7 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>1.9</v>
+        <v>1.1</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -3272,7 +3277,7 @@
     <row r="38" ht="15" customHeight="1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>A 37109-2026</t>
+          <t>A 35238-2026</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3282,14 +3287,14 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D38" s="1" t="n">
-        <v>46274</v>
+        <v>46260</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -3302,7 +3307,7 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>3</v>
+        <v>3.3</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -3345,7 +3350,7 @@
     <row r="39" ht="15" customHeight="1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>A 14149-2022</t>
+          <t>A 41863-2026</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3359,10 +3364,10 @@
         </is>
       </c>
       <c r="D39" s="1" t="n">
-        <v>44651</v>
+        <v>46303</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -3374,13 +3379,8 @@
           <t>HALLSTAHAMMAR</t>
         </is>
       </c>
-      <c r="H39" t="inlineStr">
-        <is>
-          <t>Allmännings- och besparingsskogar</t>
-        </is>
-      </c>
       <c r="I39" t="n">
-        <v>3.8</v>
+        <v>1.9</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3423,7 +3423,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 8848-2025</t>
+          <t>A 37109-2026</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3437,10 +3437,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45713</v>
+        <v>46274</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -3453,7 +3453,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -3496,7 +3496,7 @@
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 53343-2024</t>
+          <t>A 8848-2025</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3510,10 +3510,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45614</v>
+        <v>45713</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3526,7 +3526,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>0.9</v>
+        <v>2</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -3586,7 +3586,7 @@
         <v>46322</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3659,7 +3659,7 @@
         <v>46322</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -3732,7 +3732,7 @@
         <v>46322</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -3805,7 +3805,7 @@
         <v>46091</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -3878,7 +3878,7 @@
         <v>46111</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46324</v>
+        <v>46326</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
